--- a/FOA Singles/Youth-Single.xlsx
+++ b/FOA Singles/Youth-Single.xlsx
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC337"/>
+  <dimension ref="A1:AC336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39484,24 +39484,14 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>NOT AVAILABLE</t>
-        </is>
-      </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Gray</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Gray [NOT AVAILABLE]</t>
+          <t>White/Gray</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>FM-TR452-GY</t>
+          <t>CM7467WH-TR</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -39516,134 +39506,10 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>OMNUS Trundle w/ 2 Dividers</t>
+          <t>PRIAM Trundle or Drawers</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
-        <is>
-          <t>FREE SHIPPING
-OMNUS Trundle w/ 2 Dividers adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth trundle, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, Others, it is finished in Gray tones that pair easily with surrounding decor.
-Product Dimensions: 74 1 or 4" W x 40 1 or 2"D x 10 3 or 4" H
-Size: Gray [NOT AVAILABLE]
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer, Others
-Color: Gray
-Weight: 41.8 lbs</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>OMNUS Trundle w/ 2 Dividers Gray [NOT AVAILABLE] in Gray | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="J324" t="inlineStr">
-        <is>
-          <t>The OMNUS Trundle w/ Dividers brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
-        </is>
-      </c>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t>OMNUS</t>
-        </is>
-      </c>
-      <c r="L324" t="inlineStr">
-        <is>
-          <t>Trundle w/ 2 Dividers, Gray [NOT AVAILABLE]</t>
-        </is>
-      </c>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>Gray [NOT AVAILABLE] NOT AVAILABLE</t>
-        </is>
-      </c>
-      <c r="N324" t="inlineStr">
-        <is>
-          <t>Single Item</t>
-        </is>
-      </c>
-      <c r="P324" t="inlineStr">
-        <is>
-          <t>FM-TR452-GY.jpg</t>
-        </is>
-      </c>
-      <c r="Q324" t="n">
-        <v>109</v>
-      </c>
-      <c r="R324" s="1" t="n">
-        <v>109</v>
-      </c>
-      <c r="S324" t="n">
-        <v>237</v>
-      </c>
-      <c r="T324" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="U324" t="inlineStr">
-        <is>
-          <t>74 1/4"W X 40 1/2"D X 10 3/4"H</t>
-        </is>
-      </c>
-      <c r="V324" t="inlineStr">
-        <is>
-          <t>Transitional</t>
-        </is>
-      </c>
-      <c r="W324" t="inlineStr">
-        <is>
-          <t>Solid Wood, Wood Veneer, Others</t>
-        </is>
-      </c>
-      <c r="X324" t="inlineStr">
-        <is>
-          <t>Transitional,Gray,Solid Wood, Wood Veneer, Others</t>
-        </is>
-      </c>
-      <c r="Y324" t="inlineStr">
-        <is>
-          <t>MY</t>
-        </is>
-      </c>
-      <c r="Z324" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="AA324" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="AB324" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AC324" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>White/Gray</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>CM7467WH-TR</t>
-        </is>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>Youth</t>
-        </is>
-      </c>
-      <c r="F325" s="24" t="inlineStr">
-        <is>
-          <t>Trundle</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>PRIAM Trundle or Drawers</t>
-        </is>
-      </c>
-      <c r="H325" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Elevate your space with PRIAM Trundle or Drawers, styled in Contemporary and designed for everyday comfort. Built as a youth trundle, it pairs well with a wide range of interiors. With Solid Wood, Others and White  or  Gray tones, it blends structure and softness in one clean profile.
@@ -39657,113 +39523,113 @@
 Weight: 82.3 lbs</t>
         </is>
       </c>
-      <c r="I325" t="inlineStr">
+      <c r="I324" t="inlineStr">
         <is>
           <t>PRIAM Trundle or Drawers in White  or  Gray | GOODDEGG</t>
         </is>
       </c>
-      <c r="J325" t="inlineStr">
+      <c r="J324" t="inlineStr">
         <is>
           <t>The PRIAM Trundle or Drawers brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr">
+      <c r="K324" t="inlineStr">
         <is>
           <t>PRIAM</t>
         </is>
       </c>
-      <c r="L325" t="inlineStr">
+      <c r="L324" t="inlineStr">
         <is>
           <t>Trundle/Drawers</t>
         </is>
       </c>
-      <c r="N325" t="inlineStr">
+      <c r="N324" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P325" t="inlineStr">
+      <c r="P324" t="inlineStr">
         <is>
           <t>CM7467WH-3.jpg,FOA7467WH-TR-1-Z.jpg</t>
         </is>
       </c>
-      <c r="Q325" t="n">
+      <c r="Q324" t="n">
         <v>100</v>
       </c>
-      <c r="R325" s="2" t="n">
+      <c r="R324" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="S325" t="n">
+      <c r="S324" t="n">
         <v>270</v>
       </c>
-      <c r="T325" t="n">
+      <c r="T324" t="n">
         <v>82.3</v>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="U324" t="inlineStr">
         <is>
           <t>75 5/8"L X 40 3/4"W X 11"H</t>
         </is>
       </c>
-      <c r="V325" t="inlineStr">
+      <c r="V324" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W325" t="inlineStr">
+      <c r="W324" t="inlineStr">
         <is>
           <t>Solid Wood, Others</t>
         </is>
       </c>
-      <c r="X325" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>Contemporary,White/Gray,Solid Wood, Others,Trundle Converts to Drawers,Mattress Ready</t>
         </is>
       </c>
-      <c r="Y325" t="inlineStr">
+      <c r="Y324" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Z325" t="n">
+      <c r="Z324" t="n">
         <v>82.3</v>
       </c>
-      <c r="AA325" t="n">
+      <c r="AA324" t="n">
         <v>13.1</v>
       </c>
-      <c r="AB325" t="n">
+      <c r="AB324" t="n">
         <v>5.9</v>
       </c>
-      <c r="AC325" t="n">
+      <c r="AC324" t="n">
         <v>3.7</v>
       </c>
     </row>
-    <row r="326">
-      <c r="B326" t="inlineStr">
+    <row r="325">
+      <c r="B325" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr">
+      <c r="D325" t="inlineStr">
         <is>
           <t>CM7159WH-AR-VN</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr">
+      <c r="E325" t="inlineStr">
         <is>
           <t>Youth</t>
         </is>
       </c>
-      <c r="F326" s="27" t="inlineStr">
+      <c r="F325" s="27" t="inlineStr">
         <is>
           <t>Armoire</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr">
+      <c r="G325" t="inlineStr">
         <is>
           <t>DANI Armoire</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr">
+      <c r="H325" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 DANI Armoire adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth armoire, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, Others, it is finished in White tones that pair easily with surrounding decor.
@@ -39775,113 +39641,113 @@
 Weight: 114.4 lbs</t>
         </is>
       </c>
-      <c r="I326" t="inlineStr">
+      <c r="I325" t="inlineStr">
         <is>
           <t>DANI Armoire in White | GOODDEGG</t>
         </is>
       </c>
-      <c r="J326" t="inlineStr">
+      <c r="J325" t="inlineStr">
         <is>
           <t>The DANI Armoire brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr">
+      <c r="K325" t="inlineStr">
         <is>
           <t>DANI</t>
         </is>
       </c>
-      <c r="L326" t="inlineStr">
+      <c r="L325" t="inlineStr">
         <is>
           <t>Armoire</t>
         </is>
       </c>
-      <c r="N326" t="inlineStr">
+      <c r="N325" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P326" t="inlineStr">
+      <c r="P325" t="inlineStr">
         <is>
           <t>CM7159WH-AR-3.jpg,CM7159WH-AR-4.jpg,CM7159WH-AR-5.jpg,CM7159WH-AR-6.jpg,CM7159WH-AR-3-Z.jpg,CM7159WH-AR-WB.jpg</t>
         </is>
       </c>
-      <c r="Q326" t="n">
+      <c r="Q325" t="n">
         <v>289</v>
       </c>
-      <c r="R326" s="2" t="n">
+      <c r="R325" s="2" t="n">
         <v>289</v>
       </c>
-      <c r="S326" t="n">
+      <c r="S325" t="n">
         <v>717</v>
       </c>
-      <c r="T326" t="n">
+      <c r="T325" t="n">
         <v>114.4</v>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="U325" t="inlineStr">
         <is>
           <t>32 1/8"W X 16"D X 51 1/4"H</t>
         </is>
       </c>
-      <c r="V326" t="inlineStr">
+      <c r="V325" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="W326" t="inlineStr">
+      <c r="W325" t="inlineStr">
         <is>
           <t>Solid Wood, Wood Veneer, Others</t>
         </is>
       </c>
-      <c r="X326" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>Transitional,White,Solid Wood, Wood Veneer, Others</t>
         </is>
       </c>
-      <c r="Y326" t="inlineStr">
+      <c r="Y325" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Z326" t="n">
+      <c r="Z325" t="n">
         <v>35.6</v>
       </c>
-      <c r="AA326" t="n">
+      <c r="AA325" t="n">
         <v>19.5</v>
       </c>
-      <c r="AB326" t="n">
+      <c r="AB325" t="n">
         <v>56</v>
       </c>
-      <c r="AC326" t="n">
+      <c r="AC325" t="n">
         <v>22.5</v>
       </c>
     </row>
-    <row r="327">
-      <c r="B327" t="inlineStr">
+    <row r="326">
+      <c r="B326" t="inlineStr">
         <is>
           <t>Wire-Brushed Warm Gray</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr">
+      <c r="D326" t="inlineStr">
         <is>
           <t>FOA7175AR</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr">
+      <c r="E326" t="inlineStr">
         <is>
           <t>Youth</t>
         </is>
       </c>
-      <c r="F327" s="27" t="inlineStr">
+      <c r="F326" s="27" t="inlineStr">
         <is>
           <t>Armoire</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr">
+      <c r="G326" t="inlineStr">
         <is>
           <t>VEVEY Armoire</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr">
+      <c r="H326" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 VEVEY Armoire adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth armoire, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, Others, it is finished in Wire-Brushed Warm Gray tones that pair easily with surrounding decor.
@@ -39895,113 +39761,113 @@
 Weight: 156.2 lbs</t>
         </is>
       </c>
-      <c r="I327" t="inlineStr">
+      <c r="I326" t="inlineStr">
         <is>
           <t>VEVEY Armoire in Wire-Brushed Warm Gray | GOODDEGG</t>
         </is>
       </c>
-      <c r="J327" t="inlineStr">
+      <c r="J326" t="inlineStr">
         <is>
           <t>The VEVEY Armoire brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr">
+      <c r="K326" t="inlineStr">
         <is>
           <t>VEVEY</t>
         </is>
       </c>
-      <c r="L327" t="inlineStr">
+      <c r="L326" t="inlineStr">
         <is>
           <t>Armoire</t>
         </is>
       </c>
-      <c r="N327" t="inlineStr">
+      <c r="N326" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P327" t="inlineStr">
+      <c r="P326" t="inlineStr">
         <is>
           <t>FOA7175AR-1.jpg,FOA7175-1-Z.jpg</t>
         </is>
       </c>
-      <c r="Q327" t="n">
+      <c r="Q326" t="n">
         <v>369</v>
       </c>
-      <c r="R327" s="1" t="n">
+      <c r="R326" s="1" t="n">
         <v>399</v>
       </c>
-      <c r="S327" t="n">
+      <c r="S326" t="n">
         <v>897</v>
       </c>
-      <c r="T327" t="n">
+      <c r="T326" t="n">
         <v>156.2</v>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="U326" t="inlineStr">
         <is>
           <t>40"L X 18"W X 47 3/4"H</t>
         </is>
       </c>
-      <c r="V327" t="inlineStr">
+      <c r="V326" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="W327" t="inlineStr">
+      <c r="W326" t="inlineStr">
         <is>
           <t>Solid Wood, Wood Veneer, Others</t>
         </is>
       </c>
-      <c r="X327" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>Transitional,Wire-Brushed Warm Gray,Solid Wood, Wood Veneer, Others,Felt-lined Top Drawer,Round Pull Knobs,Wood Grain Texture</t>
         </is>
       </c>
-      <c r="Y327" t="inlineStr">
+      <c r="Y326" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Z327" t="n">
+      <c r="Z326" t="n">
         <v>42.8</v>
       </c>
-      <c r="AA327" t="n">
+      <c r="AA326" t="n">
         <v>21</v>
       </c>
-      <c r="AB327" t="n">
+      <c r="AB326" t="n">
         <v>52.8</v>
       </c>
-      <c r="AC327" t="n">
+      <c r="AC326" t="n">
         <v>27.4</v>
       </c>
     </row>
-    <row r="328">
-      <c r="B328" t="inlineStr">
+    <row r="327">
+      <c r="B327" t="inlineStr">
         <is>
           <t>Pearl White</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr">
+      <c r="D327" t="inlineStr">
         <is>
           <t>FM72081WH-N</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr">
+      <c r="E327" t="inlineStr">
         <is>
           <t>Youth</t>
         </is>
       </c>
-      <c r="F328" s="30" t="inlineStr">
+      <c r="F327" s="30" t="inlineStr">
         <is>
           <t>Nightstand</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr">
+      <c r="G327" t="inlineStr">
         <is>
           <t>LAREINA Nightstand</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr">
+      <c r="H327" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 LAREINA Nightstand brings a Contemporary look to your home with a refined, comfortable feel. This youth nightstand is made to fit naturally into the room. The Solid Rubberwood, Engineered Wood construction is complemented by Pearl White tones for a polished look.
@@ -40013,118 +39879,118 @@
 Weight: 59.97 lbs</t>
         </is>
       </c>
-      <c r="I328" t="inlineStr">
+      <c r="I327" t="inlineStr">
         <is>
           <t>LAREINA Nightstand in Pearl White | GOODDEGG</t>
         </is>
       </c>
-      <c r="J328" t="inlineStr">
+      <c r="J327" t="inlineStr">
         <is>
           <t>The LAREINA Nightstand keeps bedside essentials organized and within reach. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr">
+      <c r="K327" t="inlineStr">
         <is>
           <t>LAREINA</t>
         </is>
       </c>
-      <c r="L328" t="inlineStr">
+      <c r="L327" t="inlineStr">
         <is>
           <t>Nightstand</t>
         </is>
       </c>
-      <c r="N328" t="inlineStr">
+      <c r="N327" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P328" t="inlineStr">
+      <c r="P327" t="inlineStr">
         <is>
           <t>FM72081WH-N-1.jpg,FM72081WH-T-1-Z.jpg,FM72081WH-N-2.jpg,FM72081WH-N-3.jpg</t>
         </is>
       </c>
-      <c r="Q328" t="n">
+      <c r="Q327" t="n">
         <v>200</v>
       </c>
-      <c r="R328" s="1" t="n">
+      <c r="R327" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="S328" t="n">
+      <c r="S327" t="n">
         <v>510</v>
       </c>
-      <c r="T328" t="n">
+      <c r="T327" t="n">
         <v>59.97</v>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="U327" t="inlineStr">
         <is>
           <t>22.5"W X 17"D X 24"H</t>
         </is>
       </c>
-      <c r="V328" t="inlineStr">
+      <c r="V327" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="W328" t="inlineStr">
+      <c r="W327" t="inlineStr">
         <is>
           <t>Solid Rubberwood, Engineered Wood</t>
         </is>
       </c>
-      <c r="X328" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>Contemporary,Pearl White,Solid Rubberwood, Engineered Wood,Embossed Panels,Acrylic Handles &amp; Front Legs w/ Back Metal Legs,Felt-Lined Top Drawer,Metal Glide,English Dovetails</t>
         </is>
       </c>
-      <c r="Y328" t="inlineStr">
+      <c r="Y327" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="Z328" t="n">
+      <c r="Z327" t="n">
         <v>25.4</v>
       </c>
-      <c r="AA328" t="n">
+      <c r="AA327" t="n">
         <v>19.6</v>
       </c>
-      <c r="AB328" t="n">
+      <c r="AB327" t="n">
         <v>24.4</v>
       </c>
-      <c r="AC328" t="n">
+      <c r="AC327" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="329">
-      <c r="B329" t="inlineStr">
+    <row r="328">
+      <c r="B328" t="inlineStr">
         <is>
           <t>Gray</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr">
+      <c r="C328" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr">
+      <c r="D328" t="inlineStr">
         <is>
           <t>AM-BK304GY-BED</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr">
+      <c r="E328" t="inlineStr">
         <is>
           <t>Youth</t>
         </is>
       </c>
-      <c r="F329" s="32" t="inlineStr">
+      <c r="F328" s="32" t="inlineStr">
         <is>
           <t>Day Bed</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr">
+      <c r="G328" t="inlineStr">
         <is>
           <t>MARINOS Captain Bed</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr">
+      <c r="H328" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Make the room feel complete with MARINOS Captain Bed and its Rustic character. This youth day bed is made to fit naturally into the room. Finished in Gray tones, the Solid Wood, Others build balances durability with visual appeal.
@@ -40139,114 +40005,114 @@
 Weight: 171 lbs</t>
         </is>
       </c>
-      <c r="I329" t="inlineStr">
+      <c r="I328" t="inlineStr">
         <is>
           <t>MARINOS Captain Bed Twin in Gray | GOODDEGG</t>
         </is>
       </c>
-      <c r="J329" t="inlineStr">
+      <c r="J328" t="inlineStr">
         <is>
           <t>The MARINOS Captain Bed creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr">
+      <c r="K328" t="inlineStr">
         <is>
           <t>MARINOS</t>
         </is>
       </c>
-      <c r="L329" t="inlineStr">
+      <c r="L328" t="inlineStr">
         <is>
           <t>Twin Captain Bed</t>
         </is>
       </c>
-      <c r="N329" t="inlineStr">
+      <c r="N328" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="O329" t="inlineStr">
+      <c r="O328" t="inlineStr">
         <is>
           <t>AM-BK304GY-1, AM-BK304GY-2, AM-BK304GY-3, AM-BK304GY-4, AM-BK304GY-5, AM-SL109-T</t>
         </is>
       </c>
-      <c r="P329" t="inlineStr">
+      <c r="P328" t="inlineStr">
         <is>
           <t>AM-BK304GY-1.jpg</t>
         </is>
       </c>
-      <c r="Q329" t="n">
+      <c r="Q328" t="n">
         <v>449</v>
       </c>
-      <c r="R329" s="1" t="n">
+      <c r="R328" s="1" t="n">
         <v>449</v>
       </c>
-      <c r="S329" t="n">
+      <c r="S328" t="n">
         <v>1347</v>
       </c>
-      <c r="T329" t="n">
+      <c r="T328" t="n">
         <v>171</v>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="U328" t="inlineStr">
         <is>
           <t>78"W X 41"D X 34"H</t>
         </is>
       </c>
-      <c r="V329" t="inlineStr">
+      <c r="V328" t="inlineStr">
         <is>
           <t>Rustic</t>
         </is>
       </c>
-      <c r="W329" t="inlineStr">
+      <c r="W328" t="inlineStr">
         <is>
           <t>Solid Wood, Others</t>
         </is>
       </c>
-      <c r="X329" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>Rustic,Gray,Solid Wood, Others,Fits up to 6" Mattress,Large Underbed Drawers,Bronze Round Knobs,Brazilian Pine Construction</t>
         </is>
       </c>
-      <c r="Y329" t="inlineStr">
+      <c r="Y328" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="AC329" t="n">
+      <c r="AC328" t="n">
         <v>22.3</v>
       </c>
     </row>
-    <row r="330">
-      <c r="B330" t="inlineStr">
+    <row r="329">
+      <c r="B329" t="inlineStr">
         <is>
           <t>Mahogany</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr">
+      <c r="C329" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr">
+      <c r="D329" t="inlineStr">
         <is>
           <t>AM-BK304MH-BED</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr">
+      <c r="E329" t="inlineStr">
         <is>
           <t>Youth</t>
         </is>
       </c>
-      <c r="F330" s="32" t="inlineStr">
+      <c r="F329" s="32" t="inlineStr">
         <is>
           <t>Day Bed</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr">
+      <c r="G329" t="inlineStr">
         <is>
           <t>MARINOS Captain Bed</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr">
+      <c r="H329" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 MARINOS Captain Bed brings a Rustic look to your home with a refined, comfortable feel. Built as a youth day bed, it pairs well with a wide range of interiors. The Solid Wood, Others construction is complemented by Mahogany tones for a polished look.
@@ -40261,109 +40127,109 @@
 Weight: 171 lbs</t>
         </is>
       </c>
-      <c r="I330" t="inlineStr">
+      <c r="I329" t="inlineStr">
         <is>
           <t>MARINOS Captain Bed Twin in Mahogany | GOODDEGG</t>
         </is>
       </c>
-      <c r="J330" t="inlineStr">
+      <c r="J329" t="inlineStr">
         <is>
           <t>The MARINOS Captain Bed creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr">
+      <c r="K329" t="inlineStr">
         <is>
           <t>MARINOS</t>
         </is>
       </c>
-      <c r="L330" t="inlineStr">
+      <c r="L329" t="inlineStr">
         <is>
           <t>Twin Captain Bed</t>
         </is>
       </c>
-      <c r="N330" t="inlineStr">
+      <c r="N329" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="O330" t="inlineStr">
+      <c r="O329" t="inlineStr">
         <is>
           <t>AM-BK304MH-1, AM-BK304MH-2, AM-BK304MH-3, AM-BK304MH-4, AM-BK304MH-5, AM-SL109-T</t>
         </is>
       </c>
-      <c r="P330" t="inlineStr">
+      <c r="P329" t="inlineStr">
         <is>
           <t>AM-BK304MH-1.jpg</t>
         </is>
       </c>
-      <c r="Q330" t="n">
+      <c r="Q329" t="n">
         <v>449</v>
       </c>
-      <c r="R330" s="1" t="n">
+      <c r="R329" s="1" t="n">
         <v>449</v>
       </c>
-      <c r="S330" t="n">
+      <c r="S329" t="n">
         <v>1347</v>
       </c>
-      <c r="T330" t="n">
+      <c r="T329" t="n">
         <v>171</v>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="U329" t="inlineStr">
         <is>
           <t>78"W X 41"D X 34"H</t>
         </is>
       </c>
-      <c r="V330" t="inlineStr">
+      <c r="V329" t="inlineStr">
         <is>
           <t>Rustic</t>
         </is>
       </c>
-      <c r="W330" t="inlineStr">
+      <c r="W329" t="inlineStr">
         <is>
           <t>Solid Wood, Others</t>
         </is>
       </c>
-      <c r="X330" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>Rustic,Mahogany,Solid Wood, Others,Fits up to 6" Mattress,Large Underbed Drawers,Black Round Knobs,Brazilian Pine Construction</t>
         </is>
       </c>
-      <c r="Y330" t="inlineStr">
+      <c r="Y329" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="AC330" t="n">
+      <c r="AC329" t="n">
         <v>22.3</v>
       </c>
     </row>
-    <row r="331">
-      <c r="B331" t="inlineStr">
+    <row r="330">
+      <c r="B330" t="inlineStr">
         <is>
           <t>Cherry</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr">
+      <c r="D330" t="inlineStr">
         <is>
           <t>CM7905CH-DK</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr">
+      <c r="E330" t="inlineStr">
         <is>
           <t>Youth</t>
         </is>
       </c>
-      <c r="F331" s="34" t="inlineStr">
+      <c r="F330" s="34" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr">
+      <c r="G330" t="inlineStr">
         <is>
           <t>OMNUS Desk</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr">
+      <c r="H330" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 OMNUS Desk adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth desk, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, Others, it is finished in Cherry tones that pair easily with surrounding decor.
@@ -40375,113 +40241,113 @@
 Weight: 88.2 lbs</t>
         </is>
       </c>
-      <c r="I331" t="inlineStr">
+      <c r="I330" t="inlineStr">
         <is>
           <t>OMNUS Desk in Cherry | GOODDEGG</t>
         </is>
       </c>
-      <c r="J331" t="inlineStr">
+      <c r="J330" t="inlineStr">
         <is>
           <t>The OMNUS Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr">
+      <c r="K330" t="inlineStr">
         <is>
           <t>OMNUS</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr">
+      <c r="L330" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="N331" t="inlineStr">
+      <c r="N330" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P331" t="inlineStr">
+      <c r="P330" t="inlineStr">
         <is>
           <t>CM7905CH-DK.jpg,CM7905CH-DK+HC-tray.jpg</t>
         </is>
       </c>
-      <c r="Q331" t="n">
+      <c r="Q330" t="n">
         <v>289</v>
       </c>
-      <c r="R331" s="1" t="n">
+      <c r="R330" s="1" t="n">
         <v>312</v>
       </c>
-      <c r="S331" t="n">
+      <c r="S330" t="n">
         <v>690</v>
       </c>
-      <c r="T331" t="n">
+      <c r="T330" t="n">
         <v>88.2</v>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="U330" t="inlineStr">
         <is>
           <t>48"W X 20"D X 32"H</t>
         </is>
       </c>
-      <c r="V331" t="inlineStr">
+      <c r="V330" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="W331" t="inlineStr">
+      <c r="W330" t="inlineStr">
         <is>
           <t>Solid Wood, Wood Veneer, Others</t>
         </is>
       </c>
-      <c r="X331" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>Transitional,Cherry,Solid Wood, Wood Veneer, Others,Match w, Various Youth Beds</t>
         </is>
       </c>
-      <c r="Y331" t="inlineStr">
+      <c r="Y330" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Z331" t="n">
+      <c r="Z330" t="n">
         <v>23.5</v>
       </c>
-      <c r="AA331" t="n">
+      <c r="AA330" t="n">
         <v>51.5</v>
       </c>
-      <c r="AB331" t="n">
+      <c r="AB330" t="n">
         <v>36.5</v>
       </c>
-      <c r="AC331" t="n">
+      <c r="AC330" t="n">
         <v>25.6</v>
       </c>
     </row>
-    <row r="332">
-      <c r="B332" t="inlineStr">
+    <row r="331">
+      <c r="B331" t="inlineStr">
         <is>
           <t>Dark Walnut</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr">
+      <c r="D331" t="inlineStr">
         <is>
           <t>CM7905EXP-DK</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr">
+      <c r="E331" t="inlineStr">
         <is>
           <t>Youth</t>
         </is>
       </c>
-      <c r="F332" s="34" t="inlineStr">
+      <c r="F331" s="34" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr">
+      <c r="G331" t="inlineStr">
         <is>
           <t>OMNUS Desk</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr">
+      <c r="H331" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Make the room feel complete with OMNUS Desk and its Transitional character. As a youth desk, it is designed to complement your space. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, Others build balances durability with visual appeal.
@@ -40493,113 +40359,113 @@
 Weight: 88.2 lbs</t>
         </is>
       </c>
-      <c r="I332" t="inlineStr">
+      <c r="I331" t="inlineStr">
         <is>
           <t>OMNUS Desk in Dark Walnut | GOODDEGG</t>
         </is>
       </c>
-      <c r="J332" t="inlineStr">
+      <c r="J331" t="inlineStr">
         <is>
           <t>The OMNUS Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr">
+      <c r="K331" t="inlineStr">
         <is>
           <t>OMNUS</t>
         </is>
       </c>
-      <c r="L332" t="inlineStr">
+      <c r="L331" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="N332" t="inlineStr">
+      <c r="N331" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P332" t="inlineStr">
+      <c r="P331" t="inlineStr">
         <is>
           <t>CM7905EXP-DK.jpg,CM7905EXP-DK+HC.jpg</t>
         </is>
       </c>
-      <c r="Q332" t="n">
+      <c r="Q331" t="n">
         <v>289</v>
       </c>
-      <c r="R332" s="2" t="n">
+      <c r="R331" s="2" t="n">
         <v>289</v>
       </c>
-      <c r="S332" t="n">
+      <c r="S331" t="n">
         <v>657</v>
       </c>
-      <c r="T332" t="n">
+      <c r="T331" t="n">
         <v>88.2</v>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="U331" t="inlineStr">
         <is>
           <t>48"W X 20"D X 32"H</t>
         </is>
       </c>
-      <c r="V332" t="inlineStr">
+      <c r="V331" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="W332" t="inlineStr">
+      <c r="W331" t="inlineStr">
         <is>
           <t>Solid Wood, Wood Veneer, Others</t>
         </is>
       </c>
-      <c r="X332" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>Transitional,Dark Walnut,Solid Wood, Wood Veneer, Others,Match w, Various Youth Beds</t>
         </is>
       </c>
-      <c r="Y332" t="inlineStr">
+      <c r="Y331" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Z332" t="n">
+      <c r="Z331" t="n">
         <v>51</v>
       </c>
-      <c r="AA332" t="n">
+      <c r="AA331" t="n">
         <v>23</v>
       </c>
-      <c r="AB332" t="n">
+      <c r="AB331" t="n">
         <v>34.3</v>
       </c>
-      <c r="AC332" t="n">
+      <c r="AC331" t="n">
         <v>23.2</v>
       </c>
     </row>
-    <row r="333">
-      <c r="B333" t="inlineStr">
+    <row r="332">
+      <c r="B332" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr">
+      <c r="D332" t="inlineStr">
         <is>
           <t>CM7905WH-DK</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr">
+      <c r="E332" t="inlineStr">
         <is>
           <t>Youth</t>
         </is>
       </c>
-      <c r="F333" s="34" t="inlineStr">
+      <c r="F332" s="34" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr">
+      <c r="G332" t="inlineStr">
         <is>
           <t>OMNUS Desk</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr">
+      <c r="H332" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 OMNUS Desk brings a Transitional look to your home with a refined, comfortable feel. This youth desk is made to fit naturally into the room. The Solid Wood, Wood Veneer, Others construction is complemented by White tones for a polished look.
@@ -40611,113 +40477,113 @@
 Weight: 88.2 lbs</t>
         </is>
       </c>
-      <c r="I333" t="inlineStr">
+      <c r="I332" t="inlineStr">
         <is>
           <t>OMNUS Desk in White | GOODDEGG</t>
         </is>
       </c>
-      <c r="J333" t="inlineStr">
+      <c r="J332" t="inlineStr">
         <is>
           <t>The OMNUS Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr">
+      <c r="K332" t="inlineStr">
         <is>
           <t>OMNUS</t>
         </is>
       </c>
-      <c r="L333" t="inlineStr">
+      <c r="L332" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="N333" t="inlineStr">
+      <c r="N332" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P333" t="inlineStr">
+      <c r="P332" t="inlineStr">
         <is>
           <t>CM7905WH-DK.jpg</t>
         </is>
       </c>
-      <c r="Q333" t="n">
+      <c r="Q332" t="n">
         <v>289</v>
       </c>
-      <c r="R333" s="2" t="n">
+      <c r="R332" s="2" t="n">
         <v>289</v>
       </c>
-      <c r="S333" t="n">
+      <c r="S332" t="n">
         <v>657</v>
       </c>
-      <c r="T333" t="n">
+      <c r="T332" t="n">
         <v>88.2</v>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="U332" t="inlineStr">
         <is>
           <t>48"W X 20"D X 32"H</t>
         </is>
       </c>
-      <c r="V333" t="inlineStr">
+      <c r="V332" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="W333" t="inlineStr">
+      <c r="W332" t="inlineStr">
         <is>
           <t>Solid Wood, Wood Veneer, Others</t>
         </is>
       </c>
-      <c r="X333" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>Transitional,White,Solid Wood, Wood Veneer, Others,Match w, Various Youth Beds</t>
         </is>
       </c>
-      <c r="Y333" t="inlineStr">
+      <c r="Y332" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Z333" t="n">
+      <c r="Z332" t="n">
         <v>23.5</v>
       </c>
-      <c r="AA333" t="n">
+      <c r="AA332" t="n">
         <v>51.5</v>
       </c>
-      <c r="AB333" t="n">
+      <c r="AB332" t="n">
         <v>36.5</v>
       </c>
-      <c r="AC333" t="n">
+      <c r="AC332" t="n">
         <v>25.6</v>
       </c>
     </row>
-    <row r="334">
-      <c r="B334" t="inlineStr">
+    <row r="333">
+      <c r="B333" t="inlineStr">
         <is>
           <t>Cherry</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr">
+      <c r="D333" t="inlineStr">
         <is>
           <t>CM7905CH-HC</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr">
+      <c r="E333" t="inlineStr">
         <is>
           <t>Youth</t>
         </is>
       </c>
-      <c r="F334" s="34" t="inlineStr">
+      <c r="F333" s="34" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr">
+      <c r="G333" t="inlineStr">
         <is>
           <t>OMNUS Hutch</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr">
+      <c r="H333" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 OMNUS Hutch brings a Transitional look to your home with a refined, comfortable feel. Built as a youth desk, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, Others construction is complemented by Cherry tones for a polished look.
@@ -40729,113 +40595,113 @@
 Weight: 29.76 lbs</t>
         </is>
       </c>
-      <c r="I334" t="inlineStr">
+      <c r="I333" t="inlineStr">
         <is>
           <t>OMNUS Hutch in Cherry | GOODDEGG</t>
         </is>
       </c>
-      <c r="J334" t="inlineStr">
+      <c r="J333" t="inlineStr">
         <is>
           <t>The OMNUS Hutch creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr">
+      <c r="K333" t="inlineStr">
         <is>
           <t>OMNUS</t>
         </is>
       </c>
-      <c r="L334" t="inlineStr">
+      <c r="L333" t="inlineStr">
         <is>
           <t>Hutch</t>
         </is>
       </c>
-      <c r="N334" t="inlineStr">
+      <c r="N333" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P334" t="inlineStr">
+      <c r="P333" t="inlineStr">
         <is>
           <t>CM7905CH-HC.jpg,CM7903CH-Z.jpg</t>
         </is>
       </c>
-      <c r="Q334" t="n">
+      <c r="Q333" t="n">
         <v>110</v>
       </c>
-      <c r="R334" s="1" t="n">
+      <c r="R333" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="S334" t="n">
+      <c r="S333" t="n">
         <v>270</v>
       </c>
-      <c r="T334" t="n">
+      <c r="T333" t="n">
         <v>29.76</v>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="U333" t="inlineStr">
         <is>
           <t>46"W X 12"D X 24"H</t>
         </is>
       </c>
-      <c r="V334" t="inlineStr">
+      <c r="V333" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="W334" t="inlineStr">
+      <c r="W333" t="inlineStr">
         <is>
           <t>Solid Wood, Wood Veneer, Others</t>
         </is>
       </c>
-      <c r="X334" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>Transitional,Cherry,Solid Wood, Wood Veneer, Others,Match w, Various Youth Beds</t>
         </is>
       </c>
-      <c r="Y334" t="inlineStr">
+      <c r="Y333" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Z334" t="n">
+      <c r="Z333" t="n">
         <v>25.8</v>
       </c>
-      <c r="AA334" t="n">
+      <c r="AA333" t="n">
         <v>49</v>
       </c>
-      <c r="AB334" t="n">
+      <c r="AB333" t="n">
         <v>12.8</v>
       </c>
-      <c r="AC334" t="n">
+      <c r="AC333" t="n">
         <v>9.300000000000001</v>
       </c>
     </row>
-    <row r="335">
-      <c r="B335" t="inlineStr">
+    <row r="334">
+      <c r="B334" t="inlineStr">
         <is>
           <t>Dark Walnut</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
+      <c r="D334" t="inlineStr">
         <is>
           <t>CM7905EXP-HC</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr">
+      <c r="E334" t="inlineStr">
         <is>
           <t>Youth</t>
         </is>
       </c>
-      <c r="F335" s="34" t="inlineStr">
+      <c r="F334" s="34" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr">
+      <c r="G334" t="inlineStr">
         <is>
           <t>OMNUS Hutch</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr">
+      <c r="H334" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Elevate your space with OMNUS Hutch, styled in Transitional and designed for everyday comfort. As a youth desk, it is designed to complement your space. With Solid Wood, Wood Veneer, Others and Dark Walnut tones, it blends structure and softness in one clean profile.
@@ -40847,113 +40713,113 @@
 Weight: 27.6 lbs</t>
         </is>
       </c>
-      <c r="I335" t="inlineStr">
+      <c r="I334" t="inlineStr">
         <is>
           <t>OMNUS Hutch in Dark Walnut | GOODDEGG</t>
         </is>
       </c>
-      <c r="J335" t="inlineStr">
+      <c r="J334" t="inlineStr">
         <is>
           <t>The OMNUS Hutch creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr">
+      <c r="K334" t="inlineStr">
         <is>
           <t>OMNUS</t>
         </is>
       </c>
-      <c r="L335" t="inlineStr">
+      <c r="L334" t="inlineStr">
         <is>
           <t>Hutch</t>
         </is>
       </c>
-      <c r="N335" t="inlineStr">
+      <c r="N334" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P335" t="inlineStr">
+      <c r="P334" t="inlineStr">
         <is>
           <t>CM7905EXP-HC.jpg</t>
         </is>
       </c>
-      <c r="Q335" t="n">
+      <c r="Q334" t="n">
         <v>110</v>
       </c>
-      <c r="R335" s="2" t="n">
+      <c r="R334" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="S335" t="n">
+      <c r="S334" t="n">
         <v>270</v>
       </c>
-      <c r="T335" t="n">
+      <c r="T334" t="n">
         <v>27.6</v>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="U334" t="inlineStr">
         <is>
           <t>46"W X 12"D X 24"H</t>
         </is>
       </c>
-      <c r="V335" t="inlineStr">
+      <c r="V334" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="W335" t="inlineStr">
+      <c r="W334" t="inlineStr">
         <is>
           <t>Solid Wood, Wood Veneer, Others</t>
         </is>
       </c>
-      <c r="X335" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>Transitional,Dark Walnut,Solid Wood, Wood Veneer, Others,Match w, Various Youth Beds</t>
         </is>
       </c>
-      <c r="Y335" t="inlineStr">
+      <c r="Y334" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Z335" t="n">
+      <c r="Z334" t="n">
         <v>48.1</v>
       </c>
-      <c r="AA335" t="n">
+      <c r="AA334" t="n">
         <v>25</v>
       </c>
-      <c r="AB335" t="n">
+      <c r="AB334" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC335" t="n">
+      <c r="AC334" t="n">
         <v>8.699999999999999</v>
       </c>
     </row>
-    <row r="336">
-      <c r="B336" t="inlineStr">
+    <row r="335">
+      <c r="B335" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
+      <c r="D335" t="inlineStr">
         <is>
           <t>CM7905WH-HC</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr">
+      <c r="E335" t="inlineStr">
         <is>
           <t>Youth</t>
         </is>
       </c>
-      <c r="F336" s="34" t="inlineStr">
+      <c r="F335" s="34" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr">
+      <c r="G335" t="inlineStr">
         <is>
           <t>OMNUS Hutch</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr">
+      <c r="H335" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 OMNUS Hutch adds a Transitional touch while keeping the room feeling warm and welcoming. This youth desk is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, Others, it is finished in White tones that pair easily with surrounding decor.
@@ -40965,113 +40831,113 @@
 Weight: 27.6 lbs</t>
         </is>
       </c>
-      <c r="I336" t="inlineStr">
+      <c r="I335" t="inlineStr">
         <is>
           <t>OMNUS Hutch in White | GOODDEGG</t>
         </is>
       </c>
-      <c r="J336" t="inlineStr">
+      <c r="J335" t="inlineStr">
         <is>
           <t>The OMNUS Hutch creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr">
+      <c r="K335" t="inlineStr">
         <is>
           <t>OMNUS</t>
         </is>
       </c>
-      <c r="L336" t="inlineStr">
+      <c r="L335" t="inlineStr">
         <is>
           <t>Hutch</t>
         </is>
       </c>
-      <c r="N336" t="inlineStr">
+      <c r="N335" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P336" t="inlineStr">
+      <c r="P335" t="inlineStr">
         <is>
           <t>CM7905WH-HC.jpg,CM7902WH.jpg</t>
         </is>
       </c>
-      <c r="Q336" t="n">
+      <c r="Q335" t="n">
         <v>110</v>
       </c>
-      <c r="R336" s="2" t="n">
+      <c r="R335" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="S336" t="n">
+      <c r="S335" t="n">
         <v>270</v>
       </c>
-      <c r="T336" t="n">
+      <c r="T335" t="n">
         <v>27.6</v>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="U335" t="inlineStr">
         <is>
           <t>46"W X 12"D X 24"H</t>
         </is>
       </c>
-      <c r="V336" t="inlineStr">
+      <c r="V335" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="W336" t="inlineStr">
+      <c r="W335" t="inlineStr">
         <is>
           <t>Solid Wood, Wood Veneer, Others</t>
         </is>
       </c>
-      <c r="X336" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>Transitional,White,Solid Wood, Wood Veneer, Others,Match w, Various Youth Beds</t>
         </is>
       </c>
-      <c r="Y336" t="inlineStr">
+      <c r="Y335" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Z336" t="n">
+      <c r="Z335" t="n">
         <v>25.8</v>
       </c>
-      <c r="AA336" t="n">
+      <c r="AA335" t="n">
         <v>49</v>
       </c>
-      <c r="AB336" t="n">
+      <c r="AB335" t="n">
         <v>12.8</v>
       </c>
-      <c r="AC336" t="n">
+      <c r="AC335" t="n">
         <v>9.300000000000001</v>
       </c>
     </row>
-    <row r="337">
-      <c r="B337" t="inlineStr">
+    <row r="336">
+      <c r="B336" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr">
+      <c r="D336" t="inlineStr">
         <is>
           <t>CM-SR452-WH</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr">
+      <c r="E336" t="inlineStr">
         <is>
           <t>Youth</t>
         </is>
       </c>
-      <c r="F337" s="37" t="inlineStr">
+      <c r="F336" s="37" t="inlineStr">
         <is>
           <t>Shelf/Storage</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr">
+      <c r="G336" t="inlineStr">
         <is>
           <t>OMNUS Underbed Storage w/ Sliding Doors</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr">
+      <c r="H336" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 Make the room feel complete with OMNUS Underbed Storage w/ Sliding Doors and its Transitional character. This youth shelf or storage is made to fit naturally into the room. Finished in White tones, the Solid Wood, Others build balances durability with visual appeal.
@@ -41083,83 +40949,83 @@
 Weight: 52.8 lbs</t>
         </is>
       </c>
-      <c r="I337" t="inlineStr">
+      <c r="I336" t="inlineStr">
         <is>
           <t>OMNUS Underbed Storage w/ Sliding Doors in White | GOODDEGG</t>
         </is>
       </c>
-      <c r="J337" t="inlineStr">
+      <c r="J336" t="inlineStr">
         <is>
           <t>OMNUS Underbed Storage w/ Sliding Doors organizes and displays your essentials with ease. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr">
+      <c r="K336" t="inlineStr">
         <is>
           <t>OMNUS</t>
         </is>
       </c>
-      <c r="L337" t="inlineStr">
+      <c r="L336" t="inlineStr">
         <is>
           <t>Underbed Storage w/ Sliding Doors</t>
         </is>
       </c>
-      <c r="N337" t="inlineStr">
+      <c r="N336" t="inlineStr">
         <is>
           <t>Single Item</t>
         </is>
       </c>
-      <c r="P337" t="inlineStr">
+      <c r="P336" t="inlineStr">
         <is>
           <t>CM-SR452-WH-1-Z.jpg,CM-SR452-WH-2.jpg</t>
         </is>
       </c>
-      <c r="Q337" t="n">
+      <c r="Q336" t="n">
         <v>160</v>
       </c>
-      <c r="R337" s="2" t="n">
+      <c r="R336" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="S337" t="n">
+      <c r="S336" t="n">
         <v>450</v>
       </c>
-      <c r="T337" t="n">
+      <c r="T336" t="n">
         <v>52.8</v>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="U336" t="inlineStr">
         <is>
           <t>75 1/2"L X15 3/4 "W X 10 1/2"H</t>
         </is>
       </c>
-      <c r="V337" t="inlineStr">
+      <c r="V336" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="W337" t="inlineStr">
+      <c r="W336" t="inlineStr">
         <is>
           <t>Solid Wood, Others</t>
         </is>
       </c>
-      <c r="X337" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>Transitional,White,Solid Wood, Others,Storage with Sliding Doors</t>
         </is>
       </c>
-      <c r="Y337" t="inlineStr">
+      <c r="Y336" t="inlineStr">
         <is>
           <t>VN</t>
         </is>
       </c>
-      <c r="Z337" t="n">
+      <c r="Z336" t="n">
         <v>79.5</v>
       </c>
-      <c r="AA337" t="n">
+      <c r="AA336" t="n">
         <v>19.3</v>
       </c>
-      <c r="AB337" t="n">
+      <c r="AB336" t="n">
         <v>12</v>
       </c>
-      <c r="AC337" t="n">
+      <c r="AC336" t="n">
         <v>10.6</v>
       </c>
     </row>

--- a/FOA Singles/Youth-Single.xlsx
+++ b/FOA Singles/Youth-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -839,15 +839,15 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALBANI or Twin Bunk Bed adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 82"W X 45"D X 63"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White
-Weight: 182 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALBANI or Twin Bunk Bed adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 82"W X 45"D X 63"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 182 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -969,13 +969,13 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with AUBREY Triple Decker Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Sand Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 79"L X 78 1/4"W X 74 1/4"H
-Size: Twin
-Materials: Metal.
-Color: Sand Black
-Weight: 165.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with AUBREY Triple Decker Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Sand Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 79"L X 78 1/4"W X 74 1/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Sand Black&lt;br&gt;
+Weight: 165.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1097,13 +1097,13 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BALLARAT Triple Bunk Bed w/ Desk adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Silver tones that pair easily with surrounding decor.
-Product Dimensions: 118 1/4"L X 78 1/4"W X 67 3/4"H
-Size: Twin
-Materials: Metal.
-Color: Silver
-Weight: 226.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BALLARAT Triple Bunk Bed w/ Desk adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Silver tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 118 1/4"L X 78 1/4"W X 67 3/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 226.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1229,13 +1229,13 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BROCKET Metal or Full Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by Black tones for a polished look.
-Product Dimensions: 78 3/4"L X 56 3/4"W X 65"H
-Size: Full
-Materials: Metal.
-Color: Black
-Weight: 126.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BROCKET Metal or Full Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 78 3/4"L X 56 3/4"W X 65"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 126.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1357,13 +1357,13 @@
       </c>
       <c r="G6" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BROOKINGS or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Hardwood, it is finished in Dark Walnut tones that pair easily with surrounding decor.
-Product Dimensions: 60"W X 81"D X 68"H
-Size: Twin
-Materials: Solid Hardwood.
-Color: Dark Walnut
-Weight: 191.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BROOKINGS or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Hardwood, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 60"W X 81"D X 68"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 191.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H6" s="39" t="inlineStr">
@@ -1489,13 +1489,13 @@
       </c>
       <c r="G7" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with BROOKINGS or Full Bunk Bed and its Transitional character. As a youth bunk bed, it is designed to complement your space. Finished in Gray tones, the Solid Hardwood build balances durability with visual appeal.
-Product Dimensions: 60"W X 81"D X 68"H
-Size: Twin
-Materials: Solid Hardwood.
-Color: Gray
-Weight: 191.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with BROOKINGS or Full Bunk Bed and its Transitional character. As a youth bunk bed, it is designed to complement your space. Finished in Gray tones, the Solid Hardwood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 60"W X 81"D X 68"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 191.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H7" s="39" t="inlineStr">
@@ -1621,13 +1621,13 @@
       </c>
       <c r="G8" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BROOKINGS or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Hardwood construction is complemented by Dark Cherry tones for a polished look.
-Product Dimensions: 60"W X 81"D X 68"H
-Size: Twin
-Materials: Solid Hardwood.
-Color: Dark Cherry
-Weight: 191.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BROOKINGS or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Hardwood construction is complemented by Dark Cherry tones for a polished look.&lt;br&gt;
+Product Dimensions: 60"W X 81"D X 68"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: Dark Cherry&lt;br&gt;
+Weight: 191.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H8" s="39" t="inlineStr">
@@ -1753,13 +1753,13 @@
       </c>
       <c r="G9" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BROOKINGS or Full Bunk Bed, styled in Transitional and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Hardwood and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 60"W X 81"D X 68"H
-Size: Twin
-Materials: Solid Hardwood.
-Color: White
-Weight: 191.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BROOKINGS or Full Bunk Bed, styled in Transitional and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Hardwood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 60"W X 81"D X 68"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 191.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H9" s="39" t="inlineStr">
@@ -1885,16 +1885,16 @@
       </c>
       <c r="G10" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CALIFORNIA III or Full Bunk Bed w/ 2 Drawers, styled in Transitional and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Oak tones, it blends structure and softness in one clean profile.
-Product Dimensions: 78 3/8"W X 56 1/2"D X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Two Drawers Included
-Materials: Solid Wood, Wood Veneer.
-Color: Oak
-Weight: 191.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CALIFORNIA III or Full Bunk Bed w/ 2 Drawers, styled in Transitional and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 78 3/8"W X 56 1/2"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Oak&lt;br&gt;
+Weight: 191.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H10" s="41" t="inlineStr">
@@ -2020,16 +2020,16 @@
       </c>
       <c r="G11" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CALIFORNIA III or Full Bunk Bed w/ 2 Drawers adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Wire-Brushed White tones that pair easily with surrounding decor.
-Product Dimensions: 78 3/8"W X 56 1/2"D X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Two Drawers Included
-Materials: Solid Wood, Wood Veneer.
-Color: Wire-Brushed White
-Weight: 192.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CALIFORNIA III or Full Bunk Bed w/ 2 Drawers adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Wire-Brushed White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 78 3/8"W X 56 1/2"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Wire-Brushed White&lt;br&gt;
+Weight: 192.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H11" s="41" t="inlineStr">
@@ -2155,16 +2155,16 @@
       </c>
       <c r="G12" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CALIFORNIA III or Full Bunk Bed w/ 2 Drawers and its Transitional character. As a youth bunk bed, it is designed to complement your space. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 78 3/8"W X 56 1/2"D X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Two Drawers Included
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 190.74 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CALIFORNIA III or Full Bunk Bed w/ 2 Drawers and its Transitional character. As a youth bunk bed, it is designed to complement your space. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 78 3/8"W X 56 1/2"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 190.74 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H12" s="41" t="inlineStr">
@@ -2290,16 +2290,16 @@
       </c>
       <c r="G13" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CALIFORNIA III or Full Bunk Bed w/ 2 Drawers brings a Transitional look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Gray tones for a polished look.
-Product Dimensions: 78 3/8"W X 56 1/2"D X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Two Drawers Included
-Materials: Solid Wood, Wood Veneer.
-Color: Gray
-Weight: 191.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CALIFORNIA III or Full Bunk Bed w/ 2 Drawers brings a Transitional look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 78 3/8"W X 56 1/2"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 191.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H13" s="41" t="inlineStr">
@@ -2425,16 +2425,16 @@
       </c>
       <c r="G14" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CALIFORNIA III or Full Bunk Bed w/ 2 Drawers, styled in Transitional and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 78 3/8"W X 56 1/2"D X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Two Drawers Included
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 191.62 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CALIFORNIA III or Full Bunk Bed w/ 2 Drawers, styled in Transitional and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 78 3/8"W X 56 1/2"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 191.62 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H14" s="41" t="inlineStr">
@@ -2560,16 +2560,16 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CALIFORNIA IV or Full Bunk Bed w/ 2 Drawers adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 78 3/8"_x009d_W X 56 1/2"_x009d_D X 65"_x009d_H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Two Drawers Included
-Materials: Solid Wood, Wood Veneer.
-Color: Black
-Weight: 191.62 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CALIFORNIA IV or Full Bunk Bed w/ 2 Drawers adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 78 3/8"_x009d_W X 56 1/2"_x009d_D X 65"_x009d_H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 191.62 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2691,15 +2691,15 @@
       </c>
       <c r="G16" s="43" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CALIFORNIA IV or Twin Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 78 3/8"L X 41 5/8"W X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Two Drawers Included
-Materials: Solid Wood, Wood Veneer.
-Color: Black
-Weight: 171.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CALIFORNIA IV or Twin Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 78 3/8"L X 41 5/8"W X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 171.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H16" s="43" t="inlineStr">
@@ -2825,15 +2825,15 @@
       </c>
       <c r="G17" s="43" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CALIFORNIA IV or Twin Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Dark Walnut tones for a polished look.
-Product Dimensions: 78 3/8"L X 41 5/8"W X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Two Drawers Included
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 171.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CALIFORNIA IV or Twin Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
+Product Dimensions: 78 3/8"L X 41 5/8"W X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 171.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H17" s="43" t="inlineStr">
@@ -2959,15 +2959,15 @@
       </c>
       <c r="G18" s="43" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CALIFORNIA IV or Twin Bunk Bed, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 78 3/8"L X 41 5/8"W X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Two Drawers Included
-Materials: Solid Wood, Wood Veneer.
-Color: Gray
-Weight: 172.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CALIFORNIA IV or Twin Bunk Bed, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 78 3/8"L X 41 5/8"W X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 172.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H18" s="43" t="inlineStr">
@@ -3093,15 +3093,15 @@
       </c>
       <c r="G19" s="43" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CALIFORNIA IV or Twin Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 78 3/8"L X 41 5/8"W X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Two Drawers Included
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 175.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CALIFORNIA IV or Twin Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 78 3/8"L X 41 5/8"W X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 175.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H19" s="43" t="inlineStr">
@@ -3227,15 +3227,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CALLISTUS Workstation Loft Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Fabric, Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 78 3/8"L X 43 3/4"W X 68 3/4"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Removable Underseat Drawer
-Materials: Fabric, Solid Wood, Wood Veneer.
-Color: White
-Weight: 287 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CALLISTUS Workstation Loft Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Fabric, Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 78 3/8"L X 43 3/4"W X 68 3/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Removable Underseat Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 287 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3357,15 +3357,15 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CALLISTUS or Workstation Loft Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Warm Gray tones, the Fabric, Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 78 3/8"L X 43 3/4"W X 68 3/4"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Removable Underseat Drawer
-Materials: Fabric, Solid Wood, Wood Veneer.
-Color: Warm Gray
-Weight: 276.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CALLISTUS or Workstation Loft Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Warm Gray tones, the Fabric, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 78 3/8"L X 43 3/4"W X 68 3/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Removable Underseat Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Warm Gray&lt;br&gt;
+Weight: 276.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3487,15 +3487,15 @@
       </c>
       <c r="G22" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CAMERON or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Dark Walnut tones for a polished look.
-Product Dimensions: 81 3/8"W X 58"D X 60"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 180.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CAMERON or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
+Product Dimensions: 81 3/8"W X 58"D X 60"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 180.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H22" s="45" t="inlineStr">
@@ -3621,15 +3621,15 @@
       </c>
       <c r="G23" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CAMERON or Full Bunk Bed, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 81 3/8"W X 58"D X 60"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Gray
-Weight: 183.84 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CAMERON or Full Bunk Bed, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 81 3/8"W X 58"D X 60"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 183.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H23" s="45" t="inlineStr">
@@ -3755,15 +3755,15 @@
       </c>
       <c r="G24" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CAMERON or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 81 3/8"W X 58"D X 60"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 185.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CAMERON or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 81 3/8"W X 58"D X 60"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 185.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H24" s="45" t="inlineStr">
@@ -3889,15 +3889,15 @@
       </c>
       <c r="G25" s="47" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CAMERON or Twin Bunk Bed and its Transitional character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 81 3/8"L X 42 3/8"W X 60"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 149.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CAMERON or Twin Bunk Bed and its Transitional character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 81 3/8"L X 42 3/8"W X 60"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 149.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H25" s="47" t="inlineStr">
@@ -4023,15 +4023,15 @@
       </c>
       <c r="G26" s="47" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CAMERON or Twin Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Solid Wood, Wood Veneer, construction is complemented by Gray tones for a polished look.
-Product Dimensions: 81 3/8"W X 58"D X 60"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Gray
-Weight: 149.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CAMERON or Twin Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Solid Wood, Wood Veneer, construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 81 3/8"W X 58"D X 60"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 149.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H26" s="47" t="inlineStr">
@@ -4157,15 +4157,15 @@
       </c>
       <c r="G27" s="47" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CAMERON or Twin Bunk Bed, styled in Transitional and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 81 3/8"L X 42 3/8"W X 60"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 147.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CAMERON or Twin Bunk Bed, styled in Transitional and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 81 3/8"L X 42 3/8"W X 60"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 147.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H27" s="47" t="inlineStr">
@@ -4291,15 +4291,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CANBERRA II or Full Bunk Bed, styled in Cottage and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 78"L X 56 3/4"W X 66"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 166.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CANBERRA II or Full Bunk Bed, styled in Cottage and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 78"L X 56 3/4"W X 66"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 166.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4421,15 +4421,15 @@
       </c>
       <c r="G29" s="49" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CANDICE or Twin Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Solid Wood, it is finished in Gray tones that pair easily with surrounding decor.
-Product Dimensions: 78"W X 43"D X 59"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Gray
-Weight: 135.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CANDICE or Twin Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Solid Wood, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 78"W X 43"D X 59"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 135.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H29" s="49" t="inlineStr">
@@ -4557,15 +4557,15 @@
       </c>
       <c r="G30" s="49" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CANDICE or Twin Bunk Bed and its Transitional character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 78"W X 43"D X 59"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White
-Weight: 135.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CANDICE or Twin Bunk Bed and its Transitional character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 78"W X 43"D X 59"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 135.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H30" s="49" t="inlineStr">
@@ -4693,16 +4693,16 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CAROLINA or Twin Bunk Bed and its Cottage character. As a youth bunk bed, it is designed to complement your space. Finished in Cherry tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 82 5/8"L X 43 3/4"W X 57 1/2"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required
-Materials: Solid Wood, Wood Veneer.
-Color: Cherry
-Weight: 154.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CAROLINA or Twin Bunk Bed and its Cottage character. As a youth bunk bed, it is designed to complement your space. Finished in Cherry tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 82 5/8"L X 43 3/4"W X 57 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Cherry&lt;br&gt;
+Weight: 154.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4824,16 +4824,16 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CASSIDY Loft Bed w/ Drawers brings a Transitional look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Solid Wood, construction is complemented by White tones for a polished look.
-Product Dimensions: 78 3/8"L X 41"W X 70 1/2"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Eight Storage Drawers
-Metal Drawer Handles
-Materials: Solid Wood.
-Color: White
-Weight: 341.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CASSIDY Loft Bed w/ Drawers brings a Transitional look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Solid Wood, construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 78 3/8"L X 41"W X 70 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Eight Storage Drawers&lt;br&gt;
+Metal Drawer Handles&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 341.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4955,13 +4955,13 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CLAPTON or Full Bunk Bed, styled in Industrial and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal, Wood and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 79"L X 55 3/4"W X 66 1/2"H
-Size: Full
-Materials: Metal, Wood.
-Color: Black
-Weight: 167 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CLAPTON or Full Bunk Bed, styled in Industrial and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal, Wood and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 79"L X 55 3/4"W X 66 1/2"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 167 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5087,13 +5087,13 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CLAPTON Bed w/ Futon Base adds a Industrial touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Metal, Wood, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 78 3/8"L X 41"W X 66 1/2"H
-Size: Twin
-Materials: Metal, Wood.
-Color: Black
-Weight: 148.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CLAPTON Bed w/ Futon Base adds a Industrial touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Metal, Wood, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 78 3/8"L X 41"W X 66 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 148.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5219,13 +5219,13 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CLAPTON Bed w/ Workstation and its Industrial character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in Black tones, the Metal, Wood build balances durability with visual appeal.
-Product Dimensions: 77 3/8"L X 41"W X 66 1/2"H
-Size: Twin
-Materials: Metal, Wood.
-Color: Black
-Weight: 134.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CLAPTON Bed w/ Workstation and its Industrial character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in Black tones, the Metal, Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 77 3/8"L X 41"W X 66 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 134.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5351,13 +5351,13 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CLAPTON or Full Bunk Bed brings a Industrial look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal, Wood construction is complemented by Black tones for a polished look.
-Product Dimensions: 77 3/4"L X 54 7/8"W X 66 1/2"H
-Size: Twin
-Materials: Metal, Wood.
-Color: Black
-Weight: 154 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CLAPTON or Full Bunk Bed brings a Industrial look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal, Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 77 3/4"L X 54 7/8"W X 66 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 154 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5483,13 +5483,13 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CLAPTON or Twin Bunk Bed, styled in Industrial and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal, Wood and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 78 3/8"L X 41"W X 66 1/2"H
-Size: Twin
-Materials: Metal, Wood.
-Color: Black
-Weight: 134.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CLAPTON or Twin Bunk Bed, styled in Industrial and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal, Wood and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 78 3/8"L X 41"W X 66 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 134.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5615,13 +5615,13 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CLAREN or Queen Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 82 5/8"L X 62 3/4"W X 65"H
-Size: Full
-Materials: Metal.
-Color: Black
-Weight: 131.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CLAREN or Queen Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 82 5/8"L X 62 3/4"W X 65"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 131.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5743,13 +5743,13 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CLAREN or Queen Bunk Bed and its Contemporary character. As a youth bunk bed, it is designed to complement your space. Finished in Black tones, the Metal build balances durability with visual appeal.
-Product Dimensions: 82 5/8"L X 62 3/4"W X 65"H
-Size: Queen
-Materials: Metal.
-Color: Black
-Weight: 136.46 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CLAREN or Queen Bunk Bed and its Contemporary character. As a youth bunk bed, it is designed to complement your space. Finished in Black tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 82 5/8"L X 62 3/4"W X 65"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 136.46 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5871,13 +5871,13 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CLAREN or Queen Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Metal construction is complemented by Black tones for a polished look.
-Product Dimensions: 82 5/8"L X 62 3/4"W X 65"H
-Size: Twin XL
-Materials: Metal.
-Color: Black
-Weight: 118.36 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CLAREN or Queen Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 82 5/8"L X 62 3/4"W X 65"H&lt;br&gt;
+Size: Twin XL&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 118.36 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5999,13 +5999,13 @@
       </c>
       <c r="G41" s="51" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CYBILL Loft Bed brings a Contemporary look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal construction is complemented by Black tones for a polished look.
-Product Dimensions: 56"W X 77"D X 67"H
-Size: Full
-Materials: Metal.
-Color: Black
-Weight: 110.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CYBILL Loft Bed brings a Contemporary look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 56"W X 77"D X 67"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 110.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H41" s="51" t="inlineStr">
@@ -6131,13 +6131,13 @@
       </c>
       <c r="G42" s="51" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CYBILL Loft Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Silver tones, it blends structure and softness in one clean profile.
-Product Dimensions: 56"W X 77"D X 67"H
-Size: Full
-Materials: Metal.
-Color: Silver
-Weight: 110.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CYBILL Loft Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 56"W X 77"D X 67"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 110.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H42" s="51" t="inlineStr">
@@ -6263,13 +6263,13 @@
       </c>
       <c r="G43" s="51" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CYBILL Loft Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 56"W X 77"D X 67"H
-Size: Full
-Materials: Metal.
-Color: White
-Weight: 110.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CYBILL Loft Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 56"W X 77"D X 67"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 110.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H43" s="51" t="inlineStr">
@@ -6395,15 +6395,15 @@
       </c>
       <c r="G44" s="27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with DAMARIS or Full Bunk Bed and its Rustic character. As a youth bunk bed, it is designed to complement your space. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 78"W X 56"D X 61"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Gray
-Weight: 194 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with DAMARIS or Full Bunk Bed and its Rustic character. As a youth bunk bed, it is designed to complement your space. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 78"W X 56"D X 61"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 194 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H44" s="27" t="inlineStr">
@@ -6529,15 +6529,15 @@
       </c>
       <c r="G45" s="27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DAMARIS or Full Bunk Bed brings a Rustic look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Wood, construction is complemented by White tones for a polished look.
-Product Dimensions: 78"W X 56"D X 61"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White
-Weight: 194 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DAMARIS or Full Bunk Bed brings a Rustic look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Wood, construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 78"W X 56"D X 61"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 194 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H45" s="27" t="inlineStr">
@@ -6663,15 +6663,15 @@
       </c>
       <c r="G46" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ELLINGTON or Full Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Espresso tones, the Solid Wood, Wood Veneer, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 56.5"W X 99.5"D X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Built-In Drawers &amp; Front Access Steps
-Materials: Solid Wood, Wood Veneer, Engineered Wood.
-Color: Espresso
-Weight: 283.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ELLINGTON or Full Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Espresso tones, the Solid Wood, Wood Veneer, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 56.5"W X 99.5"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Built-In Drawers &amp;amp; Front Access Steps&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
+Color: Espresso&lt;br&gt;
+Weight: 283.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H46" s="54" t="inlineStr">
@@ -6797,15 +6797,15 @@
       </c>
       <c r="G47" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ELLINGTON or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, Engineered Wood construction is complemented by White tones for a polished look.
-Product Dimensions: 56.5"W X 99.5"D X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Built-In Drawers &amp; Front Access Steps
-Materials: Solid Wood, Wood Veneer, Engineered Wood.
-Color: White
-Weight: 272.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ELLINGTON or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, Engineered Wood construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 56.5"W X 99.5"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Built-In Drawers &amp;amp; Front Access Steps&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 272.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H47" s="54" t="inlineStr">
@@ -6931,15 +6931,15 @@
       </c>
       <c r="G48" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ELLINGTON or Full Bunk Bed and Trundle, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, Wood Veneer, Engineered Wood and Espresso tones, it blends structure and softness in one clean profile.
-Product Dimensions: 56.5"W X 99.5"D X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Built-In Drawers &amp; Front Access Steps
-Materials: Solid Wood, Wood Veneer, Engineered Wood.
-Color: Espresso
-Weight: 325.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ELLINGTON or Full Bunk Bed and Trundle, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, Wood Veneer, Engineered Wood and Espresso tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 56.5"W X 99.5"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Built-In Drawers &amp;amp; Front Access Steps&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
+Color: Espresso&lt;br&gt;
+Weight: 325.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H48" s="56" t="inlineStr">
@@ -7065,15 +7065,15 @@
       </c>
       <c r="G49" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ELLINGTON or Full Bunk Bed and Trundle adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 56.5"W X 99.5"D X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Built-In Drawers &amp; Front Access Steps
-Materials: Solid Wood, Wood Veneer, Engineered Wood.
-Color: White
-Weight: 316.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ELLINGTON or Full Bunk Bed and Trundle adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 56.5"W X 99.5"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Built-In Drawers &amp;amp; Front Access Steps&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 316.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H49" s="56" t="inlineStr">
@@ -7199,15 +7199,15 @@
       </c>
       <c r="G50" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with EMILEE or Full Bunk Bed, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 79"W X 61"D X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Underbed Drawers Included
-Materials: Solid Wood.
-Color: Black
-Weight: 197.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with EMILEE or Full Bunk Bed, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 79"W X 61"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Underbed Drawers Included&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 197.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H50" s="39" t="inlineStr">
@@ -7333,15 +7333,15 @@
       </c>
       <c r="G51" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EMILEE or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Solid Wood, it is finished in Espresso tones that pair easily with surrounding decor.
-Product Dimensions: 79"W X 61"D X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Underbed Drawers Included
-Materials: Solid Wood.
-Color: Espresso
-Weight: 196.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EMILEE or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Solid Wood, it is finished in Espresso tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 79"W X 61"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Underbed Drawers Included&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Espresso&lt;br&gt;
+Weight: 196.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H51" s="39" t="inlineStr">
@@ -7471,15 +7471,15 @@
       </c>
       <c r="G52" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with EMILEE or Full Bunk Bed and its Transitional character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 79"W X 61"D X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Underbed Drawers Included
-Materials: Solid Wood.
-Color: Gray
-Weight: 194.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with EMILEE or Full Bunk Bed and its Transitional character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 79"W X 61"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Underbed Drawers Included&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 194.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H52" s="39" t="inlineStr">
@@ -7605,15 +7605,15 @@
       </c>
       <c r="G53" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EMILEE or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Solid Wood, construction is complemented by White tones for a polished look.
-Product Dimensions: 79"W X 61"D X 65"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Underbed Drawers Included
-Materials: Solid Wood.
-Color: White
-Weight: 192.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EMILEE or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Solid Wood, construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 79"W X 61"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Underbed Drawers Included&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 192.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H53" s="39" t="inlineStr">
@@ -7739,13 +7739,13 @@
       </c>
       <c r="G54" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with FELGU Triple Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 41.5"W X 78"D X 78"H
-Size: Twin
-Materials: Metal.
-Color: Black
-Weight: 132 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with FELGU Triple Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 78"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 132 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H54" s="41" t="inlineStr">
@@ -7871,13 +7871,13 @@
       </c>
       <c r="G55" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FELGU Triple Metal Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Silver tones that pair easily with surrounding decor.
-Product Dimensions: 41.5"W X 78"D X 78"H
-Size: Twin
-Materials: Metal.
-Color: Silver
-Weight: 132 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FELGU Triple Metal Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Silver tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 78"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 132 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H55" s="41" t="inlineStr">
@@ -8003,13 +8003,13 @@
       </c>
       <c r="G56" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with FELGU Triple Metal Bunk Bed and its Contemporary character. As a youth bunk bed, it is designed to complement your space. Finished in White tones, the Metal build balances durability with visual appeal.
-Product Dimensions: 41.5"W X 78"D X 78"H
-Size: Twin
-Materials: Metal.
-Color: White
-Weight: 132 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with FELGU Triple Metal Bunk Bed and its Contemporary character. As a youth bunk bed, it is designed to complement your space. Finished in White tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 78"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 132 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H56" s="41" t="inlineStr">
@@ -8135,13 +8135,13 @@
       </c>
       <c r="G57" s="43" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FINNERTY or Full Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by Black tones for a polished look.
-Product Dimensions: 57"W X 78.5"D X 59"H
-Size: Full
-Materials: Metal.
-Color: Black
-Weight: 125.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FINNERTY or Full Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 57"W X 78.5"D X 59"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 125.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H57" s="43" t="inlineStr">
@@ -8267,13 +8267,13 @@
       </c>
       <c r="G58" s="43" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with FINNERTY or Full Bunk Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal and Silver tones, it blends structure and softness in one clean profile.
-Product Dimensions: 57"W X 78.5"D X 59"H
-Size: Full
-Materials: Metal.
-Color: Silver
-Weight: 125.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with FINNERTY or Full Bunk Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal and Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 57"W X 78.5"D X 59"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 125.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H58" s="43" t="inlineStr">
@@ -8399,13 +8399,13 @@
       </c>
       <c r="G59" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FINNERTY or Full Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 56"W X 79"D X 60.5"H
-Size: Twin
-Materials: Metal.
-Color: Black
-Weight: 106.48 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FINNERTY or Full Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 56"W X 79"D X 60.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 106.48 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H59" s="45" t="inlineStr">
@@ -8531,13 +8531,13 @@
       </c>
       <c r="G60" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with FINNERTY or Full Bunk Bed and its Contemporary character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in Silver tones, the Metal build balances durability with visual appeal.
-Product Dimensions: 56"W X 79"D X 60.5"H
-Size: Twin
-Materials: Metal.
-Color: Silver
-Weight: 106.48 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with FINNERTY or Full Bunk Bed and its Contemporary character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in Silver tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 56"W X 79"D X 60.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 106.48 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H60" s="45" t="inlineStr">
@@ -8663,13 +8663,13 @@
       </c>
       <c r="G61" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FINNERTY or Full Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal construction is complemented by White tones for a polished look.
-Product Dimensions: 57"W X 78.5"D X 59"H
-Size: Twin
-Materials: Metal.
-Color: White
-Weight: 125.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FINNERTY or Full Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 57"W X 78.5"D X 59"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 125.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H61" s="45" t="inlineStr">
@@ -8795,13 +8795,13 @@
       </c>
       <c r="G62" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with FINNERTY or Full Bunk Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 56"W X 79"D X 60.5"H
-Size: Twin
-Materials: Metal.
-Color: White
-Weight: 106.48 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with FINNERTY or Full Bunk Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 56"W X 79"D X 60.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 106.48 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H62" s="45" t="inlineStr">
@@ -8927,13 +8927,13 @@
       </c>
       <c r="G63" s="47" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FINSBURY or Twin Bunk adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Hardwood, Engineered Wood, it is finished in Espresso tones that pair easily with surrounding decor.
-Product Dimensions: 79"W X 42.5"D X 65"H
-Size: Twin
-Materials: Solid Hardwood, Engineered Wood.
-Color: Espresso
-Weight: 136.68 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FINSBURY or Twin Bunk adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Hardwood, Engineered Wood, it is finished in Espresso tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 79"W X 42.5"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: Espresso&lt;br&gt;
+Weight: 136.68 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H63" s="47" t="inlineStr">
@@ -9061,13 +9061,13 @@
       </c>
       <c r="G64" s="47" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with FINSBURY or Twin Bunk and its Transitional character. As a youth bunk bed, it is designed to complement your space. Finished in Gray tones, the Solid Hardwood, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 79"W X 42.5"D X 65"H
-Size: Twin
-Materials: Solid Hardwood, Engineered Wood.
-Color: Gray
-Weight: 136.68 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with FINSBURY or Twin Bunk and its Transitional character. As a youth bunk bed, it is designed to complement your space. Finished in Gray tones, the Solid Hardwood, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 79"W X 42.5"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 136.68 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H64" s="47" t="inlineStr">
@@ -9195,13 +9195,13 @@
       </c>
       <c r="G65" s="47" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FINSBURY or Twin Bunk brings a Transitional look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Hardwood, Engineered Wood construction is complemented by White tones for a polished look.
-Product Dimensions: 79"W X 42.5"D X 65"H
-Size: Twin
-Materials: Solid Hardwood, Engineered Wood.
-Color: White
-Weight: 137.79 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FINSBURY or Twin Bunk brings a Transitional look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Hardwood, Engineered Wood construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 79"W X 42.5"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 137.79 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H65" s="47" t="inlineStr">
@@ -9329,13 +9329,13 @@
       </c>
       <c r="G66" s="49" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with HECTOR or Twin Metal Bunk Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Metal, Other build balances durability with visual appeal.
-Product Dimensions: 41.5"W X 78"D X 61"H
-Size: Twin
-Materials: Metal, Other.
-Color: Black
-Weight: 72.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with HECTOR or Twin Metal Bunk Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Metal, Other build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 61"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Other.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 72.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H66" s="49" t="inlineStr">
@@ -9467,13 +9467,13 @@
       </c>
       <c r="G67" s="49" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HECTOR or Twin Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal, Other construction is complemented by Silver tones for a polished look.
-Product Dimensions: 41.5"W X 78"D X 61"H
-Size: Twin
-Materials: Metal, Other.
-Color: Silver
-Weight: 77 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HECTOR or Twin Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal, Other construction is complemented by Silver tones for a polished look.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 61"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Other.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 77 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H67" s="49" t="inlineStr">
@@ -9605,13 +9605,13 @@
       </c>
       <c r="G68" s="49" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with HECTOR or Twin Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal, Other and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 41.5"W X 78"D X 61"H
-Size: Twin
-Materials: Metal, Other.
-Color: White
-Weight: 75.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with HECTOR or Twin Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal, Other and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 61"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Other.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 75.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H68" s="49" t="inlineStr">
@@ -9743,16 +9743,16 @@
       </c>
       <c r="G69" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with HOOPLE or Full Bunk Bed, styled in Transitional and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Wood, and Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 79 1/8"L X 59"W X 64"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required
-Materials: Solid Wood.
-Color: Gray
-Weight: 181.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with HOOPLE or Full Bunk Bed, styled in Transitional and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Wood, and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 79 1/8"L X 59"W X 64"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 181.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H69" s="32" t="inlineStr">
@@ -9882,16 +9882,16 @@
       </c>
       <c r="G70" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HOOPLE or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 79 1/8"L X 59"W X 64"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required
-Materials: Solid Wood.
-Color: White
-Weight: 190.27 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HOOPLE or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 79 1/8"L X 59"W X 64"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 190.27 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H70" s="32" t="inlineStr">
@@ -10021,15 +10021,15 @@
       </c>
       <c r="G71" s="60" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with HOOPLE or full Bunk Bed W or Trundle and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Antique Gray tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 79 1/8"L X 59"W X 64"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Antique Gray
-Weight: 227.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with HOOPLE or full Bunk Bed W or Trundle and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Antique Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 79 1/8"L X 59"W X 64"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Antique Gray&lt;br&gt;
+Weight: 227.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H71" s="60" t="inlineStr">
@@ -10155,15 +10155,15 @@
       </c>
       <c r="G72" s="60" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HOOPLE or full Bunk Bed W or Trundle brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, construction is complemented by Antique White tones for a polished look.
-Product Dimensions: 79 1/8"L X 59"W X 64"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Antique White
-Weight: 238.67 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HOOPLE or full Bunk Bed W or Trundle brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, construction is complemented by Antique White tones for a polished look.&lt;br&gt;
+Product Dimensions: 79 1/8"L X 59"W X 64"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Antique White&lt;br&gt;
+Weight: 238.67 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H72" s="60" t="inlineStr">
@@ -10289,16 +10289,16 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with HORTENSE Triple Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Warm Gray tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 99 3/8"L X 78 3/8"W X 64 1/4"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Built-in Night Stand w/ Drawer
-USB port &amp; Power Outlet on Night Stand
-Materials: Solid Wood, Wood Veneer.
-Color: Warm Gray
-Weight: 224.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with HORTENSE Triple Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Warm Gray tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 99 3/8"L X 78 3/8"W X 64 1/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Built-in Night Stand w/ Drawer&lt;br&gt;
+USB port &amp;amp; Power Outlet on Night Stand&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Warm Gray&lt;br&gt;
+Weight: 224.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10415,12 +10415,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with JOJO Bunk Bed, styled in Transitional and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Pine, Engineered Wood and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 99.5"W X 42.5"D X 50"H Bonus storage &amp; convenience features (from matching set pieces): Reversible 3-Drawer Storage Staircase
-Materials: Solid Pine, Engineered Wood.
-Color: White
-Weight: 195.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with JOJO Bunk Bed, styled in Transitional and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Pine, Engineered Wood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 99.5"W X 42.5"D X 50"H Bonus storage &amp;amp; convenience features (from matching set pieces): Reversible 3-Drawer Storage Staircase&lt;/p&gt;
+&lt;p&gt;Materials: Solid Pine, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 195.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -10542,13 +10542,13 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with LAFRAY Bunk Bed w/ Futon Base, styled in Industrial and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal, and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 79 1/2"L X 60 1/4"W X 65 1/2"H
-Size: Twin
-Materials: Metal.
-Color: Black
-Weight: 191.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with LAFRAY Bunk Bed w/ Futon Base, styled in Industrial and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal, and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 79 1/2"L X 60 1/4"W X 65 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 191.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -10670,13 +10670,13 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LOVIA or Full Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal construction is complemented by Metallic Gold tones for a polished look.
-Product Dimensions: 79 3/8"L X 58"W X 65"H
-Size: Full
-Materials: Metal.
-Color: Metallic Gold
-Weight: 147.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LOVIA or Full Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal construction is complemented by Metallic Gold tones for a polished look.&lt;br&gt;
+Product Dimensions: 79 3/8"L X 58"W X 65"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Metallic Gold&lt;br&gt;
+Weight: 147.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -10802,13 +10802,13 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with LOVIA or Full Bunk Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Metallic Gold tones, it blends structure and softness in one clean profile.
-Product Dimensions: 79 3/8"L X 57 1/8"W X 65 1/8"H
-Size: Twin
-Materials: Metal.
-Color: Metallic Gold
-Weight: 144.32 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with LOVIA or Full Bunk Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Metallic Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 79 3/8"L X 57 1/8"W X 65 1/8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Metallic Gold&lt;br&gt;
+Weight: 144.32 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -10934,13 +10934,13 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LOVIA or Twin Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Metallic Gold tones that pair easily with surrounding decor.
-Product Dimensions: 79 3/8"L X 43"W X 65"H
-Size: Twin
-Materials: Metal.
-Color: Metallic Gold
-Weight: 129 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LOVIA or Twin Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Metallic Gold tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 79 3/8"L X 43"W X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Metallic Gold&lt;br&gt;
+Weight: 129 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -11066,15 +11066,15 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MELITTA or Twin Bunk Bed, styled in Rustic and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, and Mahogany tones, it blends structure and softness in one clean profile.
-Product Dimensions: 78"W X 48"D X 62"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Mahogany
-Weight: 201 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MELITTA or Twin Bunk Bed, styled in Rustic and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, and Mahogany tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 78"W X 48"D X 62"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Mahogany&lt;br&gt;
+Weight: 201 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -11196,13 +11196,13 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MOLTON or Full Metal Bunk Bed and its Contemporary character. As a youth bunk bed, it is designed to complement your space. Finished in Black tones, the Metal, Other build balances durability with visual appeal.
-Product Dimensions: 56.5"W X 78"D X 67"H
-Size: Full
-Materials: Metal, Other.
-Color: Black
-Weight: 129.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MOLTON or Full Metal Bunk Bed and its Contemporary character. As a youth bunk bed, it is designed to complement your space. Finished in Black tones, the Metal, Other build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 56.5"W X 78"D X 67"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Other.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 129.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -11333,13 +11333,13 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MOLTON or Full Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Metal, Other construction is complemented by Black tones for a polished look.
-Product Dimensions: 56"W X 78"D X 66.5"H
-Size: Twin
-Materials: Metal, Other.
-Color: Black
-Weight: 119.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MOLTON or Full Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Metal, Other construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 56"W X 78"D X 66.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Other.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 119.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -11470,13 +11470,13 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MOLTON or Twin Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Metal, Other and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 41.5"W X 78"D X 67"H
-Size: Twin
-Materials: Metal, Other.
-Color: Black
-Weight: 99.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MOLTON or Twin Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Metal, Other and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 67"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Other.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 99.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -11607,13 +11607,13 @@
       </c>
       <c r="G83" s="51" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MYLES Loft Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Metal build balances durability with visual appeal.
-Product Dimensions: 41.5"W X 78"D X 61"H
-Size: Twin
-Materials: Metal.
-Color: Black
-Weight: 64.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MYLES Loft Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 61"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 64.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H83" s="51" t="inlineStr">
@@ -11745,13 +11745,13 @@
       </c>
       <c r="G84" s="51" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MYLES Loft Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by Silver tones for a polished look.
-Product Dimensions: 41.5"W X 78"D X 61"H
-Size: Twin
-Materials: Metal.
-Color: Silver
-Weight: 64.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MYLES Loft Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by Silver tones for a polished look.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 61"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 64.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H84" s="51" t="inlineStr">
@@ -11883,13 +11883,13 @@
       </c>
       <c r="G85" s="51" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MYLES Loft Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 41.5"W X 78"D X 61"H
-Size: Twin
-Materials: Metal.
-Color: White
-Weight: 66 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MYLES Loft Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 61"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 66 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H85" s="51" t="inlineStr">
@@ -12021,15 +12021,15 @@
       </c>
       <c r="G86" s="27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with NAUTIA or Full Bunk Bed, styled in Novelty and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Wood, Engineered Wood and Oak or White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 58"W X 78"D X 63"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Engineered Wood.
-Color: Oak or White
-Weight: 183 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with NAUTIA or Full Bunk Bed, styled in Novelty and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Wood, Engineered Wood and Oak or White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 58"W X 78"D X 63"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: Oak or White&lt;br&gt;
+Weight: 183 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H86" s="27" t="inlineStr">
@@ -12155,15 +12155,15 @@
       </c>
       <c r="G87" s="27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NAUTIA or Full Bunk Bed adds a Novelty touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Wood, Engineered Wood, it is finished in Blue or White tones that pair easily with surrounding decor.
-Product Dimensions: 58"W X 78"D X 63"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Engineered Wood.
-Color: Blue or White
-Weight: 183 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NAUTIA or Full Bunk Bed adds a Novelty touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Wood, Engineered Wood, it is finished in Blue or White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 58"W X 78"D X 63"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: Blue or White&lt;br&gt;
+Weight: 183 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H87" s="27" t="inlineStr">
@@ -12289,15 +12289,15 @@
       </c>
       <c r="G88" s="34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with NAUTIA or Full Bunk Bed w/ Trundle and its Novelty character. This youth bunk bed is made to fit naturally into the room. Finished in Oak or White tones, the Solid Wood, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 58"W X 78"D X 63"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Engineered Wood.
-Color: Oak or White
-Weight: 227 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with NAUTIA or Full Bunk Bed w/ Trundle and its Novelty character. This youth bunk bed is made to fit naturally into the room. Finished in Oak or White tones, the Solid Wood, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 58"W X 78"D X 63"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: Oak or White&lt;br&gt;
+Weight: 227 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H88" s="34" t="inlineStr">
@@ -12423,15 +12423,15 @@
       </c>
       <c r="G89" s="34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NAUTIA or Full Bunk Bed w/ Trundle brings a Novelty look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Engineered Wood construction is complemented by Blue or White tones for a polished look.
-Product Dimensions: 58"W X 78"D X 63"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Engineered Wood.
-Color: Blue or White
-Weight: 227 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NAUTIA or Full Bunk Bed w/ Trundle brings a Novelty look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Engineered Wood construction is complemented by Blue or White tones for a polished look.&lt;br&gt;
+Product Dimensions: 58"W X 78"D X 63"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: Blue or White&lt;br&gt;
+Weight: 227 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H89" s="34" t="inlineStr">
@@ -12557,13 +12557,13 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OLGA I Triple Decker Bed brings a Contemporary look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal construction is complemented by Sand Black tones for a polished look.
-Product Dimensions: 78 3/4"L X 57 1/8"W X 79"H
-Size: Full
-Materials: Metal.
-Color: Sand Black
-Weight: 195.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OLGA I Triple Decker Bed brings a Contemporary look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal construction is complemented by Sand Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 78 3/4"L X 57 1/8"W X 79"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Sand Black&lt;br&gt;
+Weight: 195.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -12685,13 +12685,13 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with OLGA I or Full Bunk Bed, styled in Industrial and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Antique Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 78 3/4"L X 58 5/8"W X 68 1/8"H
-Size: Full
-Materials: Metal.
-Color: Antique Black
-Weight: 146.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with OLGA I or Full Bunk Bed, styled in Industrial and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Antique Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 78 3/4"L X 58 5/8"W X 68 1/8"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Antique Black&lt;br&gt;
+Weight: 146.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -12813,13 +12813,13 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OLGA I or Full or Full Bunk Bed adds a Industrial touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Antique Black tones that pair easily with surrounding decor.
-Product Dimensions: 78 3/4"L X 57 1/8"W X 79"H
-Size: Full
-Materials: Metal.
-Color: Antique Black
-Weight: 209.69 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OLGA I or Full or Full Bunk Bed adds a Industrial touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Antique Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 78 3/4"L X 57 1/8"W X 79"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Antique Black&lt;br&gt;
+Weight: 209.69 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -12941,13 +12941,13 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with OLGA I or Queen Bunk Bed and its Industrial character. As a youth bunk bed, it is designed to complement your space. Finished in Antique Black tones, the Metal build balances durability with visual appeal.
-Product Dimensions: 82 5/8"L X 64 5/8"W X 68 1/8"H
-Size: Full
-Materials: Metal.
-Color: Antique Black
-Weight: 174.68 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with OLGA I or Queen Bunk Bed and its Industrial character. As a youth bunk bed, it is designed to complement your space. Finished in Antique Black tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 82 5/8"L X 64 5/8"W X 68 1/8"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Antique Black&lt;br&gt;
+Weight: 174.68 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -13069,13 +13069,13 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OLGA I Triple Decker Bed brings a Contemporary look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Metal construction is complemented by Sand Black tones for a polished look.
-Product Dimensions: 78 3/4"L X 57 1/8"W X 79"H
-Size: Queen
-Materials: Metal.
-Color: Sand Black
-Weight: 213.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OLGA I Triple Decker Bed brings a Contemporary look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Metal construction is complemented by Sand Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 78 3/4"L X 57 1/8"W X 79"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Sand Black&lt;br&gt;
+Weight: 213.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -13197,13 +13197,13 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with OLGA I or Queen Bunk Bed, styled in Industrial and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Metal and Antique Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 82 5/8"L X 64 5/8"W X 68 1/8"H
-Size: Queen
-Materials: Metal.
-Color: Antique Black
-Weight: 161.43 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with OLGA I or Queen Bunk Bed, styled in Industrial and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Metal and Antique Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 82 5/8"L X 64 5/8"W X 68 1/8"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Antique Black&lt;br&gt;
+Weight: 161.43 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -13325,13 +13325,13 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OLGA I Triple Decker Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, it is finished in Sand Black tones that pair easily with surrounding decor.
-Product Dimensions: 78 3/4"L X 42 3/8"W X 79"H
-Size: Twin
-Materials: Metal.
-Color: Sand Black
-Weight: 160.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OLGA I Triple Decker Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, it is finished in Sand Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 78 3/4"L X 42 3/8"W X 79"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Sand Black&lt;br&gt;
+Weight: 160.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -13453,13 +13453,13 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with OLGA I or Twin or Twin Bunk Bed and its Industrial character. This youth bunk bed is made to fit naturally into the room. Finished in Antique Black tones, the Metal build balances durability with visual appeal.
-Product Dimensions: 78 3/4"L X 42 3/8"W X 79"H
-Size: Twin
-Materials: Metal.
-Color: Antique Black
-Weight: 174.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with OLGA I or Twin or Twin Bunk Bed and its Industrial character. This youth bunk bed is made to fit naturally into the room. Finished in Antique Black tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 78 3/4"L X 42 3/8"W X 79"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Antique Black&lt;br&gt;
+Weight: 174.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -13581,13 +13581,13 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OLGA III or Full or Queen Bunk Bed brings a Industrial look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by Antique Black tones for a polished look.
-Product Dimensions: 82 1/4"L X 63"W X 75 1/2"H
-Size: Twin
-Materials: Metal.
-Color: Antique Black
-Weight: 206.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OLGA III or Full or Queen Bunk Bed brings a Industrial look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by Antique Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 82 1/4"L X 63"W X 75 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Antique Black&lt;br&gt;
+Weight: 206.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -13709,13 +13709,13 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with OLGA or Twin Bunk Bed, styled in Industrial and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal and Antique Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 78 3/4"L X 44"W X 68 1/8"H
-Size: Twin
-Materials: Metal.
-Color: Antique Black
-Weight: 116 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with OLGA or Twin Bunk Bed, styled in Industrial and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal and Antique Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 78 3/4"L X 44"W X 68 1/8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Antique Black&lt;br&gt;
+Weight: 116 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -13841,13 +13841,13 @@
       </c>
       <c r="G100" s="43" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with OPAL III Loft Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 78 3/8"L X 41 3/4"W X 69 1/4"H
-Size: Twin
-Materials: Metal.
-Color: Black
-Weight: 137.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with OPAL III Loft Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 78 3/8"L X 41 3/4"W X 69 1/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 137.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H100" s="43" t="inlineStr">
@@ -13975,13 +13975,13 @@
       </c>
       <c r="G101" s="43" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OPAL III Loft Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Silver tones that pair easily with surrounding decor.
-Product Dimensions: 78 3/8"L X 41 3/4"W X 69 1/4"H
-Size: Twin
-Materials: Metal.
-Color: Silver
-Weight: 137.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OPAL III Loft Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Silver tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 78 3/8"L X 41 3/4"W X 69 1/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 137.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H101" s="43" t="inlineStr">
@@ -14109,13 +14109,13 @@
       </c>
       <c r="G102" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with PANOS or Full Metal Bunk Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Metal, Other build balances durability with visual appeal.
-Product Dimensions: 56.5"W X 78"D X 54"H
-Size: Twin
-Materials: Metal, Other.
-Color: Black
-Weight: 82.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with PANOS or Full Metal Bunk Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Metal, Other build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 56.5"W X 78"D X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Other.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 82.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H102" s="45" t="inlineStr">
@@ -14247,13 +14247,13 @@
       </c>
       <c r="G103" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PANOS or Full Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal, Other construction is complemented by Silver tones for a polished look.
-Product Dimensions: 56.5"W X 78"D X 54"H
-Size: Twin
-Materials: Metal, Other.
-Color: Silver
-Weight: 82.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PANOS or Full Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal, Other construction is complemented by Silver tones for a polished look.&lt;br&gt;
+Product Dimensions: 56.5"W X 78"D X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Other.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 82.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H103" s="45" t="inlineStr">
@@ -14385,13 +14385,13 @@
       </c>
       <c r="G104" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with PANOS or Full Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal, Other and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 56.5"W X 78"D X 54"H
-Size: Twin
-Materials: Metal, Other.
-Color: White
-Weight: 82.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with PANOS or Full Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal, Other and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 56.5"W X 78"D X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Other.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 82.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H104" s="45" t="inlineStr">
@@ -14523,13 +14523,13 @@
       </c>
       <c r="G105" s="47" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PHILOTUS or Twin Bunk Bed and Trundle adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 41.5"W X 78"D X 65.5"H
-Size: Twin
-Materials: Metal.
-Color: Black
-Weight: 100.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PHILOTUS or Twin Bunk Bed and Trundle adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 65.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 100.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H105" s="47" t="inlineStr">
@@ -14661,13 +14661,13 @@
       </c>
       <c r="G106" s="47" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with PHILOTUS or Twin Bunk Bed and Trundle and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Silver tones, the Metal build balances durability with visual appeal.
-Product Dimensions: 41.5"W X 78"D X 65.5"H
-Size: Twin
-Materials: Metal.
-Color: Silver
-Weight: 100.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with PHILOTUS or Twin Bunk Bed and Trundle and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Silver tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 65.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 100.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H106" s="47" t="inlineStr">
@@ -14799,13 +14799,13 @@
       </c>
       <c r="G107" s="47" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PHILOTUS or Twin Bunk Bed and Trundle brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by White tones for a polished look.
-Product Dimensions: 41.5"W X 78"D X 65.5"H
-Size: Twin
-Materials: Metal.
-Color: White
-Weight: 100.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PHILOTUS or Twin Bunk Bed and Trundle brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 65.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 100.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H107" s="47" t="inlineStr">
@@ -14937,13 +14937,13 @@
       </c>
       <c r="G108" s="49" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PLUTUS or Twin Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Metal construction is complemented by Black tones for a polished look.
-Product Dimensions: 41.5"W X 78"D X 65.5"H
-Size: Twin
-Materials: Metal.
-Color: Black
-Weight: 77 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PLUTUS or Twin Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 65.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 77 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H108" s="49" t="inlineStr">
@@ -15075,13 +15075,13 @@
       </c>
       <c r="G109" s="49" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with PLUTUS or Twin Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Metal and Silver tones, it blends structure and softness in one clean profile.
-Product Dimensions: 41.5"W X 78"D X 65.5"H
-Size: Twin
-Materials: Metal.
-Color: Silver
-Weight: 75.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with PLUTUS or Twin Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Metal and Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 65.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 75.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H109" s="49" t="inlineStr">
@@ -15213,13 +15213,13 @@
       </c>
       <c r="G110" s="49" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PLUTUS or Twin Metal Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 41.5"W X 78"D X 65.5"H
-Size: Twin
-Materials: Metal.
-Color: White
-Weight: 77 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PLUTUS or Twin Metal Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 65.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 77 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H110" s="49" t="inlineStr">
@@ -15351,13 +15351,13 @@
       </c>
       <c r="G111" s="65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-RAINBOW Metal or Twin Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 79"W X 42"D X 61"H
-Size: Twin
-Materials: Metal.
-Color: Black
-Weight: 99 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+RAINBOW Metal or Twin Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 79"W X 42"D X 61"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 99 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H111" s="65" t="inlineStr">
@@ -15485,13 +15485,13 @@
       </c>
       <c r="G112" s="65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with RAINBOW Metal or Twin Bunk Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Silver tones, the Metal build balances durability with visual appeal.
-Product Dimensions: 79"W X 42"D X 61"H
-Size: Twin
-Materials: Metal.
-Color: Silver
-Weight: 99 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with RAINBOW Metal or Twin Bunk Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Silver tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 79"W X 42"D X 61"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 99 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H112" s="65" t="inlineStr">
@@ -15619,13 +15619,13 @@
       </c>
       <c r="G113" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-RAINBOW or Twin Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by Black tones for a polished look.
-Product Dimensions: 79"W X 42"D X 59 1/2"H
-Size: Twin
-Materials: Metal.
-Color: Black
-Weight: 96.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+RAINBOW or Twin Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 79"W X 42"D X 59 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 96.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H113" s="32" t="inlineStr">
@@ -15753,13 +15753,13 @@
       </c>
       <c r="G114" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with RAINBOW or Twin Bunk Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal and Silver tones, it blends structure and softness in one clean profile.
-Product Dimensions: 79"W X 42"D X 59 1/2"H
-Size: Twin
-Materials: Metal.
-Color: Silver
-Weight: 96.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with RAINBOW or Twin Bunk Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal and Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 79"W X 42"D X 59 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 96.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H114" s="32" t="inlineStr">
@@ -15887,13 +15887,13 @@
       </c>
       <c r="G115" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-RAINBOW or Twin Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Metal, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 79"W X 42"D X 59 1/2"H
-Size: Twin
-Materials: Metal.
-Color: White
-Weight: 96.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+RAINBOW or Twin Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Metal, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 79"W X 42"D X 59 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 96.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H115" s="32" t="inlineStr">
@@ -16021,13 +16021,13 @@
       </c>
       <c r="G116" s="60" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-RHONDA Loft Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, Other, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 41.5"W X 78"D X 64"H
-Size: Twin
-Materials: Metal, Other.
-Color: Black
-Weight: 58.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+RHONDA Loft Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, Other, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 64"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Other.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 58.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H116" s="60" t="inlineStr">
@@ -16159,13 +16159,13 @@
       </c>
       <c r="G117" s="60" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with RHONDA Loft Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Silver tones, the Metal, Other build balances durability with visual appeal.
-Product Dimensions: 41.5"W X 78"D X 64"H
-Size: Twin
-Materials: Metal, Other.
-Color: Silver
-Weight: 59.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with RHONDA Loft Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Silver tones, the Metal, Other build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 64"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Other.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 59.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H117" s="60" t="inlineStr">
@@ -16297,13 +16297,13 @@
       </c>
       <c r="G118" s="60" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-RHONDA Loft Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal, Other construction is complemented by White tones for a polished look.
-Product Dimensions: 41.5"W X 78"D X 64"H
-Size: Twin
-Materials: Metal, Other.
-Color: White
-Weight: 58.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+RHONDA Loft Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal, Other construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 64"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Other.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 58.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H118" s="60" t="inlineStr">
@@ -16435,13 +16435,13 @@
       </c>
       <c r="G119" s="68" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ROTHWELL or Full Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal, construction is complemented by Matte Black tones for a polished look.
-Product Dimensions: 76.5"W X 56"D X 54"H
-Size: Twin
-Materials: Metal.
-Color: Matte Black
-Weight: 81.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ROTHWELL or Full Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal, construction is complemented by Matte Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 76.5"W X 56"D X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Matte Black&lt;br&gt;
+Weight: 81.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H119" s="68" t="inlineStr">
@@ -16569,13 +16569,13 @@
       </c>
       <c r="G120" s="68" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ROTHWELL or Full Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal, and Matte White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 76.5"W X 56"D X 54"H
-Size: Twin
-Materials: Metal.
-Color: Matte White
-Weight: 81.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ROTHWELL or Full Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal, and Matte White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 76.5"W X 56"D X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Matte White&lt;br&gt;
+Weight: 81.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H120" s="68" t="inlineStr">
@@ -16703,13 +16703,13 @@
       </c>
       <c r="G121" s="51" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ROTHWELL or Twin Metal Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Matte Black tones that pair easily with surrounding decor.
-Product Dimensions: 76.5"W X 41"D X 54"H
-Size: Twin
-Materials: Metal.
-Color: Matte Black
-Weight: 74.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ROTHWELL or Twin Metal Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Matte Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 76.5"W X 41"D X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Matte Black&lt;br&gt;
+Weight: 74.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H121" s="51" t="inlineStr">
@@ -16837,13 +16837,13 @@
       </c>
       <c r="G122" s="51" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ROTHWELL or Twin Metal Bunk Bed and its Contemporary character. As a youth bunk bed, it is designed to complement your space. Finished in Matte White tones, the Metal, build balances durability with visual appeal.
-Product Dimensions: 76.5"W X 41"D X 54"H
-Size: Twin
-Materials: Metal.
-Color: Matte White
-Weight: 74.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ROTHWELL or Twin Metal Bunk Bed and its Contemporary character. As a youth bunk bed, it is designed to complement your space. Finished in Matte White tones, the Metal, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 76.5"W X 41"D X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Matte White&lt;br&gt;
+Weight: 74.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H122" s="51" t="inlineStr">
@@ -16971,15 +16971,15 @@
       </c>
       <c r="G123" s="27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SOLPINE or Full Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Oak tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 80 3/8"L X 56 1/2"W X 70 5/8"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Oak
-Weight: 210 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SOLPINE or Full Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Oak tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 80 3/8"L X 56 1/2"W X 70 5/8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Oak&lt;br&gt;
+Weight: 210 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H123" s="27" t="inlineStr">
@@ -17105,15 +17105,15 @@
       </c>
       <c r="G124" s="27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOLPINE or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Espresso tones for a polished look.
-Product Dimensions: 80 3/8"L X 56 1/2"W X 70 5/8"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Espresso
-Weight: 210 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOLPINE or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Espresso tones for a polished look.&lt;br&gt;
+Product Dimensions: 80 3/8"L X 56 1/2"W X 70 5/8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Espresso&lt;br&gt;
+Weight: 210 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H124" s="27" t="inlineStr">
@@ -17243,15 +17243,15 @@
       </c>
       <c r="G125" s="27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SOLPINE or Full Bunk Bed, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 80 3/8"L X 56 1/2"W X 70 5/8"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Gray
-Weight: 210 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SOLPINE or Full Bunk Bed, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 80 3/8"L X 56 1/2"W X 70 5/8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 210 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H125" s="27" t="inlineStr">
@@ -17377,13 +17377,13 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SOUTHALL or Full Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal, and Matte Black or Matte White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 76.5"W X 56"D X 54"H
-Size: Twin
-Materials: Metal.
-Color: Matte Black or Matte White
-Weight: 91.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SOUTHALL or Full Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal, and Matte Black or Matte White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 76.5"W X 56"D X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Matte Black or Matte White&lt;br&gt;
+Weight: 91.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -17509,13 +17509,13 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOUTHALL or Twin Metal Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Metal, it is finished in Matte Black or Matte White tones that pair easily with surrounding decor.
-Product Dimensions: 76.5"W X 41"D X 54"H
-Size: Twin
-Materials: Metal.
-Color: Matte Black or Matte White
-Weight: 83.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOUTHALL or Twin Metal Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Metal, it is finished in Matte Black or Matte White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 76.5"W X 41"D X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Matte Black or Matte White&lt;br&gt;
+Weight: 83.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -17641,13 +17641,13 @@
       </c>
       <c r="G128" s="34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SPRING CREEK or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Hardwood, Engineered Wood construction is complemented by Dark Walnut tones for a polished look.
-Product Dimensions: 80"W X 72.5"D X 65.5"H
-Size: Twin
-Materials: Solid Hardwood, Engineered Wood.
-Color: Dark Walnut
-Weight: 187.39 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SPRING CREEK or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Hardwood, Engineered Wood construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
+Product Dimensions: 80"W X 72.5"D X 65.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 187.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H128" s="34" t="inlineStr">
@@ -17773,13 +17773,13 @@
       </c>
       <c r="G129" s="34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SPRING CREEK or Full Bunk Bed, styled in Transitional and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Hardwood, Engineered Wood and Stain Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 80"W X 72.5"D X 65.5"H
-Size: Twin
-Materials: Solid Hardwood, Engineered Wood.
-Color: Stain Gray
-Weight: 187.39 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SPRING CREEK or Full Bunk Bed, styled in Transitional and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Hardwood, Engineered Wood and Stain Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 80"W X 72.5"D X 65.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: Stain Gray&lt;br&gt;
+Weight: 187.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H129" s="34" t="inlineStr">
@@ -17905,13 +17905,13 @@
       </c>
       <c r="G130" s="34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SPRING CREEK or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Hardwood, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 80"W X 72.5"D X 65.5"H
-Size: Twin
-Materials: Solid Hardwood, Engineered Wood.
-Color: White
-Weight: 188.39 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SPRING CREEK or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Hardwood, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 80"W X 72.5"D X 65.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 188.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H130" s="34" t="inlineStr">
@@ -18037,15 +18037,15 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-STAMOS or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in Walnut tones that pair easily with surrounding decor.
-Product Dimensions: 81 1/8"L X 57 7/8"W X 63 3/4"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Walnut
-Weight: 213.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+STAMOS or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in Walnut tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 81 1/8"L X 57 7/8"W X 63 3/4"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Walnut&lt;br&gt;
+Weight: 213.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -18167,15 +18167,15 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with STAMOS or Full Bunk Bed and its Transitional character. As a youth bunk bed, it is designed to complement your space. Finished in Walnut tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 81 1/8"L X 57 7/8"W X 63 3/4"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Walnut
-Weight: 201.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with STAMOS or Full Bunk Bed and its Transitional character. As a youth bunk bed, it is designed to complement your space. Finished in Walnut tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 81 1/8"L X 57 7/8"W X 63 3/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Walnut&lt;br&gt;
+Weight: 201.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -18297,15 +18297,15 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-STAMOS or Twin Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Wood, construction is complemented by Walnut tones for a polished look.
-Product Dimensions: 81 1/8"L X 43"W X 63 3/4"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Walnut
-Weight: 176.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+STAMOS or Twin Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Wood, construction is complemented by Walnut tones for a polished look.&lt;br&gt;
+Product Dimensions: 81 1/8"L X 43"W X 63 3/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Walnut&lt;br&gt;
+Weight: 176.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -18427,13 +18427,13 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TYMON Loft Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 41.5"W X 78"D X 72"H
-Size: Twin
-Materials: Metal.
-Color: Black
-Weight: 98.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TYMON Loft Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 41.5"W X 78"D X 72"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 98.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -18564,13 +18564,13 @@
       </c>
       <c r="G135" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-UNIVERSITY or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Hardwood, Engineered Wood, it is finished in Dark Walnut tones that pair easily with surrounding decor.
-Product Dimensions: 59.5"W X 83"D X 71.5"H
-Size: Twin Bonus storage &amp; convenience features (from matching set pieces): Trundle w/ 3 Underbed Drawers
-Materials: Solid Hardwood, Engineered Wood.
-Color: Dark Walnut
-Weight: 296.51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+UNIVERSITY or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Hardwood, Engineered Wood, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 59.5"W X 83"D X 71.5"H&lt;br&gt;
+Size: Twin Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle w/ 3 Underbed Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 296.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H135" s="45" t="inlineStr">
@@ -18696,13 +18696,13 @@
       </c>
       <c r="G136" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with UNIVERSITY or Full Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Stain Gray tones, the Solid Hardwood, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 59.5"W X 83"D X 71.5"H
-Size: Twin Bonus storage &amp; convenience features (from matching set pieces): Trundle w/ 3 Underbed Drawers
-Materials: Solid Hardwood, Engineered Wood.
-Color: Stain Gray
-Weight: 296.51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with UNIVERSITY or Full Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Stain Gray tones, the Solid Hardwood, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 59.5"W X 83"D X 71.5"H&lt;br&gt;
+Size: Twin Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle w/ 3 Underbed Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: Stain Gray&lt;br&gt;
+Weight: 296.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H136" s="45" t="inlineStr">
@@ -18828,13 +18828,13 @@
       </c>
       <c r="G137" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-UNIVERSITY or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Hardwood, Engineered Wood construction is complemented by White tones for a polished look.
-Product Dimensions: 59.5"W X 83"D X 71.5"H
-Size: Twin Bonus storage &amp; convenience features (from matching set pieces): Trundle w/ 3 Underbed Drawers
-Materials: Solid Hardwood, Engineered Wood.
-Color: White
-Weight: 296.51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+UNIVERSITY or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Hardwood, Engineered Wood construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 59.5"W X 83"D X 71.5"H&lt;br&gt;
+Size: Twin Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle w/ 3 Underbed Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 296.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H137" s="45" t="inlineStr">
@@ -18960,13 +18960,13 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ALBANO or Full Bunk Bed and its Transitional character. As a youth bed, it is designed to complement your space. Finished in White tones, the Solid Hardwood, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 61"W X 81"D X 70.5"H
-Size: Twin
-Materials: Solid Hardwood, Engineered Wood.
-Color: White
-Weight: 226.19 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ALBANO or Full Bunk Bed and its Transitional character. As a youth bed, it is designed to complement your space. Finished in White tones, the Solid Hardwood, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 61"W X 81"D X 70.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 226.19 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -19088,13 +19088,13 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALBANO or Twin Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Solid Hardwood, Engineered Wood construction is complemented by White tones for a polished look.
-Product Dimensions: 45.5"W X 81"D X 80.5"H
-Size: Twin
-Materials: Solid Hardwood, Engineered Wood.
-Color: White
-Weight: 81.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALBANO or Twin Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Solid Hardwood, Engineered Wood construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 45.5"W X 81"D X 80.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 81.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -19216,16 +19216,16 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ALECIA Bed and its Transitional character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 80 1/2"L X 58 5/8"W X 54"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Materials: Solid Wood.
-Color: White
-Weight: 107.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ALECIA Bed and its Transitional character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 58 5/8"W X 54"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 107.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -19347,16 +19347,16 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALECIA Bed adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 80 1/2"L X 43 5/8"W X 52"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Materials: Solid Wood.
-Color: White
-Weight: 83.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALECIA Bed adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 43 5/8"W X 52"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 83.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -19478,17 +19478,17 @@
       </c>
       <c r="G142" s="68" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ALLIE Bed and its Contemporary character. This youth bed is made to fit naturally into the room. Finished in Pearl White tones, the Fabric, Acrylic, Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 84 1/8"L X 58"W X 54"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): English Dovetail Drawers &amp; Ball-bearing Glides
-Felt-lined Top Drawers
-Materials: Fabric, Acrylic, Solid Wood.
-Color: Pearl White
-Weight: 135.96 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ALLIE Bed and its Contemporary character. This youth bed is made to fit naturally into the room. Finished in Pearl White tones, the Fabric, Acrylic, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 84 1/8"L X 58"W X 54"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
+Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 135.96 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H142" s="68" t="inlineStr">
@@ -19614,17 +19614,17 @@
       </c>
       <c r="G143" s="68" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALLIE Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bed, it pairs well with a wide range of interiors. The Fabric, Acrylic, Solid Wood, construction is complemented by Rose Gold tones for a polished look.
-Product Dimensions: 80 1/2"L X 58"W X 54"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): English Dovetail Drawers with Ball-bearing Metal Side Glides
-Felt-lined Top Drawer
-Optional Convertible Trundle or Drawer
-Materials: Fabric, Acrylic, Solid Wood.
-Color: Rose Gold
-Weight: 138.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALLIE Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bed, it pairs well with a wide range of interiors. The Fabric, Acrylic, Solid Wood, construction is complemented by Rose Gold tones for a polished look.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 58"W X 54"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers with Ball-bearing Metal Side Glides&lt;br&gt;
+Felt-lined Top Drawer&lt;br&gt;
+Optional Convertible Trundle or Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 138.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H143" s="68" t="inlineStr">
@@ -19750,17 +19750,17 @@
       </c>
       <c r="G144" s="27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ALLIE Bed and its Contemporary character. As a youth bed, it is designed to complement your space. Finished in Rose Gold tones, the Fabric, Acrylic, Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 80 1/2"L X 41 3/4"W X 54"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): English Dovetail Drawers with Ball-bearing Metal Side Glides
-Felt-lined Top Drawer
-Optional Convertible Trundle or Drawer
-Materials: Fabric, Acrylic, Solid Wood.
-Color: Rose Gold
-Weight: 111 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ALLIE Bed and its Contemporary character. As a youth bed, it is designed to complement your space. Finished in Rose Gold tones, the Fabric, Acrylic, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 41 3/4"W X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers with Ball-bearing Metal Side Glides&lt;br&gt;
+Felt-lined Top Drawer&lt;br&gt;
+Optional Convertible Trundle or Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 111 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H144" s="27" t="inlineStr">
@@ -19886,17 +19886,17 @@
       </c>
       <c r="G145" s="27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALLIE Bed brings a Contemporary look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Fabric, Acrylic, Solid Wood, construction is complemented by Pearl White tones for a polished look.
-Product Dimensions: 84 1/8"L X 42 1/2"W X 54"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): English Dovetail Drawers &amp; Ball-bearing Glides
-Felt-lined Top Drawers
-Materials: Fabric, Acrylic, Solid Wood.
-Color: Pearl White
-Weight: 109.62 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALLIE Bed brings a Contemporary look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Fabric, Acrylic, Solid Wood, construction is complemented by Pearl White tones for a polished look.&lt;br&gt;
+Product Dimensions: 84 1/8"L X 42 1/2"W X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
+Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 109.62 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H145" s="27" t="inlineStr">
@@ -20022,16 +20022,16 @@
       </c>
       <c r="G146" s="34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ARISTON Bed, styled in Contemporary and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Leatherette, Mirror, Solid Wood, Wood Veneer, and Rose Gold tones, it blends structure and softness in one clean profile.
-Product Dimensions: 82 1/4"L X 58"W X 54"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawers
-Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 117.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ARISTON Bed, styled in Contemporary and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Leatherette, Mirror, Solid Wood, Wood Veneer, and Rose Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 82 1/4"L X 58"W X 54"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 117.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H146" s="34" t="inlineStr">
@@ -20157,16 +20157,16 @@
       </c>
       <c r="G147" s="34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARISTON Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bed is made to fit naturally into the room. Crafted from Leatherette, Mirror, Solid Wood, Wood Veneer, it is finished in Rose Gold tones that pair easily with surrounding decor.
-Product Dimensions: 82 3/4"L X 59"W X 58"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawers
-Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 118.88 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARISTON Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bed is made to fit naturally into the room. Crafted from Leatherette, Mirror, Solid Wood, Wood Veneer, it is finished in Rose Gold tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 82 3/4"L X 59"W X 58"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 118.88 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H147" s="34" t="inlineStr">
@@ -20292,16 +20292,16 @@
       </c>
       <c r="G148" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARISTON Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Leatherette, Mirror, Solid Wood, Wood Veneer, it is finished in Rose Gold tones that pair easily with surrounding decor.
-Product Dimensions: 88 1/4"L X 65"W X 58"H
-Size: Queen
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawers
-Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 135.34 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARISTON Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Leatherette, Mirror, Solid Wood, Wood Veneer, it is finished in Rose Gold tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 88 1/4"L X 65"W X 58"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 135.34 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H148" s="54" t="inlineStr">
@@ -20427,16 +20427,16 @@
       </c>
       <c r="G149" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ARISTON Bed and its Contemporary character. As a youth bed, it is designed to complement your space. Finished in Rose Gold tones, the Leatherette, Mirror, Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 87 3/4"L X 65"W X 58"H
-Size: Queen
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawers
-Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 134.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ARISTON Bed and its Contemporary character. As a youth bed, it is designed to complement your space. Finished in Rose Gold tones, the Leatherette, Mirror, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 87 3/4"L X 65"W X 58"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 134.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H149" s="54" t="inlineStr">
@@ -20562,16 +20562,16 @@
       </c>
       <c r="G150" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ARISTON Bed, styled in Contemporary and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Leatherette, Mirror, Solid Wood, Wood Veneer, and Rose Gold tones, it blends structure and softness in one clean profile.
-Product Dimensions: 82 1/4"L X 43"W X 54"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawers
-Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 99.18 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ARISTON Bed, styled in Contemporary and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Leatherette, Mirror, Solid Wood, Wood Veneer, and Rose Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 82 1/4"L X 43"W X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 99.18 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H150" s="56" t="inlineStr">
@@ -20697,16 +20697,16 @@
       </c>
       <c r="G151" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARISTON Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Leatherette, Mirror, Solid Wood, Wood Veneer, it is finished in Rose Gold tones that pair easily with surrounding decor.
-Product Dimensions: 82 3/4"L X 43"W X 58"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawers
-Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 107.06 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARISTON Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Leatherette, Mirror, Solid Wood, Wood Veneer, it is finished in Rose Gold tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 82 3/4"L X 43"W X 58"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 107.06 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H151" s="56" t="inlineStr">
@@ -20832,13 +20832,13 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BECKY Slat Kit, styled in Rustic and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Pine Wood and Mahogany tones, it blends structure and softness in one clean profile.
-Product Dimensions: 72"L X 53 3/8"W X 3/4"H
-Size: Full
-Materials: Pine Wood.
-Color: Mahogany
-Weight: 35 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BECKY Slat Kit, styled in Rustic and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Pine Wood and Mahogany tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 72"L X 53 3/8"W X 3/4"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Pine Wood.&lt;br&gt;
+Color: Mahogany&lt;br&gt;
+Weight: 35 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -20964,13 +20964,13 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BECKY Slat Kit adds a Rustic touch while keeping the room feeling warm and welcoming. This youth bed is made to fit naturally into the room. Crafted from Pine Wood, it is finished in Mahogany tones that pair easily with surrounding decor.
-Product Dimensions: 72"L X 37 7/8"W X 3/4"H
-Size: Twin
-Materials: Pine Wood.
-Color: Mahogany
-Weight: 23 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BECKY Slat Kit adds a Rustic touch while keeping the room feeling warm and welcoming. This youth bed is made to fit naturally into the room. Crafted from Pine Wood, it is finished in Mahogany tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 72"L X 37 7/8"W X 3/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Pine Wood.&lt;br&gt;
+Color: Mahogany&lt;br&gt;
+Weight: 23 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -21096,17 +21096,17 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with BELVA Bed and its Traditional character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in White tones, the Leatherette, Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 82"L X 58"W X 57 7/8"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): USB Charger in Night Stand
-Felt-lined Top Drawers
-Materials: Leatherette, Solid Wood.
-Color: White
-Weight: 134.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with BELVA Bed and its Traditional character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in White tones, the Leatherette, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 82"L X 58"W X 57 7/8"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): USB Charger in Night Stand&lt;br&gt;
+Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 134.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -21228,17 +21228,17 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BELVA Bed adds a Traditional touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Leatherette, Solid Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 82"L X 43"W X 56"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): USB Charger in Night Stand
-Felt-lined Top Drawers
-Materials: Leatherette, Solid Wood.
-Color: White
-Weight: 116.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BELVA Bed adds a Traditional touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Leatherette, Solid Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 82"L X 43"W X 56"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): USB Charger in Night Stand&lt;br&gt;
+Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 116.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -21360,15 +21360,15 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CARA Bed brings a Cottage look to your home with a refined, comfortable feel. Built as a youth bed, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Cherry tones for a polished look.
-Product Dimensions: 79"L X 41 3/4"W X 45"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Optional Drawers or Trundle
-Materials: Solid Wood, Wood Veneer.
-Color: Cherry
-Weight: 69.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CARA Bed brings a Cottage look to your home with a refined, comfortable feel. Built as a youth bed, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Cherry tones for a polished look.&lt;br&gt;
+Product Dimensions: 79"L X 41 3/4"W X 45"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Optional Drawers or Trundle&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Cherry&lt;br&gt;
+Weight: 69.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -21490,15 +21490,15 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CAREN Bed, styled in Cottage and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 79"L X 41 3/4"W X 45"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Optional Drawers or Trundle
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 67.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CAREN Bed, styled in Cottage and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 79"L X 41 3/4"W X 45"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Optional Drawers or Trundle&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 67.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -21620,15 +21620,15 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CARUS Bed and its Transitional character. This youth bed is made to fit naturally into the room. Finished in Cherry tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 80"L X 43 1/2"W X 45"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Optional Drawers or Trundle
-Materials: Solid Wood, Wood Veneer.
-Color: Cherry
-Weight: 73.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CARUS Bed and its Transitional character. This youth bed is made to fit naturally into the room. Finished in Cherry tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 80"L X 43 1/2"W X 45"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Optional Drawers or Trundle&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Cherry&lt;br&gt;
+Weight: 73.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -21750,13 +21750,13 @@
       </c>
       <c r="G159" s="65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CLEMENS Captain Bed and its Transitional character. As a youth bed, it is designed to complement your space. Finished in White tones, the Solid Hardwood, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 43.5"W X 80.5"D X 35.5"H
-Size: Twin Bonus storage &amp; convenience features (from matching set pieces): Trundle w/ 3 Drawer Storage Unit
-Materials: Solid Hardwood, Engineered Wood.
-Color: White
-Weight: 175.26 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CLEMENS Captain Bed and its Transitional character. As a youth bed, it is designed to complement your space. Finished in White tones, the Solid Hardwood, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 43.5"W X 80.5"D X 35.5"H&lt;br&gt;
+Size: Twin Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle w/ 3 Drawer Storage Unit&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 175.26 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H159" s="65" t="inlineStr">
@@ -21882,13 +21882,13 @@
       </c>
       <c r="G160" s="65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CLEMENS Captain Bed brings a Transitional look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Solid Rubberwood, Engineered Wood construction is complemented by Midnight Blue tones for a polished look.
-Product Dimensions: 43.5"W X 80.5"D X 35.5"H
-Size: Twin Bonus storage &amp; convenience features (from matching set pieces): Trundle w/ 3 Drawer Storage Unit
-Materials: Solid Rubberwood, Engineered Wood.
-Color: Midnight Blue
-Weight: 176.13 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CLEMENS Captain Bed brings a Transitional look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Solid Rubberwood, Engineered Wood construction is complemented by Midnight Blue tones for a polished look.&lt;br&gt;
+Product Dimensions: 43.5"W X 80.5"D X 35.5"H&lt;br&gt;
+Size: Twin Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle w/ 3 Drawer Storage Unit&lt;/p&gt;
+&lt;p&gt;Materials: Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Midnight Blue&lt;br&gt;
+Weight: 176.13 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H160" s="65" t="inlineStr">
@@ -22018,13 +22018,13 @@
       </c>
       <c r="G161" s="65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CLEMENS Captain Bed, styled in Transitional and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Solid Rubberwood, Engineered Wood and Dark Walnut tones, it blends structure and softness in one clean profile.
-Product Dimensions: 43.5"W X 80.5"D X 35.5"H
-Size: Twin Bonus storage &amp; convenience features (from matching set pieces): Trundle w/ 3 Drawer Storage Unit
-Materials: Solid Rubberwood, Engineered Wood.
-Color: Dark Walnut
-Weight: 172.87 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CLEMENS Captain Bed, styled in Transitional and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Solid Rubberwood, Engineered Wood and Dark Walnut tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 43.5"W X 80.5"D X 35.5"H&lt;br&gt;
+Size: Twin Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle w/ 3 Drawer Storage Unit&lt;/p&gt;
+&lt;p&gt;Materials: Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 172.87 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H161" s="65" t="inlineStr">
@@ -22154,15 +22154,15 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CRESWELL Bed, styled in Rustic and designed for everyday comfort. This youth bed is made to fit naturally into the room. With Solid Wood, and Mahogany tones, it blends structure and softness in one clean profile.
-Product Dimensions: 58"W X 78"D X 39.5"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Mahogany
-Weight: 86.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CRESWELL Bed, styled in Rustic and designed for everyday comfort. This youth bed is made to fit naturally into the room. With Solid Wood, and Mahogany tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 58"W X 78"D X 39.5"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Mahogany&lt;br&gt;
+Weight: 86.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -22284,15 +22284,15 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CRESWELL Bed adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in Mahogany tones that pair easily with surrounding decor.
-Product Dimensions: 42.5"W X 78"D X 39.5"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Mahogany
-Weight: 66.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CRESWELL Bed adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in Mahogany tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 42.5"W X 78"D X 39.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Mahogany&lt;br&gt;
+Weight: 66.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -22414,16 +22414,16 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with DANI Bed, styled in Transitional and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 92.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with DANI Bed, styled in Transitional and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 92.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -22545,16 +22545,16 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with DANI Bed, styled in Transitional and designed for everyday comfort. This youth bed is made to fit naturally into the room. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 80 1/2"L X 42 1/4"W X 44 1/4"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 70.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with DANI Bed, styled in Transitional and designed for everyday comfort. This youth bed is made to fit naturally into the room. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 42 1/4"W X 44 1/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 70.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -22676,13 +22676,13 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DAYVILLE Captain Bed brings a Transitional look to your home with a refined, comfortable feel. As a youth bed, it is designed to complement your space. The Solid Hardwood, construction is complemented by Light Oak tones for a polished look.
-Product Dimensions: 43"W X 81.5"D X 44"H
-Size: Twin Bonus storage &amp; convenience features (from matching set pieces): USB-A and USB-C Ports on Headboard
-Materials: Solid Hardwood.
-Color: Light Oak
-Weight: 193.51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DAYVILLE Captain Bed brings a Transitional look to your home with a refined, comfortable feel. As a youth bed, it is designed to complement your space. The Solid Hardwood, construction is complemented by Light Oak tones for a polished look.&lt;br&gt;
+Product Dimensions: 43"W X 81.5"D X 44"H&lt;br&gt;
+Size: Twin Bonus storage &amp;amp; convenience features (from matching set pieces): USB-A and USB-C Ports on Headboard&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: Light Oak&lt;br&gt;
+Weight: 193.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -22804,16 +22804,16 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with DIANE Bed and its Transitional character. As a youth bed, it is designed to complement your space. Finished in Blue tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required
-Materials: Solid Wood, Wood Veneer.
-Color: Blue
-Weight: 92.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with DIANE Bed and its Transitional character. As a youth bed, it is designed to complement your space. Finished in Blue tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 92.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -22935,16 +22935,16 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with DIANE Bed and its Transitional character. This youth bed is made to fit naturally into the room. Finished in Blue tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 80 1/2"L X 41 3/8"W X 44 1/4"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required
-Materials: Solid Wood, Wood Veneer.
-Color: Blue
-Weight: 70.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with DIANE Bed and its Transitional character. This youth bed is made to fit naturally into the room. Finished in Blue tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 41 3/8"W X 44 1/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 70.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -23066,13 +23066,13 @@
       </c>
       <c r="G169" s="34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DUSTRACK Bed adds a Novelty touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from MDF, Particle Board, it is finished in Blue tones that pair easily with surrounding decor.
-Product Dimensions: 82 1/2"L X 41 1/2"W X 23 1/2"H
-Size: Twin
-Materials: MDF, Particle Board.
-Color: Blue
-Weight: 94.35 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DUSTRACK Bed adds a Novelty touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from MDF, Particle Board, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 82 1/2"L X 41 1/2"W X 23 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: MDF, Particle Board.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 94.35 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H169" s="34" t="inlineStr">
@@ -23198,13 +23198,13 @@
       </c>
       <c r="G170" s="34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with DUSTRACK Bed and its Novelty character. As a youth bed, it is designed to complement your space. Finished in Red tones, the MDF, Particle Board, build balances durability with visual appeal.
-Product Dimensions: 82 1/2"L X 41 1/2"W X 23 1/2"H
-Size: Twin
-Materials: MDF, Particle Board.
-Color: Red
-Weight: 94.35 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with DUSTRACK Bed and its Novelty character. As a youth bed, it is designed to complement your space. Finished in Red tones, the MDF, Particle Board, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 82 1/2"L X 41 1/2"W X 23 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: MDF, Particle Board.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 94.35 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H170" s="34" t="inlineStr">
@@ -23330,13 +23330,13 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with FANTON Captain Bed, styled in Transitional and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Solid Hardwood, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 45.5"W X 79.5"D X 48.5"H
-Size: Twin Bonus storage &amp; convenience features (from matching set pieces): Trundle w/ 3 Drawers Storage Unit
-Materials: Solid Hardwood.
-Color: White
-Weight: 83.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with FANTON Captain Bed, styled in Transitional and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Solid Hardwood, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 45.5"W X 79.5"D X 48.5"H&lt;br&gt;
+Size: Twin Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle w/ 3 Drawers Storage Unit&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 83.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -23458,13 +23458,13 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with FIRESTALL Bed, styled in Novelty and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With MDF, Particle Board, and Red tones, it blends structure and softness in one clean profile.
-Product Dimensions: 84 1/2"L X 47 1/4"W X 35 1/2"H
-Size: Twin
-Materials: MDF, Particle Board.
-Color: Red
-Weight: 126.76 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with FIRESTALL Bed, styled in Novelty and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With MDF, Particle Board, and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 84 1/2"L X 47 1/4"W X 35 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: MDF, Particle Board.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 126.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -23586,13 +23586,13 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with GRIFFIN Bed and its Transitional character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in Charcoal Brown tones, the Solid Hardwood build balances durability with visual appeal.
-Product Dimensions: 45.5"W X 79.5"D X 48.5"H
-Size: Twin
-Materials: Solid Hardwood.
-Color: Charcoal Brown
-Weight: 76.72 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with GRIFFIN Bed and its Transitional character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in Charcoal Brown tones, the Solid Hardwood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 45.5"W X 79.5"D X 48.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: Charcoal Brown&lt;br&gt;
+Weight: 76.72 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -23714,13 +23714,13 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GT RACER Bed adds a Novelty touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Leatherette, Metal, it is finished in Silver or Gun Metal tones that pair easily with surrounding decor.
-Product Dimensions: 94 1/2"L X 62 1/4"W X 35 1/2"H
-Size: Full
-Materials: Leatherette, Metal.
-Color: Silver or Gun Metal
-Weight: 114.05 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GT RACER Bed adds a Novelty touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Leatherette, Metal, it is finished in Silver or Gun Metal tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 94 1/2"L X 62 1/4"W X 35 1/2"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Metal.&lt;br&gt;
+Color: Silver or Gun Metal&lt;br&gt;
+Weight: 114.05 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -23842,13 +23842,13 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with GT RACER Bed and its Novelty character. This youth bed is made to fit naturally into the room. Finished in Silver or Gun Metal tones, the Leatherette, Metal build balances durability with visual appeal.
-Product Dimensions: 94 1/2"L X 47 1/4"W X 35 1/2"H
-Size: Twin
-Materials: Leatherette, Metal.
-Color: Silver or Gun Metal
-Weight: 126.65 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with GT RACER Bed and its Novelty character. This youth bed is made to fit naturally into the room. Finished in Silver or Gun Metal tones, the Leatherette, Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 94 1/2"L X 47 1/4"W X 35 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Metal.&lt;br&gt;
+Color: Silver or Gun Metal&lt;br&gt;
+Weight: 126.65 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -23965,11 +23965,11 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with JOURLEY Car Bed, styled in Novelty and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With ABS, Engineered Wood and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 88.5"W X 37.5"D X 25"H
-Materials: ABS, Engineered Wood.
-Color: White</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with JOURLEY Car Bed, styled in Novelty and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With ABS, Engineered Wood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 88.5"W X 37.5"D X 25"H&lt;/p&gt;
+&lt;p&gt;Materials: ABS, Engineered Wood.&lt;br&gt;
+Color: White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -24083,11 +24083,11 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KARSTEN Car Bed adds a Novelty touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from ABS, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 82.5"W X 22"D X 41"H
-Materials: ABS, Engineered Wood.
-Color: White</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KARSTEN Car Bed adds a Novelty touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from ABS, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 82.5"W X 22"D X 41"H&lt;/p&gt;
+&lt;p&gt;Materials: ABS, Engineered Wood.&lt;br&gt;
+Color: White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -24206,13 +24206,13 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LAREINA Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Fabric, Solid Rubberwood, Engineered Wood, it is finished in Pearl White tones that pair easily with surrounding decor.
-Product Dimensions: 58"W X 80.5"D X 52"H
-Size: Full
-Materials: Fabric, Solid Rubberwood, Engineered Wood.
-Color: Pearl White
-Weight: 186.85 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LAREINA Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Fabric, Solid Rubberwood, Engineered Wood, it is finished in Pearl White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 58"W X 80.5"D X 52"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 186.85 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -24329,12 +24329,12 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with LAREINA Trundle, styled in Contemporary and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Solid Rubberwood, Engineered Wood and Pearl White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 41"W X 75"D X 11"H
-Materials: Solid Rubberwood, Engineered Wood.
-Color: Pearl White
-Weight: 69.77 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with LAREINA Trundle, styled in Contemporary and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Solid Rubberwood, Engineered Wood and Pearl White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 41"W X 75"D X 11"H&lt;/p&gt;
+&lt;p&gt;Materials: Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 69.77 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -24460,13 +24460,13 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LAREINA Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Fabric, Solid Rubberwood, Engineered Wood, it is finished in Pearl White tones that pair easily with surrounding decor.
-Product Dimensions: 42.5"W X 80.5"D X 52"H
-Size: Twin
-Materials: Fabric, Solid Rubberwood, Engineered Wood.
-Color: Pearl White
-Weight: 189.08 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LAREINA Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Fabric, Solid Rubberwood, Engineered Wood, it is finished in Pearl White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 42.5"W X 80.5"D X 52"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 189.08 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -24588,17 +24588,17 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with LYCORIDA Bed and its Transitional character. As a youth bed, it is designed to complement your space. Finished in Light Gray tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 80 1/4"L X 56 3/4"W X 54"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Dovetail Drawers
-Felt-lined Top Drawer
-Trundle Converts to Drawers
-Materials: Solid Wood.
-Color: Light Gray
-Weight: 122.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with LYCORIDA Bed and its Transitional character. As a youth bed, it is designed to complement your space. Finished in Light Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 80 1/4"L X 56 3/4"W X 54"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Dovetail Drawers&lt;br&gt;
+Felt-lined Top Drawer&lt;br&gt;
+Trundle Converts to Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 122.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -24725,17 +24725,17 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with LYCORIDA Bed and its Transitional character. This youth bed is made to fit naturally into the room. Finished in Light Gray tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 80 1/4"L X 42"W X 54"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Dovetail Drawers
-Felt-lined Top Drawer
-Trundle Converts to Drawers
-Materials: Solid Wood.
-Color: Light Gray
-Weight: 95.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with LYCORIDA Bed and its Transitional character. This youth bed is made to fit naturally into the room. Finished in Light Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 80 1/4"L X 42"W X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Dovetail Drawers&lt;br&gt;
+Felt-lined Top Drawer&lt;br&gt;
+Trundle Converts to Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 95.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -24862,15 +24862,15 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYCORIS Bed adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bed is made to fit naturally into the room. Crafted from Solid Wood, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 56.5"W X 80"D X 54"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Trundle Converts into Drawers
-Materials: Solid Wood, Engineered Wood.
-Color: White
-Weight: 122.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYCORIS Bed adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bed is made to fit naturally into the room. Crafted from Solid Wood, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 56.5"W X 80"D X 54"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle Converts into Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 122.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -24992,15 +24992,15 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYCORIS Bed adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 42"W X 80"D X 54"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Trundle Converts into Drawers
-Materials: Solid Wood, Engineered Wood.
-Color: White
-Weight: 95.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYCORIS Bed adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 42"W X 80"D X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle Converts into Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 95.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -25122,16 +25122,16 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MARILLA Bed and its Transitional character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Optional Underbed Drawers w/ Sliding Doors
-Optional Underbed Trundle and Drawers Combo
-Materials: Solid Wood.
-Color: White
-Weight: 123.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MARILLA Bed and its Transitional character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Optional Underbed Drawers w/ Sliding Doors&lt;br&gt;
+Optional Underbed Trundle and Drawers Combo&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 123.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -25253,16 +25253,16 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARILLA Bed brings a Transitional look to your home with a refined, comfortable feel. As a youth bed, it is designed to complement your space. The Solid Wood, construction is complemented by White tones for a polished look.
-Product Dimensions: 86"L X 42 7/8"W X 46 5/8"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Optional Underbed Drawers w/ Sliding Doors
-Optional Underbed Trundle and Drawers Combo
-Materials: Solid Wood.
-Color: White
-Weight: 103.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARILLA Bed brings a Transitional look to your home with a refined, comfortable feel. As a youth bed, it is designed to complement your space. The Solid Wood, construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 86"L X 42 7/8"W X 46 5/8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Optional Underbed Drawers w/ Sliding Doors&lt;br&gt;
+Optional Underbed Trundle and Drawers Combo&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 103.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -25384,17 +25384,17 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MARLEE Bed and its Transitional character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 85 1/4"W X 59"D X 50"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): English Dovetail Drawer Construction
-Round Drawer Pulls
-Materials: Solid Wood.
-Color: White
-Weight: 147.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MARLEE Bed and its Transitional character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 85 1/4"W X 59"D X 50"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawer Construction&lt;br&gt;
+Round Drawer Pulls&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 147.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -25516,17 +25516,17 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARLEE Bed adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 85 1/4"W X 44"D X 50"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): English Dovetail Drawer Construction
-Round Drawer Pulls
-Materials: Solid Wood.
-Color: White
-Weight: 127.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARLEE Bed adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 85 1/4"W X 44"D X 50"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawer Construction&lt;br&gt;
+Round Drawer Pulls&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 127.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -25648,13 +25648,13 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MCPHERSON Captain Bed w/ Trundle, styled in Transitional and designed for everyday comfort. This youth bed is made to fit naturally into the room. With Solid Hardwood, Engineered Wood and White or Oak tones, it blends structure and softness in one clean profile.
-Product Dimensions: 82.5"W X 43"D X 40.5"H
-Size: Twin
-Materials: Solid Hardwood, Engineered Wood.
-Color: White or Oak
-Weight: 218.26 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MCPHERSON Captain Bed w/ Trundle, styled in Transitional and designed for everyday comfort. This youth bed is made to fit naturally into the room. With Solid Hardwood, Engineered Wood and White or Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 82.5"W X 43"D X 40.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: White or Oak&lt;br&gt;
+Weight: 218.26 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -25776,13 +25776,13 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with NICOLI Metal Bed and its Contemporary character. This youth bed is made to fit naturally into the room. Finished in White tones, the Metal build balances durability with visual appeal.
-Product Dimensions: 77"W X 56"D X 39.5"H
-Size: Full
-Materials: Metal.
-Color: White
-Weight: 50.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with NICOLI Metal Bed and its Contemporary character. This youth bed is made to fit naturally into the room. Finished in White tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 77"W X 56"D X 39.5"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 50.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -25908,15 +25908,15 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OLIVIA Bed brings a Traditional look to your home with a refined, comfortable feel. Built as a youth bed, it pairs well with a wide range of interiors. The Leatherette, Solid Wood, Wood Veneer, construction is complemented by White tones for a polished look.
-Product Dimensions: 80 1/4"L X 58 3/4"W X 55"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Leatherette, Solid Wood, Wood Veneer.
-Color: White
-Weight: 126.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OLIVIA Bed brings a Traditional look to your home with a refined, comfortable feel. Built as a youth bed, it pairs well with a wide range of interiors. The Leatherette, Solid Wood, Wood Veneer, construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 80 1/4"L X 58 3/4"W X 55"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 126.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -26038,15 +26038,15 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OLIVIA Bed brings a Traditional look to your home with a refined, comfortable feel. As a youth bed, it is designed to complement your space. The Leatherette, Solid Wood, Wood Veneer, construction is complemented by White tones for a polished look.
-Product Dimensions: 80 1/4"L X 44"W X 55"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Leatherette, Solid Wood, Wood Veneer.
-Color: White
-Weight: 103.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OLIVIA Bed brings a Traditional look to your home with a refined, comfortable feel. As a youth bed, it is designed to complement your space. The Leatherette, Solid Wood, Wood Veneer, construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 80 1/4"L X 44"W X 55"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 103.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -26168,13 +26168,13 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ONTARIO or Twin Bunk Bed and its Transitional character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in Espresso tones, the Solid Hardwood, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 43"W X 99"D X 65"H
-Size: Twin
-Materials: Solid Hardwood, Engineered Wood.
-Color: Espresso
-Weight: 251.93 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ONTARIO or Twin Bunk Bed and its Transitional character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in Espresso tones, the Solid Hardwood, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 43"W X 99"D X 65"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: Espresso&lt;br&gt;
+Weight: 251.93 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -26291,11 +26291,11 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with OVERLANDER Car Bed and its Novelty character. This youth bed is made to fit naturally into the room. Finished in Black or White tones, the ABS, Engineered Wood, LED build balances durability with visual appeal.
-Product Dimensions: 80.5"W X 51"D X 35"H
-Materials: ABS, Engineered Wood, LED.
-Color: Black or White</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with OVERLANDER Car Bed and its Novelty character. This youth bed is made to fit naturally into the room. Finished in Black or White tones, the ABS, Engineered Wood, LED build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 80.5"W X 51"D X 35"H&lt;/p&gt;
+&lt;p&gt;Materials: ABS, Engineered Wood, LED.&lt;br&gt;
+Color: Black or White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -26409,11 +26409,11 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PACEFINDER Car Bed brings a Novelty look to your home with a refined, comfortable feel. Built as a youth bed, it pairs well with a wide range of interiors. The ABS, Engineered Wood construction is complemented by White tones for a polished look.
-Product Dimensions: 90.5"W X 43"D X 19.5"H
-Materials: ABS, Engineered Wood.
-Color: White</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PACEFINDER Car Bed brings a Novelty look to your home with a refined, comfortable feel. Built as a youth bed, it pairs well with a wide range of interiors. The ABS, Engineered Wood construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 90.5"W X 43"D X 19.5"H&lt;/p&gt;
+&lt;p&gt;Materials: ABS, Engineered Wood.&lt;br&gt;
+Color: White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -26532,13 +26532,13 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with PATROLENE Police Car Bed, styled in Novelty and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Leatherette, ABS, and Black or White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 91 3/4"L X 49 1/4"W X 34 1/2"H
-Size: Twin
-Materials: Leatherette, ABS.
-Color: Black or White
-Weight: 156.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with PATROLENE Police Car Bed, styled in Novelty and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Leatherette, ABS, and Black or White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 91 3/4"L X 49 1/4"W X 34 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, ABS.&lt;br&gt;
+Color: Black or White&lt;br&gt;
+Weight: 156.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -26660,13 +26660,13 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PEARL Bed brings a Contemporary look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Flannelette, Metal, construction is complemented by Light Pink tones for a polished look.
-Product Dimensions: 81 7/8"L X 63"W X 46"H
-Size: Full
-Materials: Flannelette, Metal.
-Color: Light Pink
-Weight: 106.92 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PEARL Bed brings a Contemporary look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Flannelette, Metal, construction is complemented by Light Pink tones for a polished look.&lt;br&gt;
+Product Dimensions: 81 7/8"L X 63"W X 46"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Flannelette, Metal.&lt;br&gt;
+Color: Light Pink&lt;br&gt;
+Weight: 106.92 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -26788,13 +26788,13 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with PEARL Bed, styled in Contemporary and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Flannelette, Metal, and Light Pink tones, it blends structure and softness in one clean profile.
-Product Dimensions: 87"L X 68 7/8"W X 46"H
-Size: Queen
-Materials: Flannelette, Metal.
-Color: Light Pink
-Weight: 115.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with PEARL Bed, styled in Contemporary and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Flannelette, Metal, and Light Pink tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 87"L X 68 7/8"W X 46"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Materials: Flannelette, Metal.&lt;br&gt;
+Color: Light Pink&lt;br&gt;
+Weight: 115.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -26916,13 +26916,13 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PEARL Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Flannelette, Metal, it is finished in Light Pink tones that pair easily with surrounding decor.
-Product Dimensions: 81 7/8"L X 48"W X 46"H
-Size: Twin
-Materials: Flannelette, Metal.
-Color: Light Pink
-Weight: 85.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PEARL Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Flannelette, Metal, it is finished in Light Pink tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 81 7/8"L X 48"W X 46"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Flannelette, Metal.&lt;br&gt;
+Color: Light Pink&lt;br&gt;
+Weight: 85.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -27044,13 +27044,13 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with POE Bed and its Novelty character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in White or Blue tones, the MDF, Particle Board, build balances durability with visual appeal.
-Product Dimensions: 90"L X 45 1/2"W X 25"H
-Size: Twin
-Materials: MDF, Particle Board.
-Color: White or Blue
-Weight: 128.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with POE Bed and its Novelty character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in White or Blue tones, the MDF, Particle Board, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 90"L X 45 1/2"W X 25"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: MDF, Particle Board.&lt;br&gt;
+Color: White or Blue&lt;br&gt;
+Weight: 128.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -27177,13 +27177,13 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-POSEIDON Captain Bed brings a Novelty look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Solid Pinewood, Engineered Wood construction is complemented by White or Oak tones for a polished look.
-Product Dimensions: 42.5"W X 100"D X 32.5"H
-Size: Twin
-Materials: Solid Pinewood, Engineered Wood.
-Color: White or Oak
-Weight: 115.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+POSEIDON Captain Bed brings a Novelty look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Solid Pinewood, Engineered Wood construction is complemented by White or Oak tones for a polished look.&lt;br&gt;
+Product Dimensions: 42.5"W X 100"D X 32.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Pinewood, Engineered Wood.&lt;br&gt;
+Color: White or Oak&lt;br&gt;
+Weight: 115.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -27305,13 +27305,13 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with POSEIDON Captain Bed w/ Trundle, styled in Novelty and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Solid Pinewood, Engineered Wood and White or Oak tones, it blends structure and softness in one clean profile.
-Product Dimensions: 42.5"W X 100"D X 32.5"H
-Size: Twin
-Materials: Solid Pinewood, Engineered Wood.
-Color: White or Oak
-Weight: 159.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with POSEIDON Captain Bed w/ Trundle, styled in Novelty and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Solid Pinewood, Engineered Wood and White or Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 42.5"W X 100"D X 32.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Pinewood, Engineered Wood.&lt;br&gt;
+Color: White or Oak&lt;br&gt;
+Weight: 159.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -27433,13 +27433,13 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with PRETTY GIRL CAR BED Bed and its Novelty character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in PINK tones, the MDF, Particle Board, build balances durability with visual appeal.
-Product Dimensions: 82 1/2"L X 45 1/2"W X 23 1/2"H
-Size: Twin
-Materials: MDF, Particle Board.
-Color: PINK
-Weight: 131.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with PRETTY GIRL CAR BED Bed and its Novelty character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in PINK tones, the MDF, Particle Board, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 82 1/2"L X 45 1/2"W X 23 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: MDF, Particle Board.&lt;br&gt;
+Color: PINK&lt;br&gt;
+Weight: 131.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -27561,15 +27561,15 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PRIAM Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in White or Gray tones that pair easily with surrounding decor.
-Product Dimensions: 79 5/8"L X 56 1/4"W X 50"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Trundle Converts to Drawers
-Materials: Solid Wood.
-Color: White or Gray
-Weight: 113 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PRIAM Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in White or Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 79 5/8"L X 56 1/4"W X 50"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle Converts to Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 113 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -27691,15 +27691,15 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PRIAM Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Solid Wood, it is finished in White or Gray tones that pair easily with surrounding decor.
-Product Dimensions: 79 5/8"L X 41 1/2"W X 50"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Trundle Converts to Drawers
-Materials: Solid Wood.
-Color: White or Gray
-Weight: 89.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PRIAM Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Solid Wood, it is finished in White or Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 79 5/8"L X 41 1/2"W X 50"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle Converts to Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 89.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -27821,13 +27821,13 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with PRINCESS CROWN SINGLE BED Bed and its Novelty character. This youth bed is made to fit naturally into the room. Finished in PINK tones, the MDF, Particle Board, build balances durability with visual appeal.
-Product Dimensions: 77"L X 42 1/2"W X 41"H
-Size: Twin
-Materials: MDF, Particle Board.
-Color: PINK
-Weight: 96.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with PRINCESS CROWN SINGLE BED Bed and its Novelty character. This youth bed is made to fit naturally into the room. Finished in PINK tones, the MDF, Particle Board, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 77"L X 42 1/2"W X 41"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: MDF, Particle Board.&lt;br&gt;
+Color: PINK&lt;br&gt;
+Weight: 96.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -27949,13 +27949,13 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with PUMPKIN CARRIAGE BED Bed and its Novelty character. As a youth bed, it is designed to complement your space. Finished in PINK tones, the MDF, Particle Board, build balances durability with visual appeal.
-Product Dimensions: 90 1/2"L X 56"W X 67"H
-Size: Twin
-Materials: MDF, Particle Board.
-Color: PINK
-Weight: 219.47 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with PUMPKIN CARRIAGE BED Bed and its Novelty character. As a youth bed, it is designed to complement your space. Finished in PINK tones, the MDF, Particle Board, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 90 1/2"L X 56"W X 67"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: MDF, Particle Board.&lt;br&gt;
+Color: PINK&lt;br&gt;
+Weight: 219.47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -28077,13 +28077,13 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with RESCUER Bed, styled in Novelty and designed for everyday comfort. This youth bed is made to fit naturally into the room. With Leatherette, Metal and Red or Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 91 3/8"L X 46 5/8"W X 47"H
-Size: Twin
-Materials: Leatherette, Metal.
-Color: Red or Black
-Weight: 156.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with RESCUER Bed, styled in Novelty and designed for everyday comfort. This youth bed is made to fit naturally into the room. With Leatherette, Metal and Red or Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 91 3/8"L X 46 5/8"W X 47"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Metal.&lt;br&gt;
+Color: Red or Black&lt;br&gt;
+Weight: 156.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -28205,13 +28205,13 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with RICHLAND Captain Bed, styled in Transitional and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Solid Hardwood, and Light Oak tones, it blends structure and softness in one clean profile.
-Product Dimensions: 58"W X 81.5"D X 44"H
-Size: Full Bonus storage &amp; convenience features (from matching set pieces): USB-A and USB-C Ports on Headboard
-Materials: Solid Hardwood.
-Color: Light Oak
-Weight: 224.66 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with RICHLAND Captain Bed, styled in Transitional and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Solid Hardwood, and Light Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 58"W X 81.5"D X 44"H&lt;br&gt;
+Size: Full Bonus storage &amp;amp; convenience features (from matching set pieces): USB-A and USB-C Ports on Headboard&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: Light Oak&lt;br&gt;
+Weight: 224.66 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -28333,13 +28333,13 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-RICHLAND or Twin Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Solid Hardwood, it is finished in Light Oak tones that pair easily with surrounding decor.
-Product Dimensions: 43"W X 82.5"D X 40"H
-Size: Twin
-Materials: Solid Hardwood.
-Color: Light Oak
-Weight: 283.52 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+RICHLAND or Twin Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Solid Hardwood, it is finished in Light Oak tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 43"W X 82.5"D X 40"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: Light Oak&lt;br&gt;
+Weight: 283.52 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -28456,11 +28456,11 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ROADSTAR Car Bed, styled in Novelty and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With ABS, Engineered Wood and Red tones, it blends structure and softness in one clean profile.
-Product Dimensions: 83"W X 42.5"D X 26.5"H
-Materials: ABS, Engineered Wood.
-Color: Red</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ROADSTAR Car Bed, styled in Novelty and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With ABS, Engineered Wood and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 83"W X 42.5"D X 26.5"H&lt;/p&gt;
+&lt;p&gt;Materials: ABS, Engineered Wood.&lt;br&gt;
+Color: Red&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -28579,16 +28579,16 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ROANNE Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bed, it pairs well with a wide range of interiors. The Fabric, Solid Wood, Wood Veneer, construction is complemented by Gray or Charcoal tones for a polished look.
-Product Dimensions: 79 1/2"L X 56 7/8"W X 45 1/8"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required
-Materials: Fabric, Solid Wood, Wood Veneer.
-Color: Gray or Charcoal
-Weight: 72.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ROANNE Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bed, it pairs well with a wide range of interiors. The Fabric, Solid Wood, Wood Veneer, construction is complemented by Gray or Charcoal tones for a polished look.&lt;br&gt;
+Product Dimensions: 79 1/2"L X 56 7/8"W X 45 1/8"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray or Charcoal&lt;br&gt;
+Weight: 72.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -28710,16 +28710,16 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ROANNE Bed brings a Transitional look to your home with a refined, comfortable feel. As a youth bed, it is designed to complement your space. The Fabric, Solid Wood, Wood Veneer, construction is complemented by Gray or Charcoal tones for a polished look.
-Product Dimensions: 79 1/2"L X 41 7/8"W X 45 1/8"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required
-Materials: Fabric, Solid Wood, Wood Veneer.
-Color: Gray or Charcoal
-Weight: 58.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ROANNE Bed brings a Transitional look to your home with a refined, comfortable feel. As a youth bed, it is designed to complement your space. The Fabric, Solid Wood, Wood Veneer, construction is complemented by Gray or Charcoal tones for a polished look.&lt;br&gt;
+Product Dimensions: 79 1/2"L X 41 7/8"W X 45 1/8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray or Charcoal&lt;br&gt;
+Weight: 58.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -28841,13 +28841,13 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SPEED JUMP BLACK Bed and its Novelty character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in BLACK tones, the MDF, Particle Board, build balances durability with visual appeal.
-Product Dimensions: 82"L X 52"W X 36"H
-Size: Twin
-Materials: MDF, Particle Board.
-Color: BLACK
-Weight: 179 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SPEED JUMP BLACK Bed and its Novelty character. Built as a youth bed, it pairs well with a wide range of interiors. Finished in BLACK tones, the MDF, Particle Board, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 82"L X 52"W X 36"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: MDF, Particle Board.&lt;br&gt;
+Color: BLACK&lt;br&gt;
+Weight: 179 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -28969,13 +28969,13 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-STUTSMAN or Twin Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Solid Hardwood, Engineered Wood, it is finished in Stain Gray tones that pair easily with surrounding decor.
-Product Dimensions: 43"W X 84"D X 77"H
-Size: Twin
-Materials: Solid Hardwood, Engineered Wood.
-Color: Stain Gray
-Weight: 111.66 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+STUTSMAN or Twin Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Solid Hardwood, Engineered Wood, it is finished in Stain Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 43"W X 84"D X 77"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: Stain Gray&lt;br&gt;
+Weight: 111.66 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -29097,15 +29097,15 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with TIBALT DayBed w/ Trundle and its Transitional character. This youth bed is made to fit naturally into the room. Finished in Dark Gray tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 78 1/2"L X 62 1/4"W X 49"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Three Drawers
-Materials: Solid Wood.
-Color: Dark Gray
-Weight: 243.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with TIBALT DayBed w/ Trundle and its Transitional character. This youth bed is made to fit naturally into the room. Finished in Dark Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 78 1/2"L X 62 1/4"W X 49"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Three Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Dark Gray&lt;br&gt;
+Weight: 243.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -29227,15 +29227,15 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TIBALT DayBed w/ Trundle brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bed, it pairs well with a wide range of interiors. The Solid Wood, construction is complemented by Dark Gray tones for a polished look.
-Product Dimensions: 78 1/2"L X 47 1/4"W X 49"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Three Drawers
-Materials: Solid Wood.
-Color: Dark Gray
-Weight: 223.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TIBALT DayBed w/ Trundle brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bed, it pairs well with a wide range of interiors. The Solid Wood, construction is complemented by Dark Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 78 1/2"L X 47 1/4"W X 49"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Three Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Dark Gray&lt;br&gt;
+Weight: 223.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -29353,11 +29353,11 @@
       </c>
       <c r="G218" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TRACKLITE Car Bed adds a Novelty touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from ABS, Engineered Wood, it is finished in Red tones that pair easily with surrounding decor.
-Product Dimensions: 88.5"W X 39"D X 25"H
-Materials: ABS, Engineered Wood.
-Color: Red</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TRACKLITE Car Bed adds a Novelty touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from ABS, Engineered Wood, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 88.5"W X 39"D X 25"H&lt;/p&gt;
+&lt;p&gt;Materials: ABS, Engineered Wood.&lt;br&gt;
+Color: Red&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H218" s="41" t="inlineStr">
@@ -29477,11 +29477,11 @@
       </c>
       <c r="G219" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with TRACKLITE Car Bed and its Novelty character. As a youth bed, it is designed to complement your space. Finished in White tones, the ABS, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 88.5"W X 39"D X 25"H
-Materials: ABS, Engineered Wood.
-Color: White</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with TRACKLITE Car Bed and its Novelty character. As a youth bed, it is designed to complement your space. Finished in White tones, the ABS, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 88.5"W X 39"D X 25"H&lt;/p&gt;
+&lt;p&gt;Materials: ABS, Engineered Wood.&lt;br&gt;
+Color: White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H219" s="41" t="inlineStr">
@@ -29605,13 +29605,13 @@
       </c>
       <c r="G220" s="43" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TRACKSTER Car Bed brings a Novelty look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Leatherette, ABS, construction is complemented by Black tones for a polished look.
-Product Dimensions: 91 3/4"L X 49 1/4"W X 34 1/2"H
-Size: Twin
-Materials: Leatherette, ABS.
-Color: Black
-Weight: 156.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TRACKSTER Car Bed brings a Novelty look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Leatherette, ABS, construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 91 3/4"L X 49 1/4"W X 34 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, ABS.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 156.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H220" s="43" t="inlineStr">
@@ -29737,13 +29737,13 @@
       </c>
       <c r="G221" s="43" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with TRACKSTER Car Bed, styled in Novelty and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Leatherette, ABS, and Blue tones, it blends structure and softness in one clean profile.
-Product Dimensions: 91 3/4"L X 49 1/4"W X 34 1/2"H
-Size: Twin
-Materials: Leatherette, ABS.
-Color: Blue
-Weight: 156.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with TRACKSTER Car Bed, styled in Novelty and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Leatherette, ABS, and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 91 3/4"L X 49 1/4"W X 34 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, ABS.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 156.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H221" s="43" t="inlineStr">
@@ -29869,13 +29869,13 @@
       </c>
       <c r="G222" s="43" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TRACKSTER Car Bed adds a Novelty touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Leatherette, ABS, it is finished in Red tones that pair easily with surrounding decor.
-Product Dimensions: 91 3/4"L X 49 1/4"W X 34 1/2"H
-Size: Twin
-Materials: Leatherette, ABS.
-Color: Red
-Weight: 156.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TRACKSTER Car Bed adds a Novelty touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Leatherette, ABS, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 91 3/4"L X 49 1/4"W X 34 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, ABS.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 156.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H222" s="43" t="inlineStr">
@@ -30001,13 +30001,13 @@
       </c>
       <c r="G223" s="43" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with TRACKSTER Car Bed and its Novelty character. This youth bed is made to fit naturally into the room. Finished in White tones, the Leatherette, ABS, build balances durability with visual appeal.
-Product Dimensions: 91 3/4"L X 49 1/4"W X 34 1/2"H
-Size: Twin
-Materials: Leatherette, ABS.
-Color: White
-Weight: 156.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with TRACKSTER Car Bed and its Novelty character. This youth bed is made to fit naturally into the room. Finished in White tones, the Leatherette, ABS, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 91 3/4"L X 49 1/4"W X 34 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, ABS.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 156.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H223" s="43" t="inlineStr">
@@ -30133,14 +30133,14 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with TROUTDALE Captain Bed, styled in Transitional and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Solid Hardwood, Engineered Wood and Stain Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 43"W X 82.5"D X 47.5"H
-Size: Twin Bonus storage &amp; convenience features (from matching set pieces): Trundle w/ Drawers
-USB-A and USB-C Ports
-Materials: Solid Hardwood, Engineered Wood.
-Color: Stain Gray
-Weight: 103.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with TROUTDALE Captain Bed, styled in Transitional and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Solid Hardwood, Engineered Wood and Stain Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 43"W X 82.5"D X 47.5"H&lt;br&gt;
+Size: Twin Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle w/ Drawers&lt;br&gt;
+USB-A and USB-C Ports&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
+Color: Stain Gray&lt;br&gt;
+Weight: 103.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -30262,16 +30262,16 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with VEVEY Bed, styled in Transitional and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Wire-Brushed Warm Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 82 1/2"L X 58 3/8"W X 50"H
-Size: Full
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Materials: Solid Wood, Wood Veneer.
-Color: Wire-Brushed Warm Gray
-Weight: 96.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with VEVEY Bed, styled in Transitional and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Wire-Brushed Warm Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 82 1/2"L X 58 3/8"W X 50"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Wire-Brushed Warm Gray&lt;br&gt;
+Weight: 96.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -30393,16 +30393,16 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with VEVEY Bed, styled in Transitional and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and Wire-Brushed Warm Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 82 1/2"L X 42 7/8"W X 50"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer
-- Foundation required Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Materials: Solid Wood, Wood Veneer.
-Color: Wire-Brushed Warm Gray
-Weight: 86.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with VEVEY Bed, styled in Transitional and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and Wire-Brushed Warm Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 82 1/2"L X 42 7/8"W X 50"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Wire-Brushed Warm Gray&lt;br&gt;
+Weight: 86.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -30524,13 +30524,13 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with WITHAM or Full Bunk Bed, styled in Transitional and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Solid Hardwood and Charcoal Brown tones, it blends structure and softness in one clean profile.
-Product Dimensions: 59"W X 78"D X 69"H
-Size: Twin
-Materials: Solid Hardwood.
-Color: Charcoal Brown
-Weight: 219.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with WITHAM or Full Bunk Bed, styled in Transitional and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Solid Hardwood and Charcoal Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 59"W X 78"D X 69"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: Charcoal Brown&lt;br&gt;
+Weight: 219.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -30652,13 +30652,13 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WITHAM or Twin Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Solid Hardwood, it is finished in Charcoal Brown tones that pair easily with surrounding decor.
-Product Dimensions: 63"W X 78.5"D X 67.5"H
-Size: Twin
-Materials: Solid Hardwood.
-Color: Charcoal Brown
-Weight: 186.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WITHAM or Twin Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Solid Hardwood, it is finished in Charcoal Brown tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 63"W X 78.5"D X 67.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: Charcoal Brown&lt;br&gt;
+Weight: 186.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -30780,17 +30780,17 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ZOHAR Bed, styled in Glam and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Velvet-like, Solid Wood, and Pink tones, it blends structure and softness in one clean profile.
-Product Dimensions: 88 1/8"L X 76 1/2"W X 56 1/2"H
-Size: Full
-Features
-- Glam design
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Velvet-like, Solid Wood.
-Color: Pink
-Weight: 205.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ZOHAR Bed, styled in Glam and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Velvet-like, Solid Wood, and Pink tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 88 1/8"L X 76 1/2"W X 56 1/2"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: Pink&lt;br&gt;
+Weight: 205.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -30912,17 +30912,17 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZOHAR Bed brings a Glam look to your home with a refined, comfortable feel. Built as a youth bed, it pairs well with a wide range of interiors. The Velvet-like, Solid Wood, construction is complemented by Pink tones for a polished look.
-Product Dimensions: 88 1/8"L X 82 1/2"W X 56 1/2"H
-Size: Queen
-Features
-- Glam design
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Velvet-like, Solid Wood.
-Color: Pink
-Weight: 223.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZOHAR Bed brings a Glam look to your home with a refined, comfortable feel. Built as a youth bed, it pairs well with a wide range of interiors. The Velvet-like, Solid Wood, construction is complemented by Pink tones for a polished look.&lt;br&gt;
+Product Dimensions: 88 1/8"L X 82 1/2"W X 56 1/2"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: Pink&lt;br&gt;
+Weight: 223.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -31044,17 +31044,17 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ZOHAR Bed, styled in Glam and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Velvet-like, Solid Wood, and Pink tones, it blends structure and softness in one clean profile.
-Product Dimensions: 88 1/8"L X 62 1/2"W X 56 1/2"H
-Size: Twin
-Features
-- Glam design
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Velvet-like, Solid Wood.
-Color: Pink
-Weight: 176 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ZOHAR Bed, styled in Glam and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Velvet-like, Solid Wood, and Pink tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 88 1/8"L X 62 1/2"W X 56 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: Pink&lt;br&gt;
+Weight: 176 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -31171,14 +31171,14 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ALECIA Chest, styled in Transitional and designed for everyday comfort. As a youth chest, it is designed to complement your space. With Solid Wood, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 34"W X 17"D X 48"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Materials: Solid Wood.
-Color: White
-Weight: 132 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ALECIA Chest, styled in Transitional and designed for everyday comfort. As a youth chest, it is designed to complement your space. With Solid Wood, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 34"W X 17"D X 48"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 132 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -31300,15 +31300,15 @@
       </c>
       <c r="G233" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ALLIE Chest and its Contemporary character. As a youth chest, it is designed to complement your space. Finished in Pearl White tones, the Acrylic, Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 30 1/8"W X 16 1/2"D X 43 1/2"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): English Dovetail Drawers
-Felt-lined Top Drawers
-Materials: Acrylic, Solid Wood.
-Color: Pearl White
-Weight: 160.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ALLIE Chest and its Contemporary character. As a youth chest, it is designed to complement your space. Finished in Pearl White tones, the Acrylic, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 30 1/8"W X 16 1/2"D X 43 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers&lt;br&gt;
+Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Acrylic, Solid Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 160.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H233" s="32" t="inlineStr">
@@ -31432,15 +31432,15 @@
       </c>
       <c r="G234" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALLIE Chest brings a Contemporary look to your home with a refined, comfortable feel. This youth chest is made to fit naturally into the room. The Acrylic, Solid Wood, construction is complemented by Rose Gold tones for a polished look.
-Product Dimensions: 30 1/8"W X 16 1/2"D X 43 1/2"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): English Dovetail Drawers
-Felt-lined Top Drawer
-Materials: Acrylic, Solid Wood.
-Color: Rose Gold
-Weight: 161 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALLIE Chest brings a Contemporary look to your home with a refined, comfortable feel. This youth chest is made to fit naturally into the room. The Acrylic, Solid Wood, construction is complemented by Rose Gold tones for a polished look.&lt;br&gt;
+Product Dimensions: 30 1/8"W X 16 1/2"D X 43 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers&lt;br&gt;
+Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Acrylic, Solid Wood.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 161 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H234" s="32" t="inlineStr">
@@ -31563,14 +31563,14 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ARISTON Chest and its Contemporary character. This youth chest is made to fit naturally into the room. Finished in Rose Gold tones, the Mirror, Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 36"W X 17"D X 52"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawers
-Materials: Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 160.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ARISTON Chest and its Contemporary character. This youth chest is made to fit naturally into the room. Finished in Rose Gold tones, the Mirror, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 36"W X 17"D X 52"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 160.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -31691,14 +31691,14 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARISTON Swivel Chest brings a Contemporary look to your home with a refined, comfortable feel. This youth chest is made to fit naturally into the room. The Mirror, Solid Wood, Wood Veneer, construction is complemented by Rose Gold tones for a polished look.
-Product Dimensions: 23"W X 17"D X 57 1/2"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawers
-Materials: Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 190 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARISTON Swivel Chest brings a Contemporary look to your home with a refined, comfortable feel. This youth chest is made to fit naturally into the room. The Mirror, Solid Wood, Wood Veneer, construction is complemented by Rose Gold tones for a polished look.&lt;br&gt;
+Product Dimensions: 23"W X 17"D X 57 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 190 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -31819,14 +31819,14 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BELVA Chest, styled in Traditional and designed for everyday comfort. As a youth chest, it is designed to complement your space. With Solid Wood, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 35"L X 17"W X 51"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Materials: Solid Wood.
-Color: White
-Weight: 134.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BELVA Chest, styled in Traditional and designed for everyday comfort. As a youth chest, it is designed to complement your space. With Solid Wood, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 35"L X 17"W X 51"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 134.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -31948,14 +31948,14 @@
       </c>
       <c r="G238" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CORRY Chest brings a Transitional look to your home with a refined, comfortable feel. This youth chest is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Dark Walnut tones for a polished look.
-Product Dimensions: 29"W X 17"D X 42"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 76 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CORRY Chest brings a Transitional look to your home with a refined, comfortable feel. This youth chest is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
+Product Dimensions: 29"W X 17"D X 42"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H238" s="32" t="inlineStr">
@@ -32079,14 +32079,14 @@
       </c>
       <c r="G239" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CORRY Chest, styled in Transitional and designed for everyday comfort. Built as a youth chest, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 29"W X 17"D X 42"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 76 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CORRY Chest, styled in Transitional and designed for everyday comfort. Built as a youth chest, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 29"W X 17"D X 42"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H239" s="32" t="inlineStr">
@@ -32209,14 +32209,14 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with DANI Chest and its Transitional character. This youth chest is made to fit naturally into the room. Finished in White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 29"W X 17"D X 42"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 101.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with DANI Chest and its Transitional character. This youth chest is made to fit naturally into the room. Finished in White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 29"W X 17"D X 42"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 101.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -32337,14 +32337,14 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with DIANE Chest, styled in Transitional and designed for everyday comfort. This youth chest is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Blue tones, it blends structure and softness in one clean profile.
-Product Dimensions: 29"W X 17"D X 42"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Blue
-Weight: 101.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with DIANE Chest, styled in Transitional and designed for everyday comfort. This youth chest is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 29"W X 17"D X 42"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 101.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -32465,12 +32465,12 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FANTON Chest adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth chest, it pairs well with a wide range of interiors. Crafted from Solid Hardwood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 31.5"W X 17.5"D X 47"H
-Materials: Solid Hardwood.
-Color: White
-Weight: 131.17 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FANTON Chest adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth chest, it pairs well with a wide range of interiors. Crafted from Solid Hardwood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 31.5"W X 17.5"D X 47"H&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 131.17 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -32591,12 +32591,12 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GRIFFIN Chest brings a Transitional look to your home with a refined, comfortable feel. Built as a youth chest, it pairs well with a wide range of interiors. The Solid Hardwood construction is complemented by Charcoal Brown tones for a polished look.
-Product Dimensions: 31.5"W X 18.5"D X 23.5"H
-Materials: Solid Hardwood.
-Color: Charcoal Brown
-Weight: 169.27 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GRIFFIN Chest brings a Transitional look to your home with a refined, comfortable feel. Built as a youth chest, it pairs well with a wide range of interiors. The Solid Hardwood construction is complemented by Charcoal Brown tones for a polished look.&lt;br&gt;
+Product Dimensions: 31.5"W X 18.5"D X 23.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: Charcoal Brown&lt;br&gt;
+Weight: 169.27 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -32717,12 +32717,12 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LAREINA Chest brings a Contemporary look to your home with a refined, comfortable feel. As a youth chest, it is designed to complement your space. The Solid Rubberwood, Engineered Wood construction is complemented by Pearl White tones for a polished look.
-Product Dimensions: 30.5"W X 17"D X 43.5"H Bonus storage &amp; convenience features (from matching set pieces): Felt-Lined Top Drawer
-Materials: Solid Rubberwood, Engineered Wood.
-Color: Pearl White
-Weight: 184.57 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LAREINA Chest brings a Contemporary look to your home with a refined, comfortable feel. As a youth chest, it is designed to complement your space. The Solid Rubberwood, Engineered Wood construction is complemented by Pearl White tones for a polished look.&lt;br&gt;
+Product Dimensions: 30.5"W X 17"D X 43.5"H Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-Lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 184.57 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -32843,15 +32843,15 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with LYCORIDA Chest, styled in Transitional and designed for everyday comfort. This youth chest is made to fit naturally into the room. With Solid Wood, and Light Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 28"W X 17"D X 42 1/4"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Dovetail Drawers
-Felt-lined Top Drawer
-Materials: Solid Wood.
-Color: Light Gray
-Weight: 141.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with LYCORIDA Chest, styled in Transitional and designed for everyday comfort. This youth chest is made to fit naturally into the room. With Solid Wood, and Light Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 28"W X 17"D X 42 1/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Dovetail Drawers&lt;br&gt;
+Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 141.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -32977,14 +32977,14 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYCORIS Chest brings a Transitional look to your home with a refined, comfortable feel. Built as a youth chest, it pairs well with a wide range of interiors. The Solid Wood, Engineered Wood construction is complemented by White tones for a polished look.
-Product Dimensions: 28"W X 17"D X 42"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Engineered Wood.
-Color: White
-Weight: 143 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYCORIS Chest brings a Transitional look to your home with a refined, comfortable feel. Built as a youth chest, it pairs well with a wide range of interiors. The Solid Wood, Engineered Wood construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 28"W X 17"D X 42"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 143 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -33105,15 +33105,15 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MARLEE Chest, styled in Transitional and designed for everyday comfort. As a youth chest, it is designed to complement your space. With Solid Wood, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 29"W X 17"D X 42 1/4"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): English Dovetail Drawer Construction
-Round Drawer Pulls
-Materials: Solid Wood.
-Color: White
-Weight: 101.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MARLEE Chest, styled in Transitional and designed for everyday comfort. As a youth chest, it is designed to complement your space. With Solid Wood, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 29"W X 17"D X 42 1/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawer Construction&lt;br&gt;
+Round Drawer Pulls&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 101.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -33234,14 +33234,14 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OLIVIA Chest adds a Traditional touch while keeping the room feeling warm and welcoming. As a youth chest, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 32"W X 17"D X 50"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 150.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OLIVIA Chest adds a Traditional touch while keeping the room feeling warm and welcoming. As a youth chest, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 32"W X 17"D X 50"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 150.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -33362,14 +33362,14 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with OMNUS Chest, styled in Transitional and designed for everyday comfort. This youth chest is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Cherry tones, it blends structure and softness in one clean profile.
-Product Dimensions: 29"W X 17"D X 42"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Cherry
-Weight: 76 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with OMNUS Chest, styled in Transitional and designed for everyday comfort. This youth chest is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Cherry tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 29"W X 17"D X 42"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Cherry&lt;br&gt;
+Weight: 76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -33495,15 +33495,15 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with OMNUS Drawers, styled in Transitional and designed for everyday comfort. Built as a youth chest, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 74 3/4"W X 18 1/2"D X 10 3/4"H
-Size: (Set of 3)
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 46 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with OMNUS Drawers, styled in Transitional and designed for everyday comfort. Built as a youth chest, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 74 3/4"W X 18 1/2"D X 10 3/4"H&lt;br&gt;
+Size: (Set of 3)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 46 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -33629,14 +33629,14 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OMNUS Drawers (Set of 3) adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth chest, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Cherry tones that pair easily with surrounding decor.
-Product Dimensions: 74 3/4"W X 18 1/2"D X 10 3/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Cherry
-Weight: 44 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OMNUS Drawers (Set of 3) adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth chest, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Cherry tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 74 3/4"W X 18 1/2"D X 10 3/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Cherry&lt;br&gt;
+Weight: 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -33757,15 +33757,15 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PRIAM Chest brings a Contemporary look to your home with a refined, comfortable feel. As a youth chest, it is designed to complement your space. The Solid Wood, construction is complemented by White or Gray tones for a polished look.
-Product Dimensions: 30"W X 18"D X 41 7/8"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Dovetail Drawers
-Materials: Solid Wood.
-Color: White or Gray
-Weight: 99 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PRIAM Chest brings a Contemporary look to your home with a refined, comfortable feel. As a youth chest, it is designed to complement your space. The Solid Wood, construction is complemented by White or Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 30"W X 18"D X 41 7/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;br&gt;
+Dovetail Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 99 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -33886,14 +33886,14 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ROANNE Chest adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth chest, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Gray tones that pair easily with surrounding decor.
-Product Dimensions: 35"W X 16 3/8"D X 35 7/8"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Gray
-Weight: 119.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ROANNE Chest adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth chest, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 35"W X 16 3/8"D X 35 7/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 119.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -34015,14 +34015,14 @@
       </c>
       <c r="G254" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-STAVROS Chest adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a youth chest, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in Gray tones that pair easily with surrounding decor.
-Product Dimensions: 28"W X 20.5"D X 50"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Gray
-Weight: 66 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+STAVROS Chest adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a youth chest, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 28"W X 20.5"D X 50"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 66 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H254" s="54" t="inlineStr">
@@ -34146,14 +34146,14 @@
       </c>
       <c r="G255" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with STAVROS Chest and its Rustic character. As a youth chest, it is designed to complement your space. Finished in Mahogany tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 28"W X 20.5"D X 50"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Mahogany
-Weight: 66 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with STAVROS Chest and its Rustic character. As a youth chest, it is designed to complement your space. Finished in Mahogany tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 28"W X 20.5"D X 50"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Mahogany&lt;br&gt;
+Weight: 66 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H255" s="54" t="inlineStr">
@@ -34277,14 +34277,14 @@
       </c>
       <c r="G256" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-STAVROS Chest brings a Rustic look to your home with a refined, comfortable feel. This youth chest is made to fit naturally into the room. The Solid Wood, construction is complemented by White tones for a polished look.
-Product Dimensions: 28"W X 20.5"D X 50"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White
-Weight: 66 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+STAVROS Chest brings a Rustic look to your home with a refined, comfortable feel. This youth chest is made to fit naturally into the room. The Solid Wood, construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 28"W X 20.5"D X 50"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 66 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H256" s="54" t="inlineStr">
@@ -34407,14 +34407,14 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with VEVEY Chest and its Transitional character. As a youth chest, it is designed to complement your space. Finished in Wire-Brushed Warm Gray tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 30"L X 18"W X 42"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Materials: Solid Wood, Wood Veneer.
-Color: Wire-Brushed Warm Gray
-Weight: 103.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with VEVEY Chest and its Transitional character. As a youth chest, it is designed to complement your space. Finished in Wire-Brushed Warm Gray tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 30"L X 18"W X 42"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Wire-Brushed Warm Gray&lt;br&gt;
+Weight: 103.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -34535,16 +34535,16 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ZOHAR Chest and its Glam character. As a youth chest, it is designed to complement your space. Finished in Pink tones, the Velvet-like, Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 34 1/2"W X 17 1/2"D X 49"H
-Features
-- Glam design
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Velvet-like, Solid Wood.
-Color: Pink
-Weight: 173.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ZOHAR Chest and its Glam character. As a youth chest, it is designed to complement your space. Finished in Pink tones, the Velvet-like, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 34 1/2"W X 17 1/2"D X 49"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: Pink&lt;br&gt;
+Weight: 173.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -34665,14 +34665,14 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALECIA Dresser adds a Transitional touch while keeping the room feeling warm and welcoming. This youth dresser is made to fit naturally into the room. Crafted from Solid Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 54"W X 17"D X 34"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Materials: Solid Wood.
-Color: White
-Weight: 140.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALECIA Dresser adds a Transitional touch while keeping the room feeling warm and welcoming. This youth dresser is made to fit naturally into the room. Crafted from Solid Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 54"W X 17"D X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 140.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -34794,15 +34794,15 @@
       </c>
       <c r="G260" s="60" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ALLIE Dresser, styled in Contemporary and designed for everyday comfort. Built as a youth dresser, it pairs well with a wide range of interiors. With Acrylic, Solid Wood, and Pearl White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 54 1/2"W X 16 1/2"D X 34"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): English Dovetail Drawers
-Felt-lined Top Drawers
-Materials: Acrylic, Solid Wood.
-Color: Pearl White
-Weight: 200.93 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ALLIE Dresser, styled in Contemporary and designed for everyday comfort. Built as a youth dresser, it pairs well with a wide range of interiors. With Acrylic, Solid Wood, and Pearl White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 54 1/2"W X 16 1/2"D X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers&lt;br&gt;
+Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Acrylic, Solid Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 200.93 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H260" s="60" t="inlineStr">
@@ -34926,15 +34926,15 @@
       </c>
       <c r="G261" s="60" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALLIE Dresser adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth dresser, it is designed to complement your space. Crafted from Acrylic, Solid Wood, it is finished in Rose Gold tones that pair easily with surrounding decor.
-Product Dimensions: 54 1/2"W X 16 1/2"D X 34"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): English Dovetail Drawers
-Felt-lined Top Drawer
-Materials: Acrylic, Solid Wood.
-Color: Rose Gold
-Weight: 198 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALLIE Dresser adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth dresser, it is designed to complement your space. Crafted from Acrylic, Solid Wood, it is finished in Rose Gold tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 54 1/2"W X 16 1/2"D X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers&lt;br&gt;
+Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Acrylic, Solid Wood.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 198 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H261" s="60" t="inlineStr">
@@ -35057,14 +35057,14 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARISTON Dresser brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth dresser, it pairs well with a wide range of interiors. The Mirror, Solid Wood, Wood Veneer, construction is complemented by Rose Gold tones for a polished look.
-Product Dimensions: 64"W X 17"D X 38"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawers
-Materials: Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 177 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARISTON Dresser brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth dresser, it pairs well with a wide range of interiors. The Mirror, Solid Wood, Wood Veneer, construction is complemented by Rose Gold tones for a polished look.&lt;br&gt;
+Product Dimensions: 64"W X 17"D X 38"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 177 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -35185,14 +35185,14 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BELVA Dresser adds a Traditional touch while keeping the room feeling warm and welcoming. This youth dresser is made to fit naturally into the room. Crafted from Solid Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 56"L X 17"W X 37"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Materials: Solid Wood.
-Color: White
-Weight: 145.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BELVA Dresser adds a Traditional touch while keeping the room feeling warm and welcoming. This youth dresser is made to fit naturally into the room. Crafted from Solid Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 56"L X 17"W X 37"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 145.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -35314,14 +35314,14 @@
       </c>
       <c r="G264" s="60" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CORRY Dresser adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth dresser, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Dark Walnut tones that pair easily with surrounding decor.
-Product Dimensions: 48"W X 17"D X 34"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 94.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CORRY Dresser adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth dresser, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"W X 17"D X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 94.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H264" s="60" t="inlineStr">
@@ -35445,14 +35445,14 @@
       </c>
       <c r="G265" s="60" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CORRY Dresser and its Transitional character. This youth dresser is made to fit naturally into the room. Finished in White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 48"W X 17"D X 34"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 94.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CORRY Dresser and its Transitional character. This youth dresser is made to fit naturally into the room. Finished in White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 48"W X 17"D X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 94.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H265" s="60" t="inlineStr">
@@ -35575,14 +35575,14 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DANI Dresser brings a Transitional look to your home with a refined, comfortable feel. Built as a youth dresser, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by White tones for a polished look.
-Product Dimensions: 48"W X 17"D X 34"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 130.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DANI Dresser brings a Transitional look to your home with a refined, comfortable feel. Built as a youth dresser, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 48"W X 17"D X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 130.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -35703,14 +35703,14 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DIANE Dresser adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth dresser, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Blue tones that pair easily with surrounding decor.
-Product Dimensions: 48"W X 17"D X 34"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Blue
-Weight: 130.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DIANE Dresser adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth dresser, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"W X 17"D X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 130.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -35831,12 +35831,12 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with FANTON Dresser and its Transitional character. As a youth dresser, it is designed to complement your space. Finished in White tones, the Solid Hardwood, build balances durability with visual appeal.
-Product Dimensions: 54"W X 17.5"D X 30.5"H
-Materials: Solid Hardwood.
-Color: White
-Weight: 62 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with FANTON Dresser and its Transitional character. As a youth dresser, it is designed to complement your space. Finished in White tones, the Solid Hardwood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 54"W X 17.5"D X 30.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 62 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -35957,12 +35957,12 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with GRIFFIN Dresser, styled in Transitional and designed for everyday comfort. As a youth dresser, it is designed to complement your space. With Solid Hardwood and Charcoal Brown tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47.2"L X 18.5"W X 31.2"H
-Materials: Solid Hardwood.
-Color: Charcoal Brown
-Weight: 175.22 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with GRIFFIN Dresser, styled in Transitional and designed for everyday comfort. As a youth dresser, it is designed to complement your space. With Solid Hardwood and Charcoal Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47.2"L X 18.5"W X 31.2"H&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: Charcoal Brown&lt;br&gt;
+Weight: 175.22 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -36083,13 +36083,13 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with LAREINA Dresser, styled in Contemporary and designed for everyday comfort. This youth dresser is made to fit naturally into the room. With Solid Rubberwood, Engineered Wood and Pearl White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 54.5"W X 17"D X 34"H Bonus storage &amp; convenience features (from matching set pieces): Hidden Jewelry Drawers
-Felt-Lined Top Drawer
-Materials: Solid Rubberwood, Engineered Wood.
-Color: Pearl White
-Weight: 223 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with LAREINA Dresser, styled in Contemporary and designed for everyday comfort. This youth dresser is made to fit naturally into the room. With Solid Rubberwood, Engineered Wood and Pearl White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 54.5"W X 17"D X 34"H Bonus storage &amp;amp; convenience features (from matching set pieces): Hidden Jewelry Drawers&lt;br&gt;
+Felt-Lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 223 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -36210,15 +36210,15 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYCORIDA Dresser adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth dresser, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in Light Gray tones that pair easily with surrounding decor.
-Product Dimensions: 48"W X 17"D X 34"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Dovetail Drawers
-Felt-lined Top Drawer
-Materials: Solid Wood.
-Color: Light Gray
-Weight: 171.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYCORIDA Dresser adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth dresser, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in Light Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"W X 17"D X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Dovetail Drawers&lt;br&gt;
+Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 171.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -36344,14 +36344,14 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with LYCORIS Dresser, styled in Transitional and designed for everyday comfort. As a youth dresser, it is designed to complement your space. With Solid Wood, Engineered Wood and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 48"W X 17"D X 34"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Engineered Wood.
-Color: White
-Weight: 166.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with LYCORIS Dresser, styled in Transitional and designed for everyday comfort. As a youth dresser, it is designed to complement your space. With Solid Wood, Engineered Wood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 48"W X 17"D X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 166.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -36472,15 +36472,15 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARLEE Dresser adds a Transitional touch while keeping the room feeling warm and welcoming. This youth dresser is made to fit naturally into the room. Crafted from Solid Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 48"W X 17"D X 34 1/8"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): English Dovetail Drawer Construction
-Round Drawer Pulls
-Materials: Solid Wood.
-Color: White
-Weight: 125.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARLEE Dresser adds a Transitional touch while keeping the room feeling warm and welcoming. This youth dresser is made to fit naturally into the room. Crafted from Solid Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"W X 17"D X 34 1/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawer Construction&lt;br&gt;
+Round Drawer Pulls&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 125.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -36601,14 +36601,14 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with OLIVIA Dresser and its Traditional character. This youth dresser is made to fit naturally into the room. Finished in White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 53"W X 17"D X 34"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 165 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with OLIVIA Dresser and its Traditional character. This youth dresser is made to fit naturally into the room. Finished in White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 53"W X 17"D X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 165 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -36729,14 +36729,14 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with OMNUS Dresser and its Transitional character. This youth dresser is made to fit naturally into the room. Finished in Cherry tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 48"W X 17"D X 34"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Cherry
-Weight: 94.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with OMNUS Dresser and its Transitional character. This youth dresser is made to fit naturally into the room. Finished in Cherry tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 48"W X 17"D X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Cherry&lt;br&gt;
+Weight: 94.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -36857,15 +36857,15 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with PRIAM Dresser, styled in Contemporary and designed for everyday comfort. This youth dresser is made to fit naturally into the room. With Solid Wood, and White or Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 5/8"W X 18"D X 33 7/8"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Dovetail Drawers
-Materials: Solid Wood.
-Color: White or Gray
-Weight: 119.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with PRIAM Dresser, styled in Contemporary and designed for everyday comfort. This youth dresser is made to fit naturally into the room. With Solid Wood, and White or Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 5/8"W X 18"D X 33 7/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;br&gt;
+Dovetail Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 119.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -36986,14 +36986,14 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ROANNE Dresser and its Transitional character. This youth dresser is made to fit naturally into the room. Finished in Gray tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 47 1/4"W X 16 3/8"D X 31 5/8"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Gray
-Weight: 139.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ROANNE Dresser and its Transitional character. This youth dresser is made to fit naturally into the room. Finished in Gray tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 47 1/4"W X 16 3/8"D X 31 5/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 139.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -37115,14 +37115,14 @@
       </c>
       <c r="G278" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with STAVROS Dresser, styled in Rustic and designed for everyday comfort. Built as a youth dresser, it pairs well with a wide range of interiors. With Solid Wood, and Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 52"W X 21"D X 34"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Gray
-Weight: 78 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with STAVROS Dresser, styled in Rustic and designed for everyday comfort. Built as a youth dresser, it pairs well with a wide range of interiors. With Solid Wood, and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 52"W X 21"D X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 78 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H278" s="56" t="inlineStr">
@@ -37246,14 +37246,14 @@
       </c>
       <c r="G279" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-STAVROS Dresser adds a Rustic touch while keeping the room feeling warm and welcoming. As a youth dresser, it is designed to complement your space. Crafted from Solid Wood, it is finished in Mahogany tones that pair easily with surrounding decor.
-Product Dimensions: 52"W X 20.5"D X 34"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Mahogany
-Weight: 78 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+STAVROS Dresser adds a Rustic touch while keeping the room feeling warm and welcoming. As a youth dresser, it is designed to complement your space. Crafted from Solid Wood, it is finished in Mahogany tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 52"W X 20.5"D X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Mahogany&lt;br&gt;
+Weight: 78 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H279" s="56" t="inlineStr">
@@ -37377,14 +37377,14 @@
       </c>
       <c r="G280" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with STAVROS Dresser and its Rustic character. This youth dresser is made to fit naturally into the room. Finished in White tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 52"W X 20.5"D X 34"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White
-Weight: 78 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with STAVROS Dresser and its Rustic character. This youth dresser is made to fit naturally into the room. Finished in White tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 52"W X 20.5"D X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 78 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H280" s="56" t="inlineStr">
@@ -37507,14 +37507,14 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VEVEY Dresser brings a Transitional look to your home with a refined, comfortable feel. This youth dresser is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Wire-Brushed Warm Gray tones for a polished look.
-Product Dimensions: 47 5/8"L X 18"W X 33 7/8"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Materials: Solid Wood, Wood Veneer.
-Color: Wire-Brushed Warm Gray
-Weight: 128.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VEVEY Dresser brings a Transitional look to your home with a refined, comfortable feel. This youth dresser is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Wire-Brushed Warm Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 5/8"L X 18"W X 33 7/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Wire-Brushed Warm Gray&lt;br&gt;
+Weight: 128.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -37635,16 +37635,16 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZOHAR Dresser brings a Glam look to your home with a refined, comfortable feel. This youth dresser is made to fit naturally into the room. The Velvet-like, Solid Wood, construction is complemented by Pink tones for a polished look.
-Product Dimensions: 58 1/2"W X 17 1/2"D X 36"H
-Features
-- Glam design
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Velvet-like, Solid Wood.
-Color: Pink
-Weight: 197.56 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZOHAR Dresser brings a Glam look to your home with a refined, comfortable feel. This youth dresser is made to fit naturally into the room. The Velvet-like, Solid Wood, construction is complemented by Pink tones for a polished look.&lt;br&gt;
+Product Dimensions: 58 1/2"W X 17 1/2"D X 36"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: Pink&lt;br&gt;
+Weight: 197.56 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -37765,15 +37765,15 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ALECIA Nightstand w/ USB, styled in Transitional and designed for everyday comfort. This youth night stand is made to fit naturally into the room. With Solid Wood, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 24"W X 16"D X 24"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-USB Charger behind Night Stand
-Materials: Solid Wood.
-Color: White
-Weight: 44 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ALECIA Nightstand w/ USB, styled in Transitional and designed for everyday comfort. This youth night stand is made to fit naturally into the room. With Solid Wood, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 24"W X 16"D X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;br&gt;
+USB Charger behind Night Stand&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -37895,15 +37895,15 @@
       </c>
       <c r="G284" s="51" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ALLIE Nightstand and its Contemporary character. Built as a youth night stand, it pairs well with a wide range of interiors. Finished in Pearl White tones, the Acrylic, Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 22 7/8"W X 16 1/2"D X 24"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): English Dovetail Drawers
-Felt-lined Top Drawers
-Materials: Acrylic, Solid Wood.
-Color: Pearl White
-Weight: 56.42 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ALLIE Nightstand and its Contemporary character. Built as a youth night stand, it pairs well with a wide range of interiors. Finished in Pearl White tones, the Acrylic, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 22 7/8"W X 16 1/2"D X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers&lt;br&gt;
+Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Acrylic, Solid Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 56.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H284" s="51" t="inlineStr">
@@ -38027,15 +38027,15 @@
       </c>
       <c r="G285" s="51" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALLIE Nightstand brings a Contemporary look to your home with a refined, comfortable feel. As a youth night stand, it is designed to complement your space. The Acrylic, Solid Wood, construction is complemented by Rose Gold tones for a polished look.
-Product Dimensions: 22 7/8"W X 16 1/2"D X 24"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): English Dovetail Drawers
-Felt-lined Top Drawer
-Materials: Acrylic, Solid Wood.
-Color: Rose Gold
-Weight: 57 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALLIE Nightstand brings a Contemporary look to your home with a refined, comfortable feel. As a youth night stand, it is designed to complement your space. The Acrylic, Solid Wood, construction is complemented by Rose Gold tones for a polished look.&lt;br&gt;
+Product Dimensions: 22 7/8"W X 16 1/2"D X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers&lt;br&gt;
+Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Acrylic, Solid Wood.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 57 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H285" s="51" t="inlineStr">
@@ -38158,14 +38158,14 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ARISTON Nightstand, styled in Contemporary and designed for everyday comfort. This youth night stand is made to fit naturally into the room. With Mirror, Solid Wood, Wood Veneer, and Rose Gold tones, it blends structure and softness in one clean profile.
-Product Dimensions: 28"W X 17"D X 28"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawers
-Materials: Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 56.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ARISTON Nightstand, styled in Contemporary and designed for everyday comfort. This youth night stand is made to fit naturally into the room. With Mirror, Solid Wood, Wood Veneer, and Rose Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 28"W X 17"D X 28"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 56.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -38286,15 +38286,15 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BELVA Nightstand w/ USB, styled in Traditional and designed for everyday comfort. This youth night stand is made to fit naturally into the room. With Solid Wood, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 24"L X16"W X 27"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-USB Charger in Night Stand
-Materials: Solid Wood.
-Color: White
-Weight: 48.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BELVA Nightstand w/ USB, styled in Traditional and designed for everyday comfort. This youth night stand is made to fit naturally into the room. With Solid Wood, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 24"L X16"W X 27"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;br&gt;
+USB Charger in Night Stand&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 48.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -38415,14 +38415,14 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CARA Nightstand and its Transitional character. This youth night stand is made to fit naturally into the room. Finished in Cherry tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 19"W X 16"D X 21"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Cherry
-Weight: 28.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CARA Nightstand and its Transitional character. This youth night stand is made to fit naturally into the room. Finished in Cherry tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 19"W X 16"D X 21"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Cherry&lt;br&gt;
+Weight: 28.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -38544,14 +38544,14 @@
       </c>
       <c r="G289" s="68" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CORRY Nightstand adds a Transitional touch while keeping the room feeling warm and welcoming. This youth night stand is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in Dark Walnut tones that pair easily with surrounding decor.
-Product Dimensions: 19"W X 16"D X 21"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 28.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CORRY Nightstand adds a Transitional touch while keeping the room feeling warm and welcoming. This youth night stand is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 19"W X 16"D X 21"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 28.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H289" s="68" t="inlineStr">
@@ -38675,14 +38675,14 @@
       </c>
       <c r="G290" s="68" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CORRY Nightstand and its Transitional character. Built as a youth night stand, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 19"W X 16"D X 21"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 28.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CORRY Nightstand and its Transitional character. Built as a youth night stand, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 19"W X 16"D X 21"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 28.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H290" s="68" t="inlineStr">
@@ -38805,14 +38805,14 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with DANI Nightstand and its Transitional character. Built as a youth night stand, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 19"W X 16"D X 21"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 39.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with DANI Nightstand and its Transitional character. Built as a youth night stand, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 19"W X 16"D X 21"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 39.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -38933,14 +38933,14 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with DIANE Nightstand, styled in Transitional and designed for everyday comfort. Built as a youth night stand, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Blue tones, it blends structure and softness in one clean profile.
-Product Dimensions: 19"W X 16"D X 21"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Blue
-Weight: 39.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with DIANE Nightstand, styled in Transitional and designed for everyday comfort. Built as a youth night stand, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 19"W X 16"D X 21"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 39.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -39061,12 +39061,12 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FANTON Nightstand brings a Transitional look to your home with a refined, comfortable feel. This youth night stand is made to fit naturally into the room. The Solid Hardwood, construction is complemented by White tones for a polished look.
-Product Dimensions: 23.5"W X 17.5"D X 23"H
-Materials: Solid Hardwood.
-Color: White
-Weight: 58.42 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FANTON Nightstand brings a Transitional look to your home with a refined, comfortable feel. This youth night stand is made to fit naturally into the room. The Solid Hardwood, construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 23.5"W X 17.5"D X 23"H&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 58.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -39187,12 +39187,12 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GRIFFIN Nightstand adds a Transitional touch while keeping the room feeling warm and welcoming. This youth night stand is made to fit naturally into the room. Crafted from Solid Hardwood, it is finished in Charcoal Brown tones that pair easily with surrounding decor.
-Product Dimensions: 19.5"W X 18.5"D X 23.5"H
-Materials: Solid Hardwood.
-Color: Charcoal Brown
-Weight: 61.71 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GRIFFIN Nightstand adds a Transitional touch while keeping the room feeling warm and welcoming. This youth night stand is made to fit naturally into the room. Crafted from Solid Hardwood, it is finished in Charcoal Brown tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 19.5"W X 18.5"D X 23.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
+Color: Charcoal Brown&lt;br&gt;
+Weight: 61.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -39313,15 +39313,15 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with LYCORIDA Nightstand, styled in Transitional and designed for everyday comfort. Built as a youth night stand, it pairs well with a wide range of interiors. With Solid Wood, and Light Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 19"W X 16"D X 21 1/2"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Dovetail Drawers
-Felt-lined Top Drawer
-Materials: Solid Wood.
-Color: Light Gray
-Weight: 46.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with LYCORIDA Nightstand, styled in Transitional and designed for everyday comfort. Built as a youth night stand, it pairs well with a wide range of interiors. With Solid Wood, and Light Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 19"W X 16"D X 21 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Dovetail Drawers&lt;br&gt;
+Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 46.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -39447,14 +39447,14 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYCORIS Nightstand brings a Transitional look to your home with a refined, comfortable feel. As a youth night stand, it is designed to complement your space. The Solid Wood, Engineered Wood construction is complemented by White tones for a polished look.
-Product Dimensions: 19"W X 16"D X 21.5"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Engineered Wood.
-Color: White
-Weight: 45 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYCORIS Nightstand brings a Transitional look to your home with a refined, comfortable feel. As a youth night stand, it is designed to complement your space. The Solid Wood, Engineered Wood construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 19"W X 16"D X 21.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 45 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -39575,15 +39575,15 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MARLEE Nightstand, styled in Transitional and designed for everyday comfort. This youth night stand is made to fit naturally into the room. With Solid Wood, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 19"W X 16"D X 21"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): English Dovetail Drawer Construction
-Round Drawer Pulls
-Materials: Solid Wood.
-Color: White
-Weight: 46.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MARLEE Nightstand, styled in Transitional and designed for everyday comfort. This youth night stand is made to fit naturally into the room. With Solid Wood, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 19"W X 16"D X 21"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawer Construction&lt;br&gt;
+Round Drawer Pulls&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 46.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -39709,13 +39709,13 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with NIGHTSTAND, styled in Novelty and designed for everyday comfort. As a youth night stand, it is designed to complement your space. With MDF, Particle Board, and PINK tones, it blends structure and softness in one clean profile.
-Product Dimensions: 19"L X 19 1/2"W X 19 3/4"H
-Size: ASSEMBLED Nightstand
-Materials: MDF, Particle Board.
-Color: PINK
-Weight: 45.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with NIGHTSTAND, styled in Novelty and designed for everyday comfort. As a youth night stand, it is designed to complement your space. With MDF, Particle Board, and PINK tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 19"L X 19 1/2"W X 19 3/4"H&lt;br&gt;
+Size: ASSEMBLED Nightstand&lt;/p&gt;
+&lt;p&gt;Materials: MDF, Particle Board.&lt;br&gt;
+Color: PINK&lt;br&gt;
+Weight: 45.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -39836,14 +39836,14 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OLIVIA Nightstand adds a Traditional touch while keeping the room feeling warm and welcoming. This youth night stand is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 24"W X 16"D X 26 5/8"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 52.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OLIVIA Nightstand adds a Traditional touch while keeping the room feeling warm and welcoming. This youth night stand is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 24"W X 16"D X 26 5/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 52.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -39964,15 +39964,15 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PRIAM Nightstand brings a Contemporary look to your home with a refined, comfortable feel. This youth night stand is made to fit naturally into the room. The Solid Wood, construction is complemented by White or Gray tones for a polished look.
-Product Dimensions: 22"W X 15 3/4"D X 23 7/8"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Dovetail Drawers
-Materials: Solid Wood.
-Color: White or Gray
-Weight: 47.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PRIAM Nightstand brings a Contemporary look to your home with a refined, comfortable feel. This youth night stand is made to fit naturally into the room. The Solid Wood, construction is complemented by White or Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 22"W X 15 3/4"D X 23 7/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;br&gt;
+Dovetail Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 47.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -40093,14 +40093,14 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ROANNE Nightstand adds a Transitional touch while keeping the room feeling warm and welcoming. This youth night stand is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in Gray tones that pair easily with surrounding decor.
-Product Dimensions: 19"W X 16 3/8"D X 24"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Gray
-Weight: 38.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ROANNE Nightstand adds a Transitional touch while keeping the room feeling warm and welcoming. This youth night stand is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 19"W X 16 3/8"D X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 38.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -40222,14 +40222,14 @@
       </c>
       <c r="G302" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with STAVROS Nightstand and its Rustic character. Built as a youth night stand, it pairs well with a wide range of interiors. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 21"W X 15"D X 25"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Gray
-Weight: 26 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with STAVROS Nightstand and its Rustic character. Built as a youth night stand, it pairs well with a wide range of interiors. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 21"W X 15"D X 25"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 26 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H302" s="39" t="inlineStr">
@@ -40353,14 +40353,14 @@
       </c>
       <c r="G303" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-STAVROS Nightstand brings a Rustic look to your home with a refined, comfortable feel. As a youth night stand, it is designed to complement your space. The Solid Wood, construction is complemented by Mahogany tones for a polished look.
-Product Dimensions: 21"W X 15"D X 25"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Mahogany
-Weight: 26 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+STAVROS Nightstand brings a Rustic look to your home with a refined, comfortable feel. As a youth night stand, it is designed to complement your space. The Solid Wood, construction is complemented by Mahogany tones for a polished look.&lt;br&gt;
+Product Dimensions: 21"W X 15"D X 25"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Mahogany&lt;br&gt;
+Weight: 26 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H303" s="39" t="inlineStr">
@@ -40484,14 +40484,14 @@
       </c>
       <c r="G304" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with STAVROS Nightstand, styled in Rustic and designed for everyday comfort. This youth night stand is made to fit naturally into the room. With Solid Wood, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 21"W X 15"D X 25"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White
-Weight: 26 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with STAVROS Nightstand, styled in Rustic and designed for everyday comfort. This youth night stand is made to fit naturally into the room. With Solid Wood, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 21"W X 15"D X 25"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 26 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H304" s="39" t="inlineStr">
@@ -40614,14 +40614,14 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with VEVEY Nightstand and its Transitional character. This youth night stand is made to fit naturally into the room. Finished in Wire-Brushed Warm Gray tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 22"L X 15 3/4"W X 23 7/8"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Materials: Solid Wood, Wood Veneer.
-Color: Wire-Brushed Warm Gray
-Weight: 46.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with VEVEY Nightstand and its Transitional character. This youth night stand is made to fit naturally into the room. Finished in Wire-Brushed Warm Gray tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 22"L X 15 3/4"W X 23 7/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Wire-Brushed Warm Gray&lt;br&gt;
+Weight: 46.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -40742,16 +40742,16 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ZOHAR Nightstand and its Glam character. This youth night stand is made to fit naturally into the room. Finished in Pink tones, the Velvet-like, Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 23"W X 17 1/2"D X 26"H
-Features
-- Glam design
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Velvet-like, Solid Wood.
-Color: Pink
-Weight: 70.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ZOHAR Nightstand and its Glam character. This youth night stand is made to fit naturally into the room. Finished in Pink tones, the Velvet-like, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 23"W X 17 1/2"D X 26"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: Pink&lt;br&gt;
+Weight: 70.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -40872,14 +40872,14 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ALLIE Trundle, styled in Contemporary and designed for everyday comfort. This youth accessory is made to fit naturally into the room. With Solid Wood, and Pearl White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 75 1/4"L X 40 3/4"W X 11 5/8"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Converts into 2 Compartment Drawer
-Materials: Solid Wood.
-Color: Pearl White
-Weight: 67.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ALLIE Trundle, styled in Contemporary and designed for everyday comfort. This youth accessory is made to fit naturally into the room. With Solid Wood, and Pearl White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 75 1/4"L X 40 3/4"W X 11 5/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Converts into 2 Compartment Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 67.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -41000,14 +41000,14 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DANI Trundle brings a Transitional look to your home with a refined, comfortable feel. As a youth accessory, it is designed to complement your space. The Solid Wood, Wood Veneer, construction is complemented by White tones for a polished look.
-Product Dimensions: 75 1/8"L X 41 1/2"W X 11 3/8"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 99 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DANI Trundle brings a Transitional look to your home with a refined, comfortable feel. As a youth accessory, it is designed to complement your space. The Solid Wood, Wood Veneer, construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 75 1/8"L X 41 1/2"W X 11 3/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 99 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -41128,14 +41128,14 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DIANE Trundle adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth accessory, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Blue tones that pair easily with surrounding decor.
-Product Dimensions: 75 1/8"L X 41 1/2"W X 11 3/8"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Blue
-Weight: 99 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DIANE Trundle adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth accessory, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 75 1/8"L X 41 1/2"W X 11 3/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 99 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -41256,14 +41256,14 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with GRANO Trundle or Drawers and its Transitional character. This youth accessory is made to fit naturally into the room. Finished in Cherry tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 74 1/4"L X 40 1/2"W X 10 3/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Cherry
-Weight: 70.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with GRANO Trundle or Drawers and its Transitional character. This youth accessory is made to fit naturally into the room. Finished in Cherry tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 74 1/4"L X 40 1/2"W X 10 3/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Cherry&lt;br&gt;
+Weight: 70.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -41385,14 +41385,14 @@
       </c>
       <c r="G311" s="65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with HOOPLE Trundle and its Transitional character. As a youth accessory, it is designed to complement your space. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 75 5/8"L X 40 7/8"W X 9 3/8"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Gray
-Weight: 46.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with HOOPLE Trundle and its Transitional character. As a youth accessory, it is designed to complement your space. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 75 5/8"L X 40 7/8"W X 9 3/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 46.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H311" s="65" t="inlineStr">
@@ -41520,14 +41520,14 @@
       </c>
       <c r="G312" s="65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HOOPLE Trundle brings a Transitional look to your home with a refined, comfortable feel. This youth accessory is made to fit naturally into the room. The Solid Wood, construction is complemented by White tones for a polished look.
-Product Dimensions: 75 5/8"L X 40 7/8"W X 9 3/8"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White
-Weight: 48.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HOOPLE Trundle brings a Transitional look to your home with a refined, comfortable feel. This youth accessory is made to fit naturally into the room. The Solid Wood, construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 75 5/8"L X 40 7/8"W X 9 3/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 48.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H312" s="65" t="inlineStr">
@@ -41654,14 +41654,14 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with OLIVIA Trundle and its Traditional character. Built as a youth accessory, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 75"W X 41 1/4"D X 11 1/2"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 46.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with OLIVIA Trundle and its Traditional character. Built as a youth accessory, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 75"W X 41 1/4"D X 11 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 46.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -41783,14 +41783,14 @@
       </c>
       <c r="G314" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OMNUS Trundle brings a Transitional look to your home with a refined, comfortable feel. As a youth accessory, it is designed to complement your space. The Solid Wood, Wood Veneer, construction is complemented by Cherry tones for a polished look.
-Product Dimensions: 74 1/4"L X 40 1/2"W X 10 3/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Cherry
-Weight: 43.65 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OMNUS Trundle brings a Transitional look to your home with a refined, comfortable feel. As a youth accessory, it is designed to complement your space. The Solid Wood, Wood Veneer, construction is complemented by Cherry tones for a polished look.&lt;br&gt;
+Product Dimensions: 74 1/4"L X 40 1/2"W X 10 3/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Cherry&lt;br&gt;
+Weight: 43.65 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H314" s="39" t="inlineStr">
@@ -41913,14 +41913,14 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ROANNE Trundle Or Drawer and its Transitional character. Built as a youth accessory, it pairs well with a wide range of interiors. Finished in Gray tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 74 3/8"L X 41"W X 11 5/8"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Converts into Two-Compartment Drawer
-Materials: Solid Wood, Wood Veneer.
-Color: Gray
-Weight: 69.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ROANNE Trundle Or Drawer and its Transitional character. Built as a youth accessory, it pairs well with a wide range of interiors. Finished in Gray tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 74 3/8"L X 41"W X 11 5/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Converts into Two-Compartment Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 69.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -42046,14 +42046,14 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VEVEY Trundle or Drawer brings a Transitional look to your home with a refined, comfortable feel. Built as a youth accessory, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Wire-Brushed Warm Gray tones for a polished look.
-Product Dimensions: 76 1/4"L X 40 7/8"W X 10 1/4"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Materials: Solid Wood, Wood Veneer.
-Color: Wire-Brushed Warm Gray
-Weight: 66.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VEVEY Trundle or Drawer brings a Transitional look to your home with a refined, comfortable feel. Built as a youth accessory, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Wire-Brushed Warm Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 76 1/4"L X 40 7/8"W X 10 1/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Wire-Brushed Warm Gray&lt;br&gt;
+Weight: 66.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -42174,14 +42174,14 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALLIE Trundle or Drawer adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth trundle, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in Rose Gold tones that pair easily with surrounding decor.
-Product Dimensions: 75 1/4"L X 40 3/4"W X 11 5/8"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Optional Convertible Trundle or Drawer
-Materials: Solid Wood.
-Color: Rose Gold
-Weight: 68 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALLIE Trundle or Drawer adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth trundle, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in Rose Gold tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 75 1/4"L X 40 3/4"W X 11 5/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Optional Convertible Trundle or Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 68 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -42302,12 +42302,12 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-IVANA Universal Metal Trundle brings a Contemporary look to your home with a refined, comfortable feel. As a youth trundle, it is designed to complement your space. The Metal construction is complemented by Black tones for a polished look.
-Product Dimensions: 74.5"W X 40.5"D X 13"H
-Materials: Metal.
-Color: Black
-Weight: 30.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+IVANA Universal Metal Trundle brings a Contemporary look to your home with a refined, comfortable feel. As a youth trundle, it is designed to complement your space. The Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 74.5"W X 40.5"D X 13"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 30.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -42429,14 +42429,14 @@
       </c>
       <c r="G319" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with OMNUS Trundle, styled in Transitional and designed for everyday comfort. This youth trundle is made to fit naturally into the room. With Solid Wood, and Espresso tones, it blends structure and softness in one clean profile.
-Product Dimensions: 40.5"W X 74"D X 10.5"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Converts to Drawers
-Materials: Solid Wood.
-Color: Espresso
-Weight: 41.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with OMNUS Trundle, styled in Transitional and designed for everyday comfort. This youth trundle is made to fit naturally into the room. With Solid Wood, and Espresso tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 40.5"W X 74"D X 10.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Converts to Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Espresso&lt;br&gt;
+Weight: 41.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H319" s="39" t="inlineStr">
@@ -42564,14 +42564,14 @@
       </c>
       <c r="G320" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OMNUS Trundle adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth trundle, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 75"W X 40.5"D X 11"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Converts to Drawers
-Materials: Solid Wood, Wood Veneer, Engineered Wood.
-Color: White
-Weight: 44 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OMNUS Trundle adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth trundle, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 75"W X 40.5"D X 11"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Converts to Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H320" s="39" t="inlineStr">
@@ -42695,14 +42695,14 @@
       </c>
       <c r="G321" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with OMNUS Trundle w/ 2 Dividers and its Transitional character. As a youth trundle, it is designed to complement your space. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 74 1/4"W X 40 1/2"D X 10 3/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 82.67 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with OMNUS Trundle w/ 2 Dividers and its Transitional character. As a youth trundle, it is designed to complement your space. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 74 1/4"W X 40 1/2"D X 10 3/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 82.67 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H321" s="41" t="inlineStr">
@@ -42830,14 +42830,14 @@
       </c>
       <c r="G322" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OMNUS Trundle w/ 2 Dividers brings a Transitional look to your home with a refined, comfortable feel. This youth trundle is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Gray tones for a polished look.
-Product Dimensions: 74 1/4"W X 40 1/2"D X 10 3/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Gray
-Weight: 82.67 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OMNUS Trundle w/ 2 Dividers brings a Transitional look to your home with a refined, comfortable feel. This youth trundle is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 74 1/4"W X 40 1/2"D X 10 3/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 82.67 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H322" s="41" t="inlineStr">
@@ -42961,14 +42961,14 @@
       </c>
       <c r="G323" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with OMNUS Trundle w/ 2 Dividers, styled in Transitional and designed for everyday comfort. Built as a youth trundle, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 74 1/4"W X 40 1/2"D X 10 3/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 83.75 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with OMNUS Trundle w/ 2 Dividers, styled in Transitional and designed for everyday comfort. Built as a youth trundle, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 74 1/4"W X 40 1/2"D X 10 3/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 83.75 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H323" s="41" t="inlineStr">
@@ -43091,14 +43091,14 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with PRIAM Trundle or Drawers, styled in Contemporary and designed for everyday comfort. Built as a youth trundle, it pairs well with a wide range of interiors. With Solid Wood, and White or Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 75 5/8"L X 40 3/4"W X 11"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Trundle Converts to Drawers
-Materials: Solid Wood.
-Color: White or Gray
-Weight: 82.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with PRIAM Trundle or Drawers, styled in Contemporary and designed for everyday comfort. Built as a youth trundle, it pairs well with a wide range of interiors. With Solid Wood, and White or Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 75 5/8"L X 40 3/4"W X 11"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle Converts to Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 82.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -43219,14 +43219,14 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DANI Armoire adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth armoire, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 32 1/8"W X 16"D X 51 1/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 114.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DANI Armoire adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth armoire, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 32 1/8"W X 16"D X 51 1/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 114.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -43347,14 +43347,14 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VEVEY Armoire adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth armoire, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Wire-Brushed Warm Gray tones that pair easily with surrounding decor.
-Product Dimensions: 40"L X 18"W X 47 3/4"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Top Drawer
-Materials: Solid Wood, Wood Veneer.
-Color: Wire-Brushed Warm Gray
-Weight: 156.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VEVEY Armoire adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth armoire, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Wire-Brushed Warm Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 40"L X 18"W X 47 3/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Wire-Brushed Warm Gray&lt;br&gt;
+Weight: 156.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -43475,12 +43475,12 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LAREINA Nightstand brings a Contemporary look to your home with a refined, comfortable feel. This youth nightstand is made to fit naturally into the room. The Solid Rubberwood, Engineered Wood construction is complemented by Pearl White tones for a polished look.
-Product Dimensions: 22.5"W X 17"D X 24"H Bonus storage &amp; convenience features (from matching set pieces): Felt-Lined Top Drawer
-Materials: Solid Rubberwood, Engineered Wood.
-Color: Pearl White
-Weight: 59.97 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LAREINA Nightstand brings a Contemporary look to your home with a refined, comfortable feel. This youth nightstand is made to fit naturally into the room. The Solid Rubberwood, Engineered Wood construction is complemented by Pearl White tones for a polished look.&lt;br&gt;
+Product Dimensions: 22.5"W X 17"D X 24"H Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-Lined Top Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 59.97 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -43606,15 +43606,15 @@
       </c>
       <c r="G328" s="68" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MARINOS Captain Bed and its Rustic character. This youth day bed is made to fit naturally into the room. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 78"W X 41"D X 34"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Large Underbed Drawers
-Materials: Solid Wood.
-Color: Gray
-Weight: 171 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MARINOS Captain Bed and its Rustic character. This youth day bed is made to fit naturally into the room. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 78"W X 41"D X 34"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Large Underbed Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 171 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H328" s="68" t="inlineStr">
@@ -43740,15 +43740,15 @@
       </c>
       <c r="G329" s="68" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARINOS Captain Bed brings a Rustic look to your home with a refined, comfortable feel. Built as a youth day bed, it pairs well with a wide range of interiors. The Solid Wood, construction is complemented by Mahogany tones for a polished look.
-Product Dimensions: 78"W X 41"D X 34"H
-Size: Twin
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Large Underbed Drawers
-Materials: Solid Wood.
-Color: Mahogany
-Weight: 171 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARINOS Captain Bed brings a Rustic look to your home with a refined, comfortable feel. Built as a youth day bed, it pairs well with a wide range of interiors. The Solid Wood, construction is complemented by Mahogany tones for a polished look.&lt;br&gt;
+Product Dimensions: 78"W X 41"D X 34"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Large Underbed Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Mahogany&lt;br&gt;
+Weight: 171 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H329" s="68" t="inlineStr">
@@ -43870,14 +43870,14 @@
       </c>
       <c r="G330" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OMNUS Desk adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth desk, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Cherry tones that pair easily with surrounding decor.
-Product Dimensions: 48"W X 20"D X 32"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Cherry
-Weight: 88.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OMNUS Desk adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth desk, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Cherry tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"W X 20"D X 32"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Cherry&lt;br&gt;
+Weight: 88.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H330" s="54" t="inlineStr">
@@ -44001,14 +44001,14 @@
       </c>
       <c r="G331" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with OMNUS Desk and its Transitional character. As a youth desk, it is designed to complement your space. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 48"W X 20"D X 32"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 88.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with OMNUS Desk and its Transitional character. As a youth desk, it is designed to complement your space. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 48"W X 20"D X 32"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 88.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H331" s="54" t="inlineStr">
@@ -44132,14 +44132,14 @@
       </c>
       <c r="G332" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OMNUS Desk brings a Transitional look to your home with a refined, comfortable feel. This youth desk is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by White tones for a polished look.
-Product Dimensions: 48"W X 20"D X 32"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 88.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OMNUS Desk brings a Transitional look to your home with a refined, comfortable feel. This youth desk is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 48"W X 20"D X 32"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 88.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H332" s="54" t="inlineStr">
@@ -44263,14 +44263,14 @@
       </c>
       <c r="G333" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OMNUS Hutch brings a Transitional look to your home with a refined, comfortable feel. Built as a youth desk, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Cherry tones for a polished look.
-Product Dimensions: 46"W X 12"D X 24"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Cherry
-Weight: 29.76 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OMNUS Hutch brings a Transitional look to your home with a refined, comfortable feel. Built as a youth desk, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Cherry tones for a polished look.&lt;br&gt;
+Product Dimensions: 46"W X 12"D X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Cherry&lt;br&gt;
+Weight: 29.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H333" s="56" t="inlineStr">
@@ -44394,14 +44394,14 @@
       </c>
       <c r="G334" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with OMNUS Hutch, styled in Transitional and designed for everyday comfort. As a youth desk, it is designed to complement your space. With Solid Wood, Wood Veneer, and Dark Walnut tones, it blends structure and softness in one clean profile.
-Product Dimensions: 46"W X 12"D X 24"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 27.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with OMNUS Hutch, styled in Transitional and designed for everyday comfort. As a youth desk, it is designed to complement your space. With Solid Wood, Wood Veneer, and Dark Walnut tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 46"W X 12"D X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 27.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H334" s="56" t="inlineStr">
@@ -44525,14 +44525,14 @@
       </c>
       <c r="G335" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OMNUS Hutch adds a Transitional touch while keeping the room feeling warm and welcoming. This youth desk is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 46"W X 12"D X 24"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 27.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OMNUS Hutch adds a Transitional touch while keeping the room feeling warm and welcoming. This youth desk is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 46"W X 12"D X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 27.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H335" s="56" t="inlineStr">
@@ -44655,14 +44655,14 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with OMNUS Underbed Storage w/ Sliding Doors and its Transitional character. This youth shelf or storage is made to fit naturally into the room. Finished in White tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 75 1/2"L X15 3/4 "W X 10 1/2"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White
-Weight: 52.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with OMNUS Underbed Storage w/ Sliding Doors and its Transitional character. This youth shelf or storage is made to fit naturally into the room. Finished in White tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 75 1/2"L X15 3/4 "W X 10 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 52.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">

--- a/FOA Singles/Youth-Single.xlsx
+++ b/FOA Singles/Youth-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD336"/>
+  <dimension ref="A1:AG336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,21 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Variable tags</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Product Category</t>
         </is>
       </c>
     </row>
@@ -932,7 +947,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, ALBANI</t>
+          <t>Youth, Bunk Bed, ALBANI, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1090,22 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, AUBREY</t>
+          <t>Youth, Bunk Bed, AUBREY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1237,22 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, BALLARAT</t>
+          <t>Youth, Bunk Bed, BALLARAT, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1380,22 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, BROCKET</t>
+          <t>Youth, Bunk Bed, BROCKET, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1527,22 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, BROOKINGS</t>
+          <t>Youth, Bunk Bed, BROOKINGS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1674,22 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, BROOKINGS</t>
+          <t>Youth, Bunk Bed, BROOKINGS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1821,22 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, BROOKINGS</t>
+          <t>Youth, Bunk Bed, BROOKINGS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1968,22 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, BROOKINGS</t>
+          <t>Youth, Bunk Bed, BROOKINGS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -1983,7 +2118,22 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CALIFORNIA III</t>
+          <t>Youth, Bunk Bed, CALIFORNIA III, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2268,22 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CALIFORNIA III</t>
+          <t>Youth, Bunk Bed, CALIFORNIA III, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2418,22 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CALIFORNIA III</t>
+          <t>Youth, Bunk Bed, CALIFORNIA III, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2568,22 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CALIFORNIA III</t>
+          <t>Youth, Bunk Bed, CALIFORNIA III, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2718,22 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CALIFORNIA III</t>
+          <t>Youth, Bunk Bed, CALIFORNIA III, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2864,22 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CALIFORNIA IV</t>
+          <t>Youth, Bunk Bed, CALIFORNIA IV, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -2788,7 +3013,22 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CALIFORNIA IV</t>
+          <t>Youth, Bunk Bed, CALIFORNIA IV, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -2922,7 +3162,22 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CALIFORNIA IV</t>
+          <t>Youth, Bunk Bed, CALIFORNIA IV, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3311,22 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CALIFORNIA IV</t>
+          <t>Youth, Bunk Bed, CALIFORNIA IV, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3460,22 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CALIFORNIA IV</t>
+          <t>Youth, Bunk Bed, CALIFORNIA IV, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3605,22 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CALLISTUS</t>
+          <t>Youth, Bunk Bed, CALLISTUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3750,22 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CALLISTUS</t>
+          <t>Youth, Bunk Bed, CALLISTUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3899,22 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CAMERON</t>
+          <t>Youth, Bunk Bed, CAMERON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -3718,7 +4048,22 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CAMERON</t>
+          <t>Youth, Bunk Bed, CAMERON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -3852,7 +4197,22 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CAMERON</t>
+          <t>Youth, Bunk Bed, CAMERON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -3986,7 +4346,22 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CAMERON</t>
+          <t>Youth, Bunk Bed, CAMERON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4495,22 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CAMERON</t>
+          <t>Youth, Bunk Bed, CAMERON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4644,22 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CAMERON</t>
+          <t>Youth, Bunk Bed, CAMERON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4789,22 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CANBERRA II</t>
+          <t>Youth, Bunk Bed, CANBERRA II, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4940,22 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CANDICE</t>
+          <t>Youth, Bunk Bed, CANDICE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -4656,7 +5091,22 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CANDICE</t>
+          <t>Youth, Bunk Bed, CANDICE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -4787,7 +5237,22 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CAROLINA</t>
+          <t>Youth, Bunk Bed, CAROLINA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -4918,7 +5383,22 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CASSIDY</t>
+          <t>Youth, Bunk Bed, CASSIDY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5530,22 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CLAPTON</t>
+          <t>Youth, Bunk Bed, CLAPTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5677,22 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CLAPTON</t>
+          <t>Youth, Bunk Bed, CLAPTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5824,22 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CLAPTON</t>
+          <t>Youth, Bunk Bed, CLAPTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5971,22 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CLAPTON</t>
+          <t>Youth, Bunk Bed, CLAPTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -5578,7 +6118,22 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CLAPTON</t>
+          <t>Youth, Bunk Bed, CLAPTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -5706,7 +6261,22 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CLAREN</t>
+          <t>Youth, Bunk Bed, CLAREN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -5834,7 +6404,22 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CLAREN</t>
+          <t>Youth, Bunk Bed, CLAREN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -5962,7 +6547,22 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CLAREN</t>
+          <t>Youth, Bunk Bed, CLAREN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6694,22 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CYBILL</t>
+          <t>Youth, Bunk Bed, CYBILL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6841,22 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CYBILL</t>
+          <t>Youth, Bunk Bed, CYBILL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6988,22 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, CYBILL</t>
+          <t>Youth, Bunk Bed, CYBILL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -6492,7 +7137,22 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, DAMARIS</t>
+          <t>Youth, Bunk Bed, DAMARIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -6626,7 +7286,22 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, DAMARIS</t>
+          <t>Youth, Bunk Bed, DAMARIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -6760,7 +7435,22 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, ELLINGTON</t>
+          <t>Youth, Bunk Bed, ELLINGTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -6894,7 +7584,22 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, ELLINGTON</t>
+          <t>Youth, Bunk Bed, ELLINGTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -7028,7 +7733,22 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, ELLINGTON</t>
+          <t>Youth, Bunk Bed, ELLINGTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7882,22 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, ELLINGTON</t>
+          <t>Youth, Bunk Bed, ELLINGTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -7296,7 +8031,22 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, EMILEE</t>
+          <t>Youth, Bunk Bed, EMILEE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -7434,7 +8184,22 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, EMILEE</t>
+          <t>Youth, Bunk Bed, EMILEE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -7568,7 +8333,22 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, EMILEE</t>
+          <t>Youth, Bunk Bed, EMILEE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -7702,7 +8482,22 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, EMILEE</t>
+          <t>Youth, Bunk Bed, EMILEE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -7834,7 +8629,22 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, FELGU</t>
+          <t>Youth, Bunk Bed, FELGU, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -7966,7 +8776,22 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, FELGU</t>
+          <t>Youth, Bunk Bed, FELGU, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8923,22 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, FELGU</t>
+          <t>Youth, Bunk Bed, FELGU, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -8230,7 +9070,22 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, FINNERTY</t>
+          <t>Youth, Bunk Bed, FINNERTY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -8362,7 +9217,22 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, FINNERTY</t>
+          <t>Youth, Bunk Bed, FINNERTY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -8494,7 +9364,22 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, FINNERTY</t>
+          <t>Youth, Bunk Bed, FINNERTY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -8626,7 +9511,22 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, FINNERTY</t>
+          <t>Youth, Bunk Bed, FINNERTY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -8758,7 +9658,22 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, FINNERTY</t>
+          <t>Youth, Bunk Bed, FINNERTY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -8890,7 +9805,22 @@
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, FINNERTY</t>
+          <t>Youth, Bunk Bed, FINNERTY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9954,22 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, FINSBURY</t>
+          <t>Youth, Bunk Bed, FINSBURY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -9158,7 +10103,22 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, FINSBURY</t>
+          <t>Youth, Bunk Bed, FINSBURY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -9292,7 +10252,22 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, FINSBURY</t>
+          <t>Youth, Bunk Bed, FINSBURY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -9430,7 +10405,22 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, HECTOR</t>
+          <t>Youth, Bunk Bed, HECTOR, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -9568,7 +10558,22 @@
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, HECTOR</t>
+          <t>Youth, Bunk Bed, HECTOR, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -9706,7 +10711,22 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, HECTOR</t>
+          <t>Youth, Bunk Bed, HECTOR, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -9845,7 +10865,22 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, HOOPLE</t>
+          <t>Youth, Bunk Bed, HOOPLE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -9984,7 +11019,22 @@
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, HOOPLE</t>
+          <t>Youth, Bunk Bed, HOOPLE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -10118,7 +11168,22 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, HOOPLE</t>
+          <t>Youth, Bunk Bed, HOOPLE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -10252,7 +11317,22 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, HOOPLE</t>
+          <t>Youth, Bunk Bed, HOOPLE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -10383,7 +11463,22 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, HORTENSE</t>
+          <t>Youth, Bunk Bed, HORTENSE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -10505,7 +11600,22 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, JOJO</t>
+          <t>Youth, Bunk Bed, JOJO, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -10633,7 +11743,22 @@
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, LAFRAY</t>
+          <t>Youth, Bunk Bed, LAFRAY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -10765,7 +11890,22 @@
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, LOVIA</t>
+          <t>Youth, Bunk Bed, LOVIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -10897,7 +12037,22 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, LOVIA</t>
+          <t>Youth, Bunk Bed, LOVIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11029,7 +12184,22 @@
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, LOVIA</t>
+          <t>Youth, Bunk Bed, LOVIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11159,7 +12329,22 @@
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, MELITTA</t>
+          <t>Youth, Bunk Bed, MELITTA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11296,7 +12481,22 @@
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, MOLTON</t>
+          <t>Youth, Bunk Bed, MOLTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11433,7 +12633,22 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, MOLTON</t>
+          <t>Youth, Bunk Bed, MOLTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11570,7 +12785,22 @@
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, MOLTON</t>
+          <t>Youth, Bunk Bed, MOLTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11708,7 +12938,22 @@
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, MYLES</t>
+          <t>Youth, Bunk Bed, MYLES, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11846,7 +13091,22 @@
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, MYLES</t>
+          <t>Youth, Bunk Bed, MYLES, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11984,7 +13244,22 @@
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, MYLES</t>
+          <t>Youth, Bunk Bed, MYLES, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -12118,7 +13393,22 @@
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, NAUTIA</t>
+          <t>Youth, Bunk Bed, NAUTIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -12252,7 +13542,22 @@
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, NAUTIA</t>
+          <t>Youth, Bunk Bed, NAUTIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -12386,7 +13691,22 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, NAUTIA</t>
+          <t>Youth, Bunk Bed, NAUTIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -12520,7 +13840,22 @@
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, NAUTIA</t>
+          <t>Youth, Bunk Bed, NAUTIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -12648,7 +13983,22 @@
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, OLGA I</t>
+          <t>Youth, Bunk Bed, OLGA I, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -12776,7 +14126,22 @@
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, OLGA I</t>
+          <t>Youth, Bunk Bed, OLGA I, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -12904,7 +14269,22 @@
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, OLGA I</t>
+          <t>Youth, Bunk Bed, OLGA I, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -13032,7 +14412,22 @@
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, OLGA I</t>
+          <t>Youth, Bunk Bed, OLGA I, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -13160,7 +14555,22 @@
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, OLGA I</t>
+          <t>Youth, Bunk Bed, OLGA I, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -13288,7 +14698,22 @@
       </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, OLGA I</t>
+          <t>Youth, Bunk Bed, OLGA I, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -13416,7 +14841,22 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, OLGA I</t>
+          <t>Youth, Bunk Bed, OLGA I, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -13544,7 +14984,22 @@
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, OLGA I</t>
+          <t>Youth, Bunk Bed, OLGA I, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -13672,7 +15127,22 @@
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, OLGA III</t>
+          <t>Youth, Bunk Bed, OLGA III, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -13804,7 +15274,22 @@
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, OLGA</t>
+          <t>Youth, Bunk Bed, OLGA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -13938,7 +15423,22 @@
       </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, OPAL III</t>
+          <t>Youth, Bunk Bed, OPAL III, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -14072,7 +15572,22 @@
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, OPAL III</t>
+          <t>Youth, Bunk Bed, OPAL III, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -14210,7 +15725,22 @@
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, PANOS</t>
+          <t>Youth, Bunk Bed, PANOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -14348,7 +15878,22 @@
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, PANOS</t>
+          <t>Youth, Bunk Bed, PANOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -14486,7 +16031,22 @@
       </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, PANOS</t>
+          <t>Youth, Bunk Bed, PANOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -14624,7 +16184,22 @@
       </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, PHILOTUS</t>
+          <t>Youth, Bunk Bed, PHILOTUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -14762,7 +16337,22 @@
       </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, PHILOTUS</t>
+          <t>Youth, Bunk Bed, PHILOTUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -14900,7 +16490,22 @@
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, PHILOTUS</t>
+          <t>Youth, Bunk Bed, PHILOTUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -15038,7 +16643,22 @@
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, PLUTUS</t>
+          <t>Youth, Bunk Bed, PLUTUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -15176,7 +16796,22 @@
       </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, PLUTUS</t>
+          <t>Youth, Bunk Bed, PLUTUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -15314,7 +16949,22 @@
       </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, PLUTUS</t>
+          <t>Youth, Bunk Bed, PLUTUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -15448,7 +17098,22 @@
       </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, RAINBOW</t>
+          <t>Youth, Bunk Bed, RAINBOW, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -15582,7 +17247,22 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, RAINBOW</t>
+          <t>Youth, Bunk Bed, RAINBOW, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -15716,7 +17396,22 @@
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, RAINBOW</t>
+          <t>Youth, Bunk Bed, RAINBOW, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -15850,7 +17545,22 @@
       </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, RAINBOW</t>
+          <t>Youth, Bunk Bed, RAINBOW, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -15984,7 +17694,22 @@
       </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, RAINBOW</t>
+          <t>Youth, Bunk Bed, RAINBOW, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -16122,7 +17847,22 @@
       </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, RHONDA</t>
+          <t>Youth, Bunk Bed, RHONDA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -16260,7 +18000,22 @@
       </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, RHONDA</t>
+          <t>Youth, Bunk Bed, RHONDA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -16398,7 +18153,22 @@
       </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, RHONDA</t>
+          <t>Youth, Bunk Bed, RHONDA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -16532,7 +18302,22 @@
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, ROTHWELL</t>
+          <t>Youth, Bunk Bed, ROTHWELL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -16666,7 +18451,22 @@
       </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, ROTHWELL</t>
+          <t>Youth, Bunk Bed, ROTHWELL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -16800,7 +18600,22 @@
       </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, ROTHWELL</t>
+          <t>Youth, Bunk Bed, ROTHWELL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -16934,7 +18749,22 @@
       </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, ROTHWELL</t>
+          <t>Youth, Bunk Bed, ROTHWELL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -17068,7 +18898,22 @@
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, SOLPINE</t>
+          <t>Youth, Bunk Bed, SOLPINE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -17206,7 +19051,22 @@
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, SOLPINE</t>
+          <t>Youth, Bunk Bed, SOLPINE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -17340,7 +19200,22 @@
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, SOLPINE</t>
+          <t>Youth, Bunk Bed, SOLPINE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -17472,7 +19347,22 @@
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, SOUTHALL</t>
+          <t>Youth, Bunk Bed, SOUTHALL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -17604,7 +19494,22 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, SOUTHALL</t>
+          <t>Youth, Bunk Bed, SOUTHALL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -17736,7 +19641,22 @@
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, SPRING CREEK</t>
+          <t>Youth, Bunk Bed, SPRING CREEK, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -17868,7 +19788,22 @@
       </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, SPRING CREEK</t>
+          <t>Youth, Bunk Bed, SPRING CREEK, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -18000,7 +19935,22 @@
       </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, SPRING CREEK</t>
+          <t>Youth, Bunk Bed, SPRING CREEK, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -18130,7 +20080,22 @@
       </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, STAMOS</t>
+          <t>Youth, Bunk Bed, STAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -18260,7 +20225,22 @@
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, STAMOS</t>
+          <t>Youth, Bunk Bed, STAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -18390,7 +20370,22 @@
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, STAMOS</t>
+          <t>Youth, Bunk Bed, STAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -18527,7 +20522,22 @@
       </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, TYMON</t>
+          <t>Youth, Bunk Bed, TYMON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -18659,7 +20669,22 @@
       </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, UNIVERSITY</t>
+          <t>Youth, Bunk Bed, UNIVERSITY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -18791,7 +20816,22 @@
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, UNIVERSITY</t>
+          <t>Youth, Bunk Bed, UNIVERSITY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -18923,7 +20963,22 @@
       </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>Youth, Bunk Bed, UNIVERSITY</t>
+          <t>Youth, Bunk Bed, UNIVERSITY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Bunk Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -19051,7 +21106,22 @@
       </c>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>Youth, Bed, ALBANO</t>
+          <t>Youth, Bed, ALBANO, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -19179,7 +21249,22 @@
       </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>Youth, Bed, ALBANO</t>
+          <t>Youth, Bed, ALBANO, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -19310,7 +21395,22 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>Youth, Bed, ALECIA</t>
+          <t>Youth, Bed, ALECIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -19441,7 +21541,22 @@
       </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>Youth, Bed, ALECIA</t>
+          <t>Youth, Bed, ALECIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -19577,7 +21692,22 @@
       </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>Youth, Bed, ALLIE</t>
+          <t>Youth, Bed, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -19713,7 +21843,22 @@
       </c>
       <c r="AD143" t="inlineStr">
         <is>
-          <t>Youth, Bed, ALLIE</t>
+          <t>Youth, Bed, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -19849,7 +21994,22 @@
       </c>
       <c r="AD144" t="inlineStr">
         <is>
-          <t>Youth, Bed, ALLIE</t>
+          <t>Youth, Bed, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -19985,7 +22145,22 @@
       </c>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>Youth, Bed, ALLIE</t>
+          <t>Youth, Bed, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -20120,7 +22295,22 @@
       </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>Youth, Bed, ARISTON</t>
+          <t>Youth, Bed, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -20255,7 +22445,22 @@
       </c>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>Youth, Bed, ARISTON</t>
+          <t>Youth, Bed, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -20390,7 +22595,22 @@
       </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>Youth, Bed, ARISTON</t>
+          <t>Youth, Bed, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -20525,7 +22745,22 @@
       </c>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>Youth, Bed, ARISTON</t>
+          <t>Youth, Bed, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -20660,7 +22895,22 @@
       </c>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>Youth, Bed, ARISTON</t>
+          <t>Youth, Bed, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -20795,7 +23045,22 @@
       </c>
       <c r="AD151" t="inlineStr">
         <is>
-          <t>Youth, Bed, ARISTON</t>
+          <t>Youth, Bed, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -20927,7 +23192,22 @@
       </c>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>Youth, Bed, BECKY</t>
+          <t>Youth, Bed, BECKY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -21059,7 +23339,22 @@
       </c>
       <c r="AD153" t="inlineStr">
         <is>
-          <t>Youth, Bed, BECKY</t>
+          <t>Youth, Bed, BECKY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -21191,7 +23486,22 @@
       </c>
       <c r="AD154" t="inlineStr">
         <is>
-          <t>Youth, Bed, BELVA</t>
+          <t>Youth, Bed, BELVA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -21323,7 +23633,22 @@
       </c>
       <c r="AD155" t="inlineStr">
         <is>
-          <t>Youth, Bed, BELVA</t>
+          <t>Youth, Bed, BELVA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -21453,7 +23778,22 @@
       </c>
       <c r="AD156" t="inlineStr">
         <is>
-          <t>Youth, Bed, CARA</t>
+          <t>Youth, Bed, CARA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -21583,7 +23923,22 @@
       </c>
       <c r="AD157" t="inlineStr">
         <is>
-          <t>Youth, Bed, CAREN</t>
+          <t>Youth, Bed, CAREN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -21713,7 +24068,22 @@
       </c>
       <c r="AD158" t="inlineStr">
         <is>
-          <t>Youth, Bed, CARUS</t>
+          <t>Youth, Bed, CARUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -21845,7 +24215,22 @@
       </c>
       <c r="AD159" t="inlineStr">
         <is>
-          <t>Youth, Bed, CLEMENS</t>
+          <t>Youth, Bed, CLEMENS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -21981,7 +24366,22 @@
       </c>
       <c r="AD160" t="inlineStr">
         <is>
-          <t>Youth, Bed, CLEMENS</t>
+          <t>Youth, Bed, CLEMENS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -22117,7 +24517,22 @@
       </c>
       <c r="AD161" t="inlineStr">
         <is>
-          <t>Youth, Bed, CLEMENS</t>
+          <t>Youth, Bed, CLEMENS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -22247,7 +24662,22 @@
       </c>
       <c r="AD162" t="inlineStr">
         <is>
-          <t>Youth, Bed, CRESWELL</t>
+          <t>Youth, Bed, CRESWELL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -22377,7 +24807,22 @@
       </c>
       <c r="AD163" t="inlineStr">
         <is>
-          <t>Youth, Bed, CRESWELL</t>
+          <t>Youth, Bed, CRESWELL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -22508,7 +24953,22 @@
       </c>
       <c r="AD164" t="inlineStr">
         <is>
-          <t>Youth, Bed, DANI</t>
+          <t>Youth, Bed, DANI, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -22639,7 +25099,22 @@
       </c>
       <c r="AD165" t="inlineStr">
         <is>
-          <t>Youth, Bed, DANI</t>
+          <t>Youth, Bed, DANI, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -22767,7 +25242,22 @@
       </c>
       <c r="AD166" t="inlineStr">
         <is>
-          <t>Youth, Bed, DAYVILLE</t>
+          <t>Youth, Bed, DAYVILLE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -22898,7 +25388,22 @@
       </c>
       <c r="AD167" t="inlineStr">
         <is>
-          <t>Youth, Bed, DIANE</t>
+          <t>Youth, Bed, DIANE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -23029,7 +25534,22 @@
       </c>
       <c r="AD168" t="inlineStr">
         <is>
-          <t>Youth, Bed, DIANE</t>
+          <t>Youth, Bed, DIANE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -23161,7 +25681,22 @@
       </c>
       <c r="AD169" t="inlineStr">
         <is>
-          <t>Youth, Bed, DUSTRACK</t>
+          <t>Youth, Bed, DUSTRACK, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -23293,7 +25828,22 @@
       </c>
       <c r="AD170" t="inlineStr">
         <is>
-          <t>Youth, Bed, DUSTRACK</t>
+          <t>Youth, Bed, DUSTRACK, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -23421,7 +25971,22 @@
       </c>
       <c r="AD171" t="inlineStr">
         <is>
-          <t>Youth, Bed, FANTON</t>
+          <t>Youth, Bed, FANTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -23549,7 +26114,22 @@
       </c>
       <c r="AD172" t="inlineStr">
         <is>
-          <t>Youth, Bed, FIRESTALL</t>
+          <t>Youth, Bed, FIRESTALL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -23677,7 +26257,22 @@
       </c>
       <c r="AD173" t="inlineStr">
         <is>
-          <t>Youth, Bed, GRIFFIN</t>
+          <t>Youth, Bed, GRIFFIN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -23805,7 +26400,22 @@
       </c>
       <c r="AD174" t="inlineStr">
         <is>
-          <t>Youth, Bed, GT RACER</t>
+          <t>Youth, Bed, GT RACER, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -23933,7 +26543,22 @@
       </c>
       <c r="AD175" t="inlineStr">
         <is>
-          <t>Youth, Bed, GT RACER</t>
+          <t>Youth, Bed, GT RACER, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -24051,7 +26676,22 @@
       </c>
       <c r="AD176" t="inlineStr">
         <is>
-          <t>Youth, Bed, JOURLEY</t>
+          <t>Youth, Bed, JOURLEY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -24169,7 +26809,22 @@
       </c>
       <c r="AD177" t="inlineStr">
         <is>
-          <t>Youth, Bed, KARSTEN</t>
+          <t>Youth, Bed, KARSTEN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -24297,7 +26952,22 @@
       </c>
       <c r="AD178" t="inlineStr">
         <is>
-          <t>Youth, Bed, LAREINA</t>
+          <t>Youth, Bed, LAREINA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -24423,7 +27093,22 @@
       </c>
       <c r="AD179" t="inlineStr">
         <is>
-          <t>Youth, Bed, LAREINA</t>
+          <t>Youth, Bed, LAREINA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -24551,7 +27236,22 @@
       </c>
       <c r="AD180" t="inlineStr">
         <is>
-          <t>Youth, Bed, LAREINA</t>
+          <t>Youth, Bed, LAREINA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -24688,7 +27388,22 @@
       </c>
       <c r="AD181" t="inlineStr">
         <is>
-          <t>Youth, Bed, LYCORIDA</t>
+          <t>Youth, Bed, LYCORIDA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -24825,7 +27540,22 @@
       </c>
       <c r="AD182" t="inlineStr">
         <is>
-          <t>Youth, Bed, LYCORIDA</t>
+          <t>Youth, Bed, LYCORIDA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -24955,7 +27685,22 @@
       </c>
       <c r="AD183" t="inlineStr">
         <is>
-          <t>Youth, Bed, LYCORIS</t>
+          <t>Youth, Bed, LYCORIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -25085,7 +27830,22 @@
       </c>
       <c r="AD184" t="inlineStr">
         <is>
-          <t>Youth, Bed, LYCORIS</t>
+          <t>Youth, Bed, LYCORIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -25216,7 +27976,22 @@
       </c>
       <c r="AD185" t="inlineStr">
         <is>
-          <t>Youth, Bed, MARILLA</t>
+          <t>Youth, Bed, MARILLA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -25347,7 +28122,22 @@
       </c>
       <c r="AD186" t="inlineStr">
         <is>
-          <t>Youth, Bed, MARILLA</t>
+          <t>Youth, Bed, MARILLA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -25479,7 +28269,22 @@
       </c>
       <c r="AD187" t="inlineStr">
         <is>
-          <t>Youth, Bed, MARLEE</t>
+          <t>Youth, Bed, MARLEE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -25611,7 +28416,22 @@
       </c>
       <c r="AD188" t="inlineStr">
         <is>
-          <t>Youth, Bed, MARLEE</t>
+          <t>Youth, Bed, MARLEE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -25739,7 +28559,22 @@
       </c>
       <c r="AD189" t="inlineStr">
         <is>
-          <t>Youth, Bed, MCPHERSON</t>
+          <t>Youth, Bed, MCPHERSON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -25871,7 +28706,22 @@
       </c>
       <c r="AD190" t="inlineStr">
         <is>
-          <t>Youth, Bed, NICOLI</t>
+          <t>Youth, Bed, NICOLI, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26001,7 +28851,22 @@
       </c>
       <c r="AD191" t="inlineStr">
         <is>
-          <t>Youth, Bed, OLIVIA</t>
+          <t>Youth, Bed, OLIVIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26131,7 +28996,22 @@
       </c>
       <c r="AD192" t="inlineStr">
         <is>
-          <t>Youth, Bed, OLIVIA</t>
+          <t>Youth, Bed, OLIVIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26259,7 +29139,22 @@
       </c>
       <c r="AD193" t="inlineStr">
         <is>
-          <t>Youth, Bed, ONTARIO</t>
+          <t>Youth, Bed, ONTARIO, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26377,7 +29272,22 @@
       </c>
       <c r="AD194" t="inlineStr">
         <is>
-          <t>Youth, Bed, OVERLANDER</t>
+          <t>Youth, Bed, OVERLANDER, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26495,7 +29405,22 @@
       </c>
       <c r="AD195" t="inlineStr">
         <is>
-          <t>Youth, Bed, PACEFINDER</t>
+          <t>Youth, Bed, PACEFINDER, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26623,7 +29548,22 @@
       </c>
       <c r="AD196" t="inlineStr">
         <is>
-          <t>Youth, Bed, PATROLENE</t>
+          <t>Youth, Bed, PATROLENE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26751,7 +29691,22 @@
       </c>
       <c r="AD197" t="inlineStr">
         <is>
-          <t>Youth, Bed, PEARL</t>
+          <t>Youth, Bed, PEARL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26879,7 +29834,22 @@
       </c>
       <c r="AD198" t="inlineStr">
         <is>
-          <t>Youth, Bed, PEARL</t>
+          <t>Youth, Bed, PEARL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -27007,7 +29977,22 @@
       </c>
       <c r="AD199" t="inlineStr">
         <is>
-          <t>Youth, Bed, PEARL</t>
+          <t>Youth, Bed, PEARL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -27140,7 +30125,22 @@
       </c>
       <c r="AD200" t="inlineStr">
         <is>
-          <t>Youth, Bed, POE</t>
+          <t>Youth, Bed, POE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -27268,7 +30268,22 @@
       </c>
       <c r="AD201" t="inlineStr">
         <is>
-          <t>Youth, Bed, POSEIDON</t>
+          <t>Youth, Bed, POSEIDON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -27396,7 +30411,22 @@
       </c>
       <c r="AD202" t="inlineStr">
         <is>
-          <t>Youth, Bed, POSEIDON</t>
+          <t>Youth, Bed, POSEIDON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -27524,7 +30554,22 @@
       </c>
       <c r="AD203" t="inlineStr">
         <is>
-          <t>Youth, Bed, PRETTY GIRL CAR BED</t>
+          <t>Youth, Bed, PRETTY GIRL CAR BED, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -27654,7 +30699,22 @@
       </c>
       <c r="AD204" t="inlineStr">
         <is>
-          <t>Youth, Bed, PRIAM</t>
+          <t>Youth, Bed, PRIAM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -27784,7 +30844,22 @@
       </c>
       <c r="AD205" t="inlineStr">
         <is>
-          <t>Youth, Bed, PRIAM</t>
+          <t>Youth, Bed, PRIAM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -27912,7 +30987,22 @@
       </c>
       <c r="AD206" t="inlineStr">
         <is>
-          <t>Youth, Bed, PRINCESS CROWN SINGLE BED</t>
+          <t>Youth, Bed, PRINCESS CROWN SINGLE BED, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -28040,7 +31130,22 @@
       </c>
       <c r="AD207" t="inlineStr">
         <is>
-          <t>Youth, Bed, PUMPKIN CARRIAGE BED</t>
+          <t>Youth, Bed, PUMPKIN CARRIAGE BED, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -28168,7 +31273,22 @@
       </c>
       <c r="AD208" t="inlineStr">
         <is>
-          <t>Youth, Bed, RESCUER</t>
+          <t>Youth, Bed, RESCUER, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -28296,7 +31416,22 @@
       </c>
       <c r="AD209" t="inlineStr">
         <is>
-          <t>Youth, Bed, RICHLAND</t>
+          <t>Youth, Bed, RICHLAND, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -28424,7 +31559,22 @@
       </c>
       <c r="AD210" t="inlineStr">
         <is>
-          <t>Youth, Bed, RICHLAND</t>
+          <t>Youth, Bed, RICHLAND, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -28542,7 +31692,22 @@
       </c>
       <c r="AD211" t="inlineStr">
         <is>
-          <t>Youth, Bed, ROADSTAR</t>
+          <t>Youth, Bed, ROADSTAR, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -28673,7 +31838,22 @@
       </c>
       <c r="AD212" t="inlineStr">
         <is>
-          <t>Youth, Bed, ROANNE</t>
+          <t>Youth, Bed, ROANNE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -28804,7 +31984,22 @@
       </c>
       <c r="AD213" t="inlineStr">
         <is>
-          <t>Youth, Bed, ROANNE</t>
+          <t>Youth, Bed, ROANNE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -28932,7 +32127,22 @@
       </c>
       <c r="AD214" t="inlineStr">
         <is>
-          <t>Youth, Bed, SPEED JUMP BLACK</t>
+          <t>Youth, Bed, SPEED JUMP BLACK, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -29060,7 +32270,22 @@
       </c>
       <c r="AD215" t="inlineStr">
         <is>
-          <t>Youth, Bed, STUTSMAN</t>
+          <t>Youth, Bed, STUTSMAN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -29190,7 +32415,22 @@
       </c>
       <c r="AD216" t="inlineStr">
         <is>
-          <t>Youth, Bed, TIBALT</t>
+          <t>Youth, Bed, TIBALT, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -29320,7 +32560,22 @@
       </c>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>Youth, Bed, TIBALT</t>
+          <t>Youth, Bed, TIBALT, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -29444,7 +32699,22 @@
       </c>
       <c r="AD218" t="inlineStr">
         <is>
-          <t>Youth, Bed, TRACKLITE</t>
+          <t>Youth, Bed, TRACKLITE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -29568,7 +32838,22 @@
       </c>
       <c r="AD219" t="inlineStr">
         <is>
-          <t>Youth, Bed, TRACKLITE</t>
+          <t>Youth, Bed, TRACKLITE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -29700,7 +32985,22 @@
       </c>
       <c r="AD220" t="inlineStr">
         <is>
-          <t>Youth, Bed, TRACKSTER</t>
+          <t>Youth, Bed, TRACKSTER, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -29832,7 +33132,22 @@
       </c>
       <c r="AD221" t="inlineStr">
         <is>
-          <t>Youth, Bed, TRACKSTER</t>
+          <t>Youth, Bed, TRACKSTER, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -29964,7 +33279,22 @@
       </c>
       <c r="AD222" t="inlineStr">
         <is>
-          <t>Youth, Bed, TRACKSTER</t>
+          <t>Youth, Bed, TRACKSTER, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -30096,7 +33426,22 @@
       </c>
       <c r="AD223" t="inlineStr">
         <is>
-          <t>Youth, Bed, TRACKSTER</t>
+          <t>Youth, Bed, TRACKSTER, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -30225,7 +33570,22 @@
       </c>
       <c r="AD224" t="inlineStr">
         <is>
-          <t>Youth, Bed, TROUTDALE</t>
+          <t>Youth, Bed, TROUTDALE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -30356,7 +33716,22 @@
       </c>
       <c r="AD225" t="inlineStr">
         <is>
-          <t>Youth, Bed, VEVEY</t>
+          <t>Youth, Bed, VEVEY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -30487,7 +33862,22 @@
       </c>
       <c r="AD226" t="inlineStr">
         <is>
-          <t>Youth, Bed, VEVEY</t>
+          <t>Youth, Bed, VEVEY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -30615,7 +34005,22 @@
       </c>
       <c r="AD227" t="inlineStr">
         <is>
-          <t>Youth, Bed, WITHAM</t>
+          <t>Youth, Bed, WITHAM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -30743,7 +34148,22 @@
       </c>
       <c r="AD228" t="inlineStr">
         <is>
-          <t>Youth, Bed, WITHAM</t>
+          <t>Youth, Bed, WITHAM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -30875,7 +34295,22 @@
       </c>
       <c r="AD229" t="inlineStr">
         <is>
-          <t>Youth, Bed, ZOHAR</t>
+          <t>Youth, Bed, ZOHAR, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -31007,7 +34442,22 @@
       </c>
       <c r="AD230" t="inlineStr">
         <is>
-          <t>Youth, Bed, ZOHAR</t>
+          <t>Youth, Bed, ZOHAR, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -31139,7 +34589,22 @@
       </c>
       <c r="AD231" t="inlineStr">
         <is>
-          <t>Youth, Bed, ZOHAR</t>
+          <t>Youth, Bed, ZOHAR, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -31267,7 +34732,22 @@
       </c>
       <c r="AD232" t="inlineStr">
         <is>
-          <t>Youth, Chest, ALECIA</t>
+          <t>Youth, Chest, ALECIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -31399,7 +34879,22 @@
       </c>
       <c r="AD233" t="inlineStr">
         <is>
-          <t>Youth, Chest, ALLIE</t>
+          <t>Youth, Chest, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -31531,7 +35026,22 @@
       </c>
       <c r="AD234" t="inlineStr">
         <is>
-          <t>Youth, Chest, ALLIE</t>
+          <t>Youth, Chest, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -31659,7 +35169,22 @@
       </c>
       <c r="AD235" t="inlineStr">
         <is>
-          <t>Youth, Chest, ARISTON</t>
+          <t>Youth, Chest, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -31787,7 +35312,22 @@
       </c>
       <c r="AD236" t="inlineStr">
         <is>
-          <t>Youth, Chest, ARISTON</t>
+          <t>Youth, Chest, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -31915,7 +35455,22 @@
       </c>
       <c r="AD237" t="inlineStr">
         <is>
-          <t>Youth, Chest, BELVA</t>
+          <t>Youth, Chest, BELVA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -32046,7 +35601,22 @@
       </c>
       <c r="AD238" t="inlineStr">
         <is>
-          <t>Youth, Chest, CORRY</t>
+          <t>Youth, Chest, CORRY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -32177,7 +35747,22 @@
       </c>
       <c r="AD239" t="inlineStr">
         <is>
-          <t>Youth, Chest, CORRY</t>
+          <t>Youth, Chest, CORRY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -32305,7 +35890,22 @@
       </c>
       <c r="AD240" t="inlineStr">
         <is>
-          <t>Youth, Chest, DANI</t>
+          <t>Youth, Chest, DANI, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG240" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -32433,7 +36033,22 @@
       </c>
       <c r="AD241" t="inlineStr">
         <is>
-          <t>Youth, Chest, DIANE</t>
+          <t>Youth, Chest, DIANE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -32559,7 +36174,22 @@
       </c>
       <c r="AD242" t="inlineStr">
         <is>
-          <t>Youth, Chest, FANTON</t>
+          <t>Youth, Chest, FANTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -32685,7 +36315,22 @@
       </c>
       <c r="AD243" t="inlineStr">
         <is>
-          <t>Youth, Chest, GRIFFIN</t>
+          <t>Youth, Chest, GRIFFIN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -32811,7 +36456,22 @@
       </c>
       <c r="AD244" t="inlineStr">
         <is>
-          <t>Youth, Chest, LAREINA</t>
+          <t>Youth, Chest, LAREINA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -32945,7 +36605,22 @@
       </c>
       <c r="AD245" t="inlineStr">
         <is>
-          <t>Youth, Chest, LYCORIDA</t>
+          <t>Youth, Chest, LYCORIDA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -33073,7 +36748,22 @@
       </c>
       <c r="AD246" t="inlineStr">
         <is>
-          <t>Youth, Chest, LYCORIS</t>
+          <t>Youth, Chest, LYCORIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -33202,7 +36892,22 @@
       </c>
       <c r="AD247" t="inlineStr">
         <is>
-          <t>Youth, Chest, MARLEE</t>
+          <t>Youth, Chest, MARLEE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -33330,7 +37035,22 @@
       </c>
       <c r="AD248" t="inlineStr">
         <is>
-          <t>Youth, Chest, OLIVIA</t>
+          <t>Youth, Chest, OLIVIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -33458,7 +37178,22 @@
       </c>
       <c r="AD249" t="inlineStr">
         <is>
-          <t>Youth, Chest, OMNUS</t>
+          <t>Youth, Chest, OMNUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -33597,7 +37332,22 @@
       </c>
       <c r="AD250" t="inlineStr">
         <is>
-          <t>Youth, Chest, OMNUS</t>
+          <t>Youth, Chest, OMNUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -33725,7 +37475,22 @@
       </c>
       <c r="AD251" t="inlineStr">
         <is>
-          <t>Youth, Chest, OMNUS</t>
+          <t>Youth, Chest, OMNUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -33854,7 +37619,22 @@
       </c>
       <c r="AD252" t="inlineStr">
         <is>
-          <t>Youth, Chest, PRIAM</t>
+          <t>Youth, Chest, PRIAM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -33982,7 +37762,22 @@
       </c>
       <c r="AD253" t="inlineStr">
         <is>
-          <t>Youth, Chest, ROANNE</t>
+          <t>Youth, Chest, ROANNE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -34113,7 +37908,22 @@
       </c>
       <c r="AD254" t="inlineStr">
         <is>
-          <t>Youth, Chest, STAVROS</t>
+          <t>Youth, Chest, STAVROS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -34244,7 +38054,22 @@
       </c>
       <c r="AD255" t="inlineStr">
         <is>
-          <t>Youth, Chest, STAVROS</t>
+          <t>Youth, Chest, STAVROS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -34375,7 +38200,22 @@
       </c>
       <c r="AD256" t="inlineStr">
         <is>
-          <t>Youth, Chest, STAVROS</t>
+          <t>Youth, Chest, STAVROS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -34503,7 +38343,22 @@
       </c>
       <c r="AD257" t="inlineStr">
         <is>
-          <t>Youth, Chest, VEVEY</t>
+          <t>Youth, Chest, VEVEY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -34633,7 +38488,22 @@
       </c>
       <c r="AD258" t="inlineStr">
         <is>
-          <t>Youth, Chest, ZOHAR</t>
+          <t>Youth, Chest, ZOHAR, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -34761,7 +38631,22 @@
       </c>
       <c r="AD259" t="inlineStr">
         <is>
-          <t>Youth, Dresser, ALECIA</t>
+          <t>Youth, Dresser, ALECIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF259" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -34893,7 +38778,22 @@
       </c>
       <c r="AD260" t="inlineStr">
         <is>
-          <t>Youth, Dresser, ALLIE</t>
+          <t>Youth, Dresser, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF260" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -35025,7 +38925,22 @@
       </c>
       <c r="AD261" t="inlineStr">
         <is>
-          <t>Youth, Dresser, ALLIE</t>
+          <t>Youth, Dresser, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -35153,7 +39068,22 @@
       </c>
       <c r="AD262" t="inlineStr">
         <is>
-          <t>Youth, Dresser, ARISTON</t>
+          <t>Youth, Dresser, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -35281,7 +39211,22 @@
       </c>
       <c r="AD263" t="inlineStr">
         <is>
-          <t>Youth, Dresser, BELVA</t>
+          <t>Youth, Dresser, BELVA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -35412,7 +39357,22 @@
       </c>
       <c r="AD264" t="inlineStr">
         <is>
-          <t>Youth, Dresser, CORRY</t>
+          <t>Youth, Dresser, CORRY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -35543,7 +39503,22 @@
       </c>
       <c r="AD265" t="inlineStr">
         <is>
-          <t>Youth, Dresser, CORRY</t>
+          <t>Youth, Dresser, CORRY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -35671,7 +39646,22 @@
       </c>
       <c r="AD266" t="inlineStr">
         <is>
-          <t>Youth, Dresser, DANI</t>
+          <t>Youth, Dresser, DANI, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -35799,7 +39789,22 @@
       </c>
       <c r="AD267" t="inlineStr">
         <is>
-          <t>Youth, Dresser, DIANE</t>
+          <t>Youth, Dresser, DIANE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -35925,7 +39930,22 @@
       </c>
       <c r="AD268" t="inlineStr">
         <is>
-          <t>Youth, Dresser, FANTON</t>
+          <t>Youth, Dresser, FANTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF268" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -36051,7 +40071,22 @@
       </c>
       <c r="AD269" t="inlineStr">
         <is>
-          <t>Youth, Dresser, GRIFFIN</t>
+          <t>Youth, Dresser, GRIFFIN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -36178,7 +40213,22 @@
       </c>
       <c r="AD270" t="inlineStr">
         <is>
-          <t>Youth, Dresser, LAREINA</t>
+          <t>Youth, Dresser, LAREINA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -36312,7 +40362,22 @@
       </c>
       <c r="AD271" t="inlineStr">
         <is>
-          <t>Youth, Dresser, LYCORIDA</t>
+          <t>Youth, Dresser, LYCORIDA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -36440,7 +40505,22 @@
       </c>
       <c r="AD272" t="inlineStr">
         <is>
-          <t>Youth, Dresser, LYCORIS</t>
+          <t>Youth, Dresser, LYCORIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -36569,7 +40649,22 @@
       </c>
       <c r="AD273" t="inlineStr">
         <is>
-          <t>Youth, Dresser, MARLEE</t>
+          <t>Youth, Dresser, MARLEE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -36697,7 +40792,22 @@
       </c>
       <c r="AD274" t="inlineStr">
         <is>
-          <t>Youth, Dresser, OLIVIA</t>
+          <t>Youth, Dresser, OLIVIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -36825,7 +40935,22 @@
       </c>
       <c r="AD275" t="inlineStr">
         <is>
-          <t>Youth, Dresser, OMNUS</t>
+          <t>Youth, Dresser, OMNUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -36954,7 +41079,22 @@
       </c>
       <c r="AD276" t="inlineStr">
         <is>
-          <t>Youth, Dresser, PRIAM</t>
+          <t>Youth, Dresser, PRIAM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -37082,7 +41222,22 @@
       </c>
       <c r="AD277" t="inlineStr">
         <is>
-          <t>Youth, Dresser, ROANNE</t>
+          <t>Youth, Dresser, ROANNE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -37213,7 +41368,22 @@
       </c>
       <c r="AD278" t="inlineStr">
         <is>
-          <t>Youth, Dresser, STAVROS</t>
+          <t>Youth, Dresser, STAVROS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE278" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF278" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG278" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -37344,7 +41514,22 @@
       </c>
       <c r="AD279" t="inlineStr">
         <is>
-          <t>Youth, Dresser, STAVROS</t>
+          <t>Youth, Dresser, STAVROS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -37475,7 +41660,22 @@
       </c>
       <c r="AD280" t="inlineStr">
         <is>
-          <t>Youth, Dresser, STAVROS</t>
+          <t>Youth, Dresser, STAVROS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -37603,7 +41803,22 @@
       </c>
       <c r="AD281" t="inlineStr">
         <is>
-          <t>Youth, Dresser, VEVEY</t>
+          <t>Youth, Dresser, VEVEY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -37733,7 +41948,22 @@
       </c>
       <c r="AD282" t="inlineStr">
         <is>
-          <t>Youth, Dresser, ZOHAR</t>
+          <t>Youth, Dresser, ZOHAR, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF282" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Dressers</t>
         </is>
       </c>
     </row>
@@ -37862,7 +42092,22 @@
       </c>
       <c r="AD283" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, ALECIA</t>
+          <t>Youth, Night Stand, ALECIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -37994,7 +42239,22 @@
       </c>
       <c r="AD284" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, ALLIE</t>
+          <t>Youth, Night Stand, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF284" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -38126,7 +42386,22 @@
       </c>
       <c r="AD285" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, ALLIE</t>
+          <t>Youth, Night Stand, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF285" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG285" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -38254,7 +42529,22 @@
       </c>
       <c r="AD286" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, ARISTON</t>
+          <t>Youth, Night Stand, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF286" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -38383,7 +42673,22 @@
       </c>
       <c r="AD287" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, BELVA</t>
+          <t>Youth, Night Stand, BELVA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF287" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG287" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -38511,7 +42816,22 @@
       </c>
       <c r="AD288" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, CARA</t>
+          <t>Youth, Night Stand, CARA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -38642,7 +42962,22 @@
       </c>
       <c r="AD289" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, CORRY</t>
+          <t>Youth, Night Stand, CORRY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE289" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF289" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG289" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -38773,7 +43108,22 @@
       </c>
       <c r="AD290" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, CORRY</t>
+          <t>Youth, Night Stand, CORRY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF290" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG290" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -38901,7 +43251,22 @@
       </c>
       <c r="AD291" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, DANI</t>
+          <t>Youth, Night Stand, DANI, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF291" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG291" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -39029,7 +43394,22 @@
       </c>
       <c r="AD292" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, DIANE</t>
+          <t>Youth, Night Stand, DIANE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE292" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF292" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG292" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -39155,7 +43535,22 @@
       </c>
       <c r="AD293" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, FANTON</t>
+          <t>Youth, Night Stand, FANTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE293" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF293" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG293" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -39281,7 +43676,22 @@
       </c>
       <c r="AD294" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, GRIFFIN</t>
+          <t>Youth, Night Stand, GRIFFIN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE294" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF294" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG294" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -39415,7 +43825,22 @@
       </c>
       <c r="AD295" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, LYCORIDA</t>
+          <t>Youth, Night Stand, LYCORIDA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE295" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF295" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG295" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -39543,7 +43968,22 @@
       </c>
       <c r="AD296" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, LYCORIS</t>
+          <t>Youth, Night Stand, LYCORIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE296" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF296" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG296" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -39672,7 +44112,22 @@
       </c>
       <c r="AD297" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, MARLEE</t>
+          <t>Youth, Night Stand, MARLEE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE297" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF297" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG297" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -39804,7 +44259,22 @@
       </c>
       <c r="AD298" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, NIGHTSTAND - ASSEMBLED</t>
+          <t>Youth, Night Stand, NIGHTSTAND - ASSEMBLED, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE298" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF298" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG298" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -39932,7 +44402,22 @@
       </c>
       <c r="AD299" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, OLIVIA</t>
+          <t>Youth, Night Stand, OLIVIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE299" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF299" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG299" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -40061,7 +44546,22 @@
       </c>
       <c r="AD300" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, PRIAM</t>
+          <t>Youth, Night Stand, PRIAM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF300" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -40189,7 +44689,22 @@
       </c>
       <c r="AD301" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, ROANNE</t>
+          <t>Youth, Night Stand, ROANNE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE301" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF301" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG301" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -40320,7 +44835,22 @@
       </c>
       <c r="AD302" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, STAVROS</t>
+          <t>Youth, Night Stand, STAVROS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE302" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF302" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG302" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -40451,7 +44981,22 @@
       </c>
       <c r="AD303" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, STAVROS</t>
+          <t>Youth, Night Stand, STAVROS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE303" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF303" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG303" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -40582,7 +45127,22 @@
       </c>
       <c r="AD304" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, STAVROS</t>
+          <t>Youth, Night Stand, STAVROS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE304" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF304" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG304" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -40710,7 +45270,22 @@
       </c>
       <c r="AD305" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, VEVEY</t>
+          <t>Youth, Night Stand, VEVEY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE305" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF305" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG305" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -40840,7 +45415,22 @@
       </c>
       <c r="AD306" t="inlineStr">
         <is>
-          <t>Youth, Night Stand, ZOHAR</t>
+          <t>Youth, Night Stand, ZOHAR, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE306" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF306" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG306" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -40968,7 +45558,22 @@
       </c>
       <c r="AD307" t="inlineStr">
         <is>
-          <t>Youth, Accessory, ALLIE</t>
+          <t>Youth, Accessory, ALLIE, HOME DECOR &amp; ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="AE307" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF307" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG307" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture Accessories &gt; Outdoor Furniture Covers</t>
         </is>
       </c>
     </row>
@@ -41096,7 +45701,22 @@
       </c>
       <c r="AD308" t="inlineStr">
         <is>
-          <t>Youth, Accessory, DANI</t>
+          <t>Youth, Accessory, DANI, HOME DECOR &amp; ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="AE308" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF308" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG308" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture Accessories &gt; Outdoor Furniture Covers</t>
         </is>
       </c>
     </row>
@@ -41224,7 +45844,22 @@
       </c>
       <c r="AD309" t="inlineStr">
         <is>
-          <t>Youth, Accessory, DIANE</t>
+          <t>Youth, Accessory, DIANE, HOME DECOR &amp; ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="AE309" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF309" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG309" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture Accessories &gt; Outdoor Furniture Covers</t>
         </is>
       </c>
     </row>
@@ -41352,7 +45987,22 @@
       </c>
       <c r="AD310" t="inlineStr">
         <is>
-          <t>Youth, Accessory, GRANO</t>
+          <t>Youth, Accessory, GRANO, HOME DECOR &amp; ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="AE310" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF310" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG310" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture Accessories &gt; Outdoor Furniture Covers</t>
         </is>
       </c>
     </row>
@@ -41487,7 +46137,22 @@
       </c>
       <c r="AD311" t="inlineStr">
         <is>
-          <t>Youth, Accessory, HOOPLE</t>
+          <t>Youth, Accessory, HOOPLE, HOME DECOR &amp; ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="AE311" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF311" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG311" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture Accessories &gt; Outdoor Furniture Covers</t>
         </is>
       </c>
     </row>
@@ -41622,7 +46287,22 @@
       </c>
       <c r="AD312" t="inlineStr">
         <is>
-          <t>Youth, Accessory, HOOPLE</t>
+          <t>Youth, Accessory, HOOPLE, HOME DECOR &amp; ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="AE312" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF312" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG312" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture Accessories &gt; Outdoor Furniture Covers</t>
         </is>
       </c>
     </row>
@@ -41750,7 +46430,22 @@
       </c>
       <c r="AD313" t="inlineStr">
         <is>
-          <t>Youth, Accessory, OLIVIA</t>
+          <t>Youth, Accessory, OLIVIA, HOME DECOR &amp; ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="AE313" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF313" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG313" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture Accessories &gt; Outdoor Furniture Covers</t>
         </is>
       </c>
     </row>
@@ -41881,7 +46576,22 @@
       </c>
       <c r="AD314" t="inlineStr">
         <is>
-          <t>Youth, Accessory, OMNUS</t>
+          <t>Youth, Accessory, OMNUS, HOME DECOR &amp; ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="AE314" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF314" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG314" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture Accessories &gt; Outdoor Furniture Covers</t>
         </is>
       </c>
     </row>
@@ -42014,7 +46724,22 @@
       </c>
       <c r="AD315" t="inlineStr">
         <is>
-          <t>Youth, Accessory, ROANNE</t>
+          <t>Youth, Accessory, ROANNE, HOME DECOR &amp; ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF315" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture Accessories &gt; Outdoor Furniture Covers</t>
         </is>
       </c>
     </row>
@@ -42142,7 +46867,22 @@
       </c>
       <c r="AD316" t="inlineStr">
         <is>
-          <t>Youth, Accessory, VEVEY</t>
+          <t>Youth, Accessory, VEVEY, HOME DECOR &amp; ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="AE316" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF316" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG316" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture Accessories &gt; Outdoor Furniture Covers</t>
         </is>
       </c>
     </row>
@@ -42270,7 +47010,22 @@
       </c>
       <c r="AD317" t="inlineStr">
         <is>
-          <t>Youth, Trundle, ALLIE</t>
+          <t>Youth, Trundle, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF317" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Trundle Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -42396,7 +47151,22 @@
       </c>
       <c r="AD318" t="inlineStr">
         <is>
-          <t>Youth, Trundle, IVANA</t>
+          <t>Youth, Trundle, IVANA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF318" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Trundle Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -42531,7 +47301,22 @@
       </c>
       <c r="AD319" t="inlineStr">
         <is>
-          <t>Youth, Trundle, OMNUS</t>
+          <t>Youth, Trundle, OMNUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF319" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Trundle Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -42662,7 +47447,22 @@
       </c>
       <c r="AD320" t="inlineStr">
         <is>
-          <t>Youth, Trundle, OMNUS</t>
+          <t>Youth, Trundle, OMNUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF320" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Trundle Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -42797,7 +47597,22 @@
       </c>
       <c r="AD321" t="inlineStr">
         <is>
-          <t>Youth, Trundle, OMNUS</t>
+          <t>Youth, Trundle, OMNUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF321" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Trundle Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -42928,7 +47743,22 @@
       </c>
       <c r="AD322" t="inlineStr">
         <is>
-          <t>Youth, Trundle, OMNUS</t>
+          <t>Youth, Trundle, OMNUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE322" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF322" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG322" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Trundle Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -43059,7 +47889,22 @@
       </c>
       <c r="AD323" t="inlineStr">
         <is>
-          <t>Youth, Trundle, OMNUS</t>
+          <t>Youth, Trundle, OMNUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE323" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF323" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG323" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Trundle Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -43187,7 +48032,22 @@
       </c>
       <c r="AD324" t="inlineStr">
         <is>
-          <t>Youth, Trundle, PRIAM</t>
+          <t>Youth, Trundle, PRIAM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE324" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF324" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames &gt; Trundle Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -43315,7 +48175,22 @@
       </c>
       <c r="AD325" t="inlineStr">
         <is>
-          <t>Youth, Armoire, DANI</t>
+          <t>Youth, Armoire, DANI, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE325" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF325" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG325" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Armoires &amp; Wardrobes</t>
         </is>
       </c>
     </row>
@@ -43443,7 +48318,22 @@
       </c>
       <c r="AD326" t="inlineStr">
         <is>
-          <t>Youth, Armoire, VEVEY</t>
+          <t>Youth, Armoire, VEVEY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE326" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF326" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG326" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage &gt; Armoires &amp; Wardrobes</t>
         </is>
       </c>
     </row>
@@ -43465,7 +48355,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Nightstand</t>
+          <t>Night Stand</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -43569,7 +48459,22 @@
       </c>
       <c r="AD327" t="inlineStr">
         <is>
-          <t>Youth, Nightstand, LAREINA</t>
+          <t>Youth, Night Stand, LAREINA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE327" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF327" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Nightstands</t>
         </is>
       </c>
     </row>
@@ -43703,7 +48608,22 @@
       </c>
       <c r="AD328" t="inlineStr">
         <is>
-          <t>Youth, Day Bed, MARINOS</t>
+          <t>Youth, Day Bed, MARINOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE328" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF328" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG328" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Daybeds</t>
         </is>
       </c>
     </row>
@@ -43837,7 +48757,22 @@
       </c>
       <c r="AD329" t="inlineStr">
         <is>
-          <t>Youth, Day Bed, MARINOS</t>
+          <t>Youth, Day Bed, MARINOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE329" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF329" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Daybeds</t>
         </is>
       </c>
     </row>
@@ -43968,7 +48903,22 @@
       </c>
       <c r="AD330" t="inlineStr">
         <is>
-          <t>Youth, Desk, OMNUS</t>
+          <t>Youth, Desk, OMNUS, OFFICE FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE330" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF330" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Office Furniture &gt; Desks</t>
         </is>
       </c>
     </row>
@@ -44099,7 +49049,22 @@
       </c>
       <c r="AD331" t="inlineStr">
         <is>
-          <t>Youth, Desk, OMNUS</t>
+          <t>Youth, Desk, OMNUS, OFFICE FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE331" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF331" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Office Furniture &gt; Desks</t>
         </is>
       </c>
     </row>
@@ -44230,7 +49195,22 @@
       </c>
       <c r="AD332" t="inlineStr">
         <is>
-          <t>Youth, Desk, OMNUS</t>
+          <t>Youth, Desk, OMNUS, OFFICE FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE332" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF332" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Office Furniture &gt; Desks</t>
         </is>
       </c>
     </row>
@@ -44361,7 +49341,22 @@
       </c>
       <c r="AD333" t="inlineStr">
         <is>
-          <t>Youth, Desk, OMNUS</t>
+          <t>Youth, Desk, OMNUS, OFFICE FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE333" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF333" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Office Furniture &gt; Desks</t>
         </is>
       </c>
     </row>
@@ -44492,7 +49487,22 @@
       </c>
       <c r="AD334" t="inlineStr">
         <is>
-          <t>Youth, Desk, OMNUS</t>
+          <t>Youth, Desk, OMNUS, OFFICE FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE334" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF334" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG334" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Office Furniture &gt; Desks</t>
         </is>
       </c>
     </row>
@@ -44623,7 +49633,22 @@
       </c>
       <c r="AD335" t="inlineStr">
         <is>
-          <t>Youth, Desk, OMNUS</t>
+          <t>Youth, Desk, OMNUS, OFFICE FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE335" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF335" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Office Furniture &gt; Desks</t>
         </is>
       </c>
     </row>
@@ -44751,7 +49776,22 @@
       </c>
       <c r="AD336" t="inlineStr">
         <is>
-          <t>Youth, Shelf/Storage, OMNUS</t>
+          <t>Youth, Shelf/Storage, OMNUS, OFFICE FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE336" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF336" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG336" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage</t>
         </is>
       </c>
     </row>

--- a/FOA Singles/Youth-Single.xlsx
+++ b/FOA Singles/Youth-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1437,7 +1437,7 @@
 Product Dimensions: 60"W X 81"D X 68"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
+Color: Dark Walnut or Gray or Dark Cherry or White&lt;br&gt;
 Weight: 191.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1580,11 +1580,11 @@
       <c r="G7" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with BROOKINGS or Full Bunk Bed and its Transitional character. As a youth bunk bed, it is designed to complement your space. Finished in Gray tones, the Solid Hardwood build balances durability with visual appeal.&lt;br&gt;
+BROOKINGS or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Hardwood, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 60"W X 81"D X 68"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Dark Walnut or Gray or Dark Cherry or White&lt;br&gt;
 Weight: 191.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1727,11 +1727,11 @@
       <c r="G8" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BROOKINGS or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Hardwood construction is complemented by Dark Cherry tones for a polished look.&lt;br&gt;
+BROOKINGS or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Hardwood, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 60"W X 81"D X 68"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
-Color: Dark Cherry&lt;br&gt;
+Color: Dark Walnut or Gray or Dark Cherry or White&lt;br&gt;
 Weight: 191.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1874,11 +1874,11 @@
       <c r="G9" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with BROOKINGS or Full Bunk Bed, styled in Transitional and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Hardwood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+BROOKINGS or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Hardwood, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 60"W X 81"D X 68"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Solid Hardwood.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Dark Walnut or Gray or Dark Cherry or White&lt;br&gt;
 Weight: 191.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2027,9 +2027,9 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Oak&lt;br&gt;
-Weight: 191.4 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Wire-Brushed White or Dark Walnut or Gray or White&lt;br&gt;
+Weight: 191.4 or 192.5 or 190.74 or 191.62 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H10" s="41" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -2171,15 +2171,15 @@
       <c r="G11" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CALIFORNIA III or Full Bunk Bed w/ 2 Drawers adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Wire-Brushed White tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with CALIFORNIA III or Full Bunk Bed w/ 2 Drawers, styled in Transitional and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 78 3/8"W X 56 1/2"D X 65"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Wire-Brushed White&lt;br&gt;
-Weight: 192.5 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Wire-Brushed White or Dark Walnut or Gray or White&lt;br&gt;
+Weight: 191.4 or 192.5 or 190.74 or 191.62 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H11" s="41" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -2321,15 +2321,15 @@
       <c r="G12" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with CALIFORNIA III or Full Bunk Bed w/ 2 Drawers and its Transitional character. As a youth bunk bed, it is designed to complement your space. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with CALIFORNIA III or Full Bunk Bed w/ 2 Drawers, styled in Transitional and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 78 3/8"W X 56 1/2"D X 65"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
-Weight: 190.74 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Wire-Brushed White or Dark Walnut or Gray or White&lt;br&gt;
+Weight: 191.4 or 192.5 or 190.74 or 191.62 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H12" s="41" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -2471,15 +2471,15 @@
       <c r="G13" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CALIFORNIA III or Full Bunk Bed w/ 2 Drawers brings a Transitional look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Elevate your space with CALIFORNIA III or Full Bunk Bed w/ 2 Drawers, styled in Transitional and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 78 3/8"W X 56 1/2"D X 65"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 191.4 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Wire-Brushed White or Dark Walnut or Gray or White&lt;br&gt;
+Weight: 191.4 or 192.5 or 190.74 or 191.62 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H13" s="41" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -2621,15 +2621,15 @@
       <c r="G14" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with CALIFORNIA III or Full Bunk Bed w/ 2 Drawers, styled in Transitional and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Elevate your space with CALIFORNIA III or Full Bunk Bed w/ 2 Drawers, styled in Transitional and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 78 3/8"W X 56 1/2"D X 65"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 191.62 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Wire-Brushed White or Dark Walnut or Gray or White&lt;br&gt;
+Weight: 191.4 or 192.5 or 190.74 or 191.62 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H14" s="41" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2922,9 +2922,9 @@
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 171.6 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Black or Dark Walnut or Gray or White&lt;br&gt;
+Weight: 171.6 or 171.5 or 172.7 or 175.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H16" s="43" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -3066,14 +3066,14 @@
       <c r="G17" s="43" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CALIFORNIA IV or Twin Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
+Make the room feel complete with CALIFORNIA IV or Twin Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 78 3/8"L X 41 5/8"W X 65"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
-Weight: 171.5 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Black or Dark Walnut or Gray or White&lt;br&gt;
+Weight: 171.6 or 171.5 or 172.7 or 175.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H17" s="43" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -3215,14 +3215,14 @@
       <c r="G18" s="43" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with CALIFORNIA IV or Twin Bunk Bed, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with CALIFORNIA IV or Twin Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 78 3/8"L X 41 5/8"W X 65"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 172.7 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Black or Dark Walnut or Gray or White&lt;br&gt;
+Weight: 171.6 or 171.5 or 172.7 or 175.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H18" s="43" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -3364,14 +3364,14 @@
       <c r="G19" s="43" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CALIFORNIA IV or Twin Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with CALIFORNIA IV or Twin Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 78 3/8"L X 41 5/8"W X 65"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Two Drawers Included&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 175.1 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Black or Dark Walnut or Gray or White&lt;br&gt;
+Weight: 171.6 or 171.5 or 172.7 or 175.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H19" s="43" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -3808,9 +3808,9 @@
 Size: Full&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
-Weight: 180.5 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or Gray or White&lt;br&gt;
+Weight: 180.5 or 183.84 or 185.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H22" s="45" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -3952,14 +3952,14 @@
       <c r="G23" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with CAMERON or Full Bunk Bed, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+CAMERON or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
 Product Dimensions: 81 3/8"W X 58"D X 60"H&lt;br&gt;
 Size: Full&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 183.84 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or Gray or White&lt;br&gt;
+Weight: 180.5 or 183.84 or 185.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H23" s="45" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -4101,14 +4101,14 @@
       <c r="G24" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CAMERON or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+CAMERON or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
 Product Dimensions: 81 3/8"W X 58"D X 60"H&lt;br&gt;
 Size: Full&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 185.8 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or Gray or White&lt;br&gt;
+Weight: 180.5 or 183.84 or 185.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H24" s="45" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -4251,13 +4251,13 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with CAMERON or Twin Bunk Bed and its Transitional character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 81 3/8"L X 42 3/8"W X 60"H&lt;br&gt;
+Product Dimensions: 81 3/8"L X 42 3/8"W X 60"H / 81 3/8"W X 58"D X 60"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
-Weight: 149.5 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or Gray or White&lt;br&gt;
+Weight: 149.5 or 147.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H25" s="47" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -4399,14 +4399,14 @@
       <c r="G26" s="47" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CAMERON or Twin Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Solid Wood, Wood Veneer, construction is complemented by Gray tones for a polished look.&lt;br&gt;
-Product Dimensions: 81 3/8"W X 58"D X 60"H&lt;br&gt;
+Make the room feel complete with CAMERON or Twin Bunk Bed and its Transitional character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 81 3/8"L X 42 3/8"W X 60"H / 81 3/8"W X 58"D X 60"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 149.5 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or Gray or White&lt;br&gt;
+Weight: 149.5 or 147.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H26" s="47" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -4548,14 +4548,14 @@
       <c r="G27" s="47" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with CAMERON or Twin Bunk Bed, styled in Transitional and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
-Product Dimensions: 81 3/8"L X 42 3/8"W X 60"H&lt;br&gt;
+Make the room feel complete with CAMERON or Twin Bunk Bed and its Transitional character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 81 3/8"L X 42 3/8"W X 60"H / 81 3/8"W X 58"D X 60"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 147.4 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or Gray or White&lt;br&gt;
+Weight: 149.5 or 147.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H27" s="47" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -4847,8 +4847,8 @@
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or White&lt;br&gt;
 Weight: 135.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -4993,13 +4993,13 @@
       <c r="G30" s="49" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with CANDICE or Twin Bunk Bed and its Transitional character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+CANDICE or Twin Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Solid Wood, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 78"W X 43"D X 59"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or White&lt;br&gt;
 Weight: 135.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -6604,7 +6604,7 @@
 Product Dimensions: 56"W X 77"D X 67"H&lt;br&gt;
 Size: Full&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Silver or White&lt;br&gt;
 Weight: 110.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -6747,11 +6747,11 @@
       <c r="G42" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with CYBILL Loft Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
+CYBILL Loft Bed brings a Contemporary look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 56"W X 77"D X 67"H&lt;br&gt;
 Size: Full&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Black or Silver or White&lt;br&gt;
 Weight: 110.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -6894,11 +6894,11 @@
       <c r="G43" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CYBILL Loft Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+CYBILL Loft Bed brings a Contemporary look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 56"W X 77"D X 67"H&lt;br&gt;
 Size: Full&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Black or Silver or White&lt;br&gt;
 Weight: 110.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -7046,8 +7046,8 @@
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or White&lt;br&gt;
 Weight: 194 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -7190,13 +7190,13 @@
       <c r="G45" s="27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-DAMARIS or Full Bunk Bed brings a Rustic look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Wood, construction is complemented by White tones for a polished look.&lt;br&gt;
+Make the room feel complete with DAMARIS or Full Bunk Bed and its Rustic character. As a youth bunk bed, it is designed to complement your space. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 78"W X 56"D X 61"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or White&lt;br&gt;
 Weight: 194 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -7345,8 +7345,8 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Built-In Drawers &amp;amp; Front Access Steps&lt;/p&gt;
 &lt;p&gt;Materials: Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
-Color: Espresso&lt;br&gt;
-Weight: 283.8 lbs&lt;/p&gt;</t>
+Color: Espresso or White&lt;br&gt;
+Weight: 283.8 or 272.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H46" s="54" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
@@ -7488,14 +7488,14 @@
       <c r="G47" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ELLINGTON or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, Engineered Wood construction is complemented by White tones for a polished look.&lt;br&gt;
+Make the room feel complete with ELLINGTON or Full Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Espresso tones, the Solid Wood, Wood Veneer, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 56.5"W X 99.5"D X 65"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Built-In Drawers &amp;amp; Front Access Steps&lt;/p&gt;
 &lt;p&gt;Materials: Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 272.2 lbs&lt;/p&gt;</t>
+Color: Espresso or White&lt;br&gt;
+Weight: 283.8 or 272.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H47" s="54" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -7643,8 +7643,8 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Built-In Drawers &amp;amp; Front Access Steps&lt;/p&gt;
 &lt;p&gt;Materials: Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
-Color: Espresso&lt;br&gt;
-Weight: 325.6 lbs&lt;/p&gt;</t>
+Color: Espresso or White&lt;br&gt;
+Weight: 325.6 or 316.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H48" s="56" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
@@ -7786,14 +7786,14 @@
       <c r="G49" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ELLINGTON or Full Bunk Bed and Trundle adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with ELLINGTON or Full Bunk Bed and Trundle, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, Wood Veneer, Engineered Wood and Espresso tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 56.5"W X 99.5"D X 65"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Built-In Drawers &amp;amp; Front Access Steps&lt;/p&gt;
 &lt;p&gt;Materials: Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 316.2 lbs&lt;/p&gt;</t>
+Color: Espresso or White&lt;br&gt;
+Weight: 325.6 or 316.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H49" s="56" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
@@ -7940,9 +7940,9 @@
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Underbed Drawers Included&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 197.2 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Black or Espresso or Gray or White&lt;br&gt;
+Weight: 197.2 or 196.9 or 194.7 or 192.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H50" s="39" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
@@ -8084,14 +8084,14 @@
       <c r="G51" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-EMILEE or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Solid Wood, it is finished in Espresso tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with EMILEE or Full Bunk Bed, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 79"W X 61"D X 65"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Underbed Drawers Included&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Espresso&lt;br&gt;
-Weight: 196.9 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Black or Espresso or Gray or White&lt;br&gt;
+Weight: 197.2 or 196.9 or 194.7 or 192.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H51" s="39" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -8237,14 +8237,14 @@
       <c r="G52" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with EMILEE or Full Bunk Bed and its Transitional character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with EMILEE or Full Bunk Bed, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 79"W X 61"D X 65"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Underbed Drawers Included&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 194.7 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Black or Espresso or Gray or White&lt;br&gt;
+Weight: 197.2 or 196.9 or 194.7 or 192.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H52" s="39" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
@@ -8386,14 +8386,14 @@
       <c r="G53" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-EMILEE or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Solid Wood, construction is complemented by White tones for a polished look.&lt;br&gt;
+Elevate your space with EMILEE or Full Bunk Bed, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 79"W X 61"D X 65"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Underbed Drawers Included&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 192.5 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Black or Espresso or Gray or White&lt;br&gt;
+Weight: 197.2 or 196.9 or 194.7 or 192.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H53" s="39" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -8539,7 +8539,7 @@
 Product Dimensions: 41.5"W X 78"D X 78"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Silver or White&lt;br&gt;
 Weight: 132 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
@@ -8682,11 +8682,11 @@
       <c r="G55" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FELGU Triple Metal Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Silver tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with FELGU Triple Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 41.5"W X 78"D X 78"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Black or Silver or White&lt;br&gt;
 Weight: 132 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -8829,11 +8829,11 @@
       <c r="G56" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with FELGU Triple Metal Bunk Bed and its Contemporary character. As a youth bunk bed, it is designed to complement your space. Finished in White tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with FELGU Triple Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 41.5"W X 78"D X 78"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Black or Silver or White&lt;br&gt;
 Weight: 132 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
@@ -8980,7 +8980,7 @@
 Product Dimensions: 57"W X 78.5"D X 59"H&lt;br&gt;
 Size: Full&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Silver&lt;br&gt;
 Weight: 125.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -9123,11 +9123,11 @@
       <c r="G58" s="43" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with FINNERTY or Full Bunk Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal and Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
+FINNERTY or Full Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 57"W X 78.5"D X 59"H&lt;br&gt;
 Size: Full&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Black or Silver&lt;br&gt;
 Weight: 125.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
@@ -9271,11 +9271,11 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 FINNERTY or Full Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 56"W X 79"D X 60.5"H&lt;br&gt;
+Product Dimensions: 56"W X 79"D X 60.5"H / 57"W X 78.5"D X 59"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 106.48 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 106.48 or 125.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H59" s="45" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -9417,12 +9417,12 @@
       <c r="G60" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with FINNERTY or Full Bunk Bed and its Contemporary character. Built as a youth bunk bed, it pairs well with a wide range of interiors. Finished in Silver tones, the Metal build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 56"W X 79"D X 60.5"H&lt;br&gt;
+FINNERTY or Full Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 56"W X 79"D X 60.5"H / 57"W X 78.5"D X 59"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Silver&lt;br&gt;
-Weight: 106.48 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 106.48 or 125.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H60" s="45" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
@@ -9564,12 +9564,12 @@
       <c r="G61" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FINNERTY or Full Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal construction is complemented by White tones for a polished look.&lt;br&gt;
-Product Dimensions: 57"W X 78.5"D X 59"H&lt;br&gt;
+FINNERTY or Full Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 56"W X 79"D X 60.5"H / 57"W X 78.5"D X 59"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 125.4 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 106.48 or 125.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H61" s="45" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -9711,12 +9711,12 @@
       <c r="G62" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with FINNERTY or Full Bunk Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
-Product Dimensions: 56"W X 79"D X 60.5"H&lt;br&gt;
+FINNERTY or Full Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 56"W X 79"D X 60.5"H / 57"W X 78.5"D X 59"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 106.48 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 106.48 or 125.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H62" s="45" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
@@ -9862,8 +9862,8 @@
 Product Dimensions: 79"W X 42.5"D X 65"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
-Color: Espresso&lt;br&gt;
-Weight: 136.68 lbs&lt;/p&gt;</t>
+Color: Espresso or Gray or White&lt;br&gt;
+Weight: 136.68 or 137.79 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H63" s="47" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -10007,12 +10007,12 @@
       <c r="G64" s="47" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with FINSBURY or Twin Bunk and its Transitional character. As a youth bunk bed, it is designed to complement your space. Finished in Gray tones, the Solid Hardwood, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+FINSBURY or Twin Bunk adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Hardwood, Engineered Wood, it is finished in Espresso tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 79"W X 42.5"D X 65"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 136.68 lbs&lt;/p&gt;</t>
+Color: Espresso or Gray or White&lt;br&gt;
+Weight: 136.68 or 137.79 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H64" s="47" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
@@ -10156,12 +10156,12 @@
       <c r="G65" s="47" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FINSBURY or Twin Bunk brings a Transitional look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Hardwood, Engineered Wood construction is complemented by White tones for a polished look.&lt;br&gt;
+FINSBURY or Twin Bunk adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Solid Hardwood, Engineered Wood, it is finished in Espresso tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 79"W X 42.5"D X 65"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 137.79 lbs&lt;/p&gt;</t>
+Color: Espresso or Gray or White&lt;br&gt;
+Weight: 136.68 or 137.79 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H65" s="47" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -10309,8 +10309,8 @@
 Product Dimensions: 41.5"W X 78"D X 61"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Other.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 72.6 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 72.6 or 77 or 75.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H66" s="49" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
@@ -10458,12 +10458,12 @@
       <c r="G67" s="49" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HECTOR or Twin Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal, Other construction is complemented by Silver tones for a polished look.&lt;br&gt;
+Make the room feel complete with HECTOR or Twin Metal Bunk Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Metal, Other build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 41.5"W X 78"D X 61"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Other.&lt;br&gt;
-Color: Silver&lt;br&gt;
-Weight: 77 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 72.6 or 77 or 75.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H67" s="49" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -10611,12 +10611,12 @@
       <c r="G68" s="49" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with HECTOR or Twin Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal, Other and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with HECTOR or Twin Metal Bunk Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Metal, Other build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 41.5"W X 78"D X 61"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Other.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 75.9 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 72.6 or 77 or 75.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H68" s="49" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
@@ -10770,9 +10770,9 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Foundation required&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 181.5 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or White&lt;br&gt;
+Weight: 181.5 or 190.27 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H69" s="32" t="inlineStr">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
@@ -10918,15 +10918,15 @@
       <c r="G70" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HOOPLE or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with HOOPLE or Full Bunk Bed, styled in Transitional and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Wood, and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 79 1/8"L X 59"W X 64"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Foundation required&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 190.27 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or White&lt;br&gt;
+Weight: 181.5 or 190.27 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H70" s="32" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
@@ -11077,9 +11077,9 @@
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Antique Gray&lt;br&gt;
-Weight: 227.7 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Antique Gray or Antique White&lt;br&gt;
+Weight: 227.7 or 238.67 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H71" s="60" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
@@ -11221,14 +11221,14 @@
       <c r="G72" s="60" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HOOPLE or full Bunk Bed W or Trundle brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, construction is complemented by Antique White tones for a polished look.&lt;br&gt;
+Make the room feel complete with HOOPLE or full Bunk Bed W or Trundle and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Antique Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 79 1/8"L X 59"W X 64"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Antique White&lt;br&gt;
-Weight: 238.67 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Antique Gray or Antique White&lt;br&gt;
+Weight: 227.7 or 238.67 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H72" s="60" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr">
@@ -12842,8 +12842,8 @@
 Product Dimensions: 41.5"W X 78"D X 61"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 64.9 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 64.9 or 66 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H83" s="51" t="inlineStr">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
@@ -12991,12 +12991,12 @@
       <c r="G84" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MYLES Loft Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by Silver tones for a polished look.&lt;br&gt;
+Make the room feel complete with MYLES Loft Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Metal build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 41.5"W X 78"D X 61"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Silver&lt;br&gt;
-Weight: 64.9 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 64.9 or 66 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H84" s="51" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr">
@@ -13144,12 +13144,12 @@
       <c r="G85" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with MYLES Loft Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with MYLES Loft Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Metal build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 41.5"W X 78"D X 61"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 66 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 64.9 or 66 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H85" s="51" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr">
@@ -13303,7 +13303,7 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
-Color: Oak or White&lt;br&gt;
+Color: Oak or White or Blue or White&lt;br&gt;
 Weight: 183 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13388,7 +13388,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr">
@@ -13446,13 +13446,13 @@
       <c r="G87" s="27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NAUTIA or Full Bunk Bed adds a Novelty touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Wood, Engineered Wood, it is finished in Blue or White tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with NAUTIA or Full Bunk Bed, styled in Novelty and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Wood, Engineered Wood and Oak or White tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 58"W X 78"D X 63"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
-Color: Blue or White&lt;br&gt;
+Color: Oak or White or Blue or White&lt;br&gt;
 Weight: 183 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13537,7 +13537,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
@@ -13601,7 +13601,7 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
-Color: Oak or White&lt;br&gt;
+Color: Oak or White or Blue or White&lt;br&gt;
 Weight: 227 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13686,7 +13686,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
@@ -13744,13 +13744,13 @@
       <c r="G89" s="34" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NAUTIA or Full Bunk Bed w/ Trundle brings a Novelty look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Engineered Wood construction is complemented by Blue or White tones for a polished look.&lt;br&gt;
+Make the room feel complete with NAUTIA or Full Bunk Bed w/ Trundle and its Novelty character. This youth bunk bed is made to fit naturally into the room. Finished in Oak or White tones, the Solid Wood, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 58"W X 78"D X 63"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
-Color: Blue or White&lt;br&gt;
+Color: Oak or White or Blue or White&lt;br&gt;
 Weight: 227 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13835,7 +13835,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr">
@@ -14264,7 +14264,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD92" t="inlineStr">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD94" t="inlineStr">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr">
@@ -14836,7 +14836,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr">
@@ -14979,7 +14979,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr">
@@ -15122,7 +15122,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr">
@@ -15331,7 +15331,7 @@
 Product Dimensions: 78 3/8"L X 41 3/4"W X 69 1/4"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Silver&lt;br&gt;
 Weight: 137.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr">
@@ -15476,11 +15476,11 @@
       <c r="G101" s="43" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-OPAL III Loft Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Silver tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with OPAL III Loft Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 78 3/8"L X 41 3/4"W X 69 1/4"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Black or Silver&lt;br&gt;
 Weight: 137.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
@@ -15629,7 +15629,7 @@
 Product Dimensions: 56.5"W X 78"D X 54"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Other.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Silver or White&lt;br&gt;
 Weight: 82.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -15720,7 +15720,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
@@ -15778,11 +15778,11 @@
       <c r="G103" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PANOS or Full Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal, Other construction is complemented by Silver tones for a polished look.&lt;br&gt;
+Make the room feel complete with PANOS or Full Metal Bunk Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Metal, Other build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 56.5"W X 78"D X 54"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Other.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Black or Silver or White&lt;br&gt;
 Weight: 82.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
@@ -15931,11 +15931,11 @@
       <c r="G104" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with PANOS or Full Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal, Other and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with PANOS or Full Metal Bunk Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Black tones, the Metal, Other build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 56.5"W X 78"D X 54"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Other.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Black or Silver or White&lt;br&gt;
 Weight: 82.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16026,7 +16026,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr">
@@ -16088,7 +16088,7 @@
 Product Dimensions: 41.5"W X 78"D X 65.5"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Silver or White&lt;br&gt;
 Weight: 100.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
@@ -16237,11 +16237,11 @@
       <c r="G106" s="47" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with PHILOTUS or Twin Bunk Bed and Trundle and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Silver tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+PHILOTUS or Twin Bunk Bed and Trundle adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 41.5"W X 78"D X 65.5"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Black or Silver or White&lt;br&gt;
 Weight: 100.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr">
@@ -16390,11 +16390,11 @@
       <c r="G107" s="47" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PHILOTUS or Twin Bunk Bed and Trundle brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by White tones for a polished look.&lt;br&gt;
+PHILOTUS or Twin Bunk Bed and Trundle adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 41.5"W X 78"D X 65.5"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Black or Silver or White&lt;br&gt;
 Weight: 100.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -16547,8 +16547,8 @@
 Product Dimensions: 41.5"W X 78"D X 65.5"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 77 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 77 or 75.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H108" s="49" t="inlineStr">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
@@ -16696,12 +16696,12 @@
       <c r="G109" s="49" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with PLUTUS or Twin Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Metal and Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
+PLUTUS or Twin Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 41.5"W X 78"D X 65.5"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Silver&lt;br&gt;
-Weight: 75.9 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 77 or 75.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H109" s="49" t="inlineStr">
@@ -16791,7 +16791,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr">
@@ -16849,12 +16849,12 @@
       <c r="G110" s="49" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PLUTUS or Twin Metal Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+PLUTUS or Twin Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 41.5"W X 78"D X 65.5"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 77 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 77 or 75.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H110" s="49" t="inlineStr">
@@ -16944,7 +16944,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr">
@@ -17006,7 +17006,7 @@
 Product Dimensions: 79"W X 42"D X 61"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Silver&lt;br&gt;
 Weight: 99 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17093,7 +17093,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr">
@@ -17151,11 +17151,11 @@
       <c r="G112" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with RAINBOW Metal or Twin Bunk Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Silver tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+RAINBOW Metal or Twin Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 79"W X 42"D X 61"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Black or Silver&lt;br&gt;
 Weight: 99 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17242,7 +17242,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr">
@@ -17304,7 +17304,7 @@
 Product Dimensions: 79"W X 42"D X 59 1/2"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Silver or White&lt;br&gt;
 Weight: 96.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr">
@@ -17449,11 +17449,11 @@
       <c r="G114" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with RAINBOW or Twin Bunk Bed, styled in Contemporary and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Metal and Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
+RAINBOW or Twin Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 79"W X 42"D X 59 1/2"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Black or Silver or White&lt;br&gt;
 Weight: 96.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr">
@@ -17598,11 +17598,11 @@
       <c r="G115" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-RAINBOW or Twin Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bunk bed is made to fit naturally into the room. Crafted from Metal, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+RAINBOW or Twin Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 79"W X 42"D X 59 1/2"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Black or Silver or White&lt;br&gt;
 Weight: 96.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr">
@@ -17751,8 +17751,8 @@
 Product Dimensions: 41.5"W X 78"D X 64"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Other.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 58.3 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 58.3 or 59.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H116" s="60" t="inlineStr">
@@ -17842,7 +17842,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
@@ -17900,12 +17900,12 @@
       <c r="G117" s="60" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with RHONDA Loft Bed and its Contemporary character. This youth bunk bed is made to fit naturally into the room. Finished in Silver tones, the Metal, Other build balances durability with visual appeal.&lt;br&gt;
+RHONDA Loft Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, Other, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 41.5"W X 78"D X 64"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Other.&lt;br&gt;
-Color: Silver&lt;br&gt;
-Weight: 59.4 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 58.3 or 59.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H117" s="60" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr">
@@ -18053,12 +18053,12 @@
       <c r="G118" s="60" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-RHONDA Loft Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Metal, Other construction is complemented by White tones for a polished look.&lt;br&gt;
+RHONDA Loft Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Metal, Other, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 41.5"W X 78"D X 64"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Other.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 58.3 lbs&lt;/p&gt;</t>
+Color: Black or Silver or White&lt;br&gt;
+Weight: 58.3 or 59.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H118" s="60" t="inlineStr">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
@@ -18209,8 +18209,8 @@
 ROTHWELL or Full Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal, construction is complemented by Matte Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 76.5"W X 56"D X 54"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
-&lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Matte Black&lt;br&gt;
+&lt;p&gt;Materials: Metal, Others.&lt;br&gt;
+Color: Matte Black or Matte White&lt;br&gt;
 Weight: 81.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -18297,7 +18297,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
@@ -18355,11 +18355,11 @@
       <c r="G120" s="68" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with ROTHWELL or Full Metal Bunk Bed, styled in Contemporary and designed for everyday comfort. This youth bunk bed is made to fit naturally into the room. With Metal, and Matte White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+ROTHWELL or Full Metal Bunk Bed brings a Contemporary look to your home with a refined, comfortable feel. As a youth bunk bed, it is designed to complement your space. The Metal, construction is complemented by Matte Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 76.5"W X 56"D X 54"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
-&lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Matte White&lt;br&gt;
+&lt;p&gt;Materials: Metal, Others.&lt;br&gt;
+Color: Matte Black or Matte White&lt;br&gt;
 Weight: 81.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -18446,7 +18446,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr">
@@ -18507,8 +18507,8 @@
 ROTHWELL or Twin Metal Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Matte Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 76.5"W X 41"D X 54"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
-&lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Matte Black&lt;br&gt;
+&lt;p&gt;Materials: Metal, Others.&lt;br&gt;
+Color: Matte Black or Matte White&lt;br&gt;
 Weight: 74.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -18595,7 +18595,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
@@ -18653,11 +18653,11 @@
       <c r="G122" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with ROTHWELL or Twin Metal Bunk Bed and its Contemporary character. As a youth bunk bed, it is designed to complement your space. Finished in Matte White tones, the Metal, build balances durability with visual appeal.&lt;br&gt;
+ROTHWELL or Twin Metal Bunk Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bunk bed, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Matte Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 76.5"W X 41"D X 54"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
-&lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Matte White&lt;br&gt;
+&lt;p&gt;Materials: Metal, Others.&lt;br&gt;
+Color: Matte Black or Matte White&lt;br&gt;
 Weight: 74.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
@@ -18807,8 +18807,8 @@
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Oak&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Espresso or Gray&lt;br&gt;
 Weight: 210 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -18893,7 +18893,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
@@ -18951,13 +18951,13 @@
       <c r="G124" s="27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SOLPINE or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Espresso tones for a polished look.&lt;br&gt;
+Make the room feel complete with SOLPINE or Full Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Oak tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 80 3/8"L X 56 1/2"W X 70 5/8"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Espresso&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Espresso or Gray&lt;br&gt;
 Weight: 210 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -19104,13 +19104,13 @@
       <c r="G125" s="27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with SOLPINE or Full Bunk Bed, styled in Transitional and designed for everyday comfort. As a youth bunk bed, it is designed to complement your space. With Solid Wood, Wood Veneer, and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with SOLPINE or Full Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Oak tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 80 3/8"L X 56 1/2"W X 70 5/8"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Espresso or Gray&lt;br&gt;
 Weight: 210 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -19195,7 +19195,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
@@ -19489,7 +19489,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr">
@@ -19551,8 +19551,8 @@
 Product Dimensions: 80"W X 72.5"D X 65.5"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
-Weight: 187.39 lbs&lt;/p&gt;</t>
+Color: Dark Walnut or Stain Gray or White&lt;br&gt;
+Weight: 187.39 or 188.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H128" s="34" t="inlineStr">
@@ -19636,7 +19636,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
@@ -19694,12 +19694,12 @@
       <c r="G129" s="34" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with SPRING CREEK or Full Bunk Bed, styled in Transitional and designed for everyday comfort. Built as a youth bunk bed, it pairs well with a wide range of interiors. With Solid Hardwood, Engineered Wood and Stain Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+SPRING CREEK or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Hardwood, Engineered Wood construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
 Product Dimensions: 80"W X 72.5"D X 65.5"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
-Color: Stain Gray&lt;br&gt;
-Weight: 187.39 lbs&lt;/p&gt;</t>
+Color: Dark Walnut or Stain Gray or White&lt;br&gt;
+Weight: 187.39 or 188.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H129" s="34" t="inlineStr">
@@ -19783,7 +19783,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
@@ -19841,12 +19841,12 @@
       <c r="G130" s="34" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SPRING CREEK or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Hardwood, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+SPRING CREEK or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. This youth bunk bed is made to fit naturally into the room. The Solid Hardwood, Engineered Wood construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
 Product Dimensions: 80"W X 72.5"D X 65.5"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 188.39 lbs&lt;/p&gt;</t>
+Color: Dark Walnut or Stain Gray or White&lt;br&gt;
+Weight: 187.39 or 188.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H130" s="34" t="inlineStr">
@@ -19930,7 +19930,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr">
@@ -20075,7 +20075,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
@@ -20220,7 +20220,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
@@ -20365,7 +20365,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr">
@@ -20577,9 +20577,9 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 UNIVERSITY or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Hardwood, Engineered Wood, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 59.5"W X 83"D X 71.5"H&lt;br&gt;
-Size: Twin Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle w/ 3 Underbed Drawers&lt;/p&gt;
+Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
+Color: Dark Walnut or Stain Gray or White&lt;br&gt;
 Weight: 296.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -20664,7 +20664,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -20722,11 +20722,11 @@
       <c r="G136" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with UNIVERSITY or Full Bunk Bed and its Transitional character. This youth bunk bed is made to fit naturally into the room. Finished in Stain Gray tones, the Solid Hardwood, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+UNIVERSITY or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Hardwood, Engineered Wood, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 59.5"W X 83"D X 71.5"H&lt;br&gt;
-Size: Twin Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle w/ 3 Underbed Drawers&lt;/p&gt;
+Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
-Color: Stain Gray&lt;br&gt;
+Color: Dark Walnut or Stain Gray or White&lt;br&gt;
 Weight: 296.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -20811,7 +20811,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr">
@@ -20869,11 +20869,11 @@
       <c r="G137" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-UNIVERSITY or Full Bunk Bed brings a Transitional look to your home with a refined, comfortable feel. Built as a youth bunk bed, it pairs well with a wide range of interiors. The Solid Hardwood, Engineered Wood construction is complemented by White tones for a polished look.&lt;br&gt;
+UNIVERSITY or Full Bunk Bed adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth bunk bed, it is designed to complement your space. Crafted from Solid Hardwood, Engineered Wood, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 59.5"W X 83"D X 71.5"H&lt;br&gt;
-Size: Twin Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle w/ 3 Underbed Drawers&lt;/p&gt;
+Size: Twin&lt;/p&gt;
 &lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Dark Walnut or Stain Gray or White&lt;br&gt;
 Weight: 296.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -20958,7 +20958,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -21101,7 +21101,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD138" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -21390,7 +21390,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD140" t="inlineStr">
@@ -21536,7 +21536,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
@@ -21595,15 +21595,15 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with ALLIE Bed and its Contemporary character. This youth bed is made to fit naturally into the room. Finished in Pearl White tones, the Fabric, Acrylic, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 84 1/8"L X 58"W X 54"H&lt;br&gt;
+Product Dimensions: 84 1/8"L X 58"W X 54"H / 80 1/2"L X 58"W X 54"H&lt;br&gt;
 Size: Full&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
 Felt-lined Top Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
-Color: Pearl White&lt;br&gt;
-Weight: 135.96 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 135.96 or 138.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H142" s="68" t="inlineStr">
@@ -21687,7 +21687,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD142" t="inlineStr">
@@ -21745,16 +21745,16 @@
       <c r="G143" s="68" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALLIE Bed brings a Contemporary look to your home with a refined, comfortable feel. Built as a youth bed, it pairs well with a wide range of interiors. The Fabric, Acrylic, Solid Wood, construction is complemented by Rose Gold tones for a polished look.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 58"W X 54"H&lt;br&gt;
+Make the room feel complete with ALLIE Bed and its Contemporary character. This youth bed is made to fit naturally into the room. Finished in Pearl White tones, the Fabric, Acrylic, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 84 1/8"L X 58"W X 54"H / 80 1/2"L X 58"W X 54"H&lt;br&gt;
 Size: Full&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers with Ball-bearing Metal Side Glides&lt;br&gt;
-Felt-lined Top Drawer&lt;br&gt;
-Optional Convertible Trundle or Drawer&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
-Color: Rose Gold&lt;br&gt;
-Weight: 138.2 lbs&lt;/p&gt;</t>
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
+Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 135.96 or 138.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H143" s="68" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr">
@@ -21897,15 +21897,15 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with ALLIE Bed and its Contemporary character. As a youth bed, it is designed to complement your space. Finished in Rose Gold tones, the Fabric, Acrylic, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 41 3/4"W X 54"H&lt;br&gt;
+Product Dimensions: 80 1/2"L X 41 3/4"W X 54"H / 84 1/8"L X 42 1/2"W X 54"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers with Ball-bearing Metal Side Glides&lt;br&gt;
 Felt-lined Top Drawer&lt;br&gt;
 Optional Convertible Trundle or Drawer&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
-Color: Rose Gold&lt;br&gt;
-Weight: 111 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Rose Gold or Pearl White&lt;br&gt;
+Weight: 111 or 109.62 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H144" s="27" t="inlineStr">
@@ -21989,7 +21989,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD144" t="inlineStr">
@@ -22047,16 +22047,16 @@
       <c r="G145" s="27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALLIE Bed brings a Contemporary look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Fabric, Acrylic, Solid Wood, construction is complemented by Pearl White tones for a polished look.&lt;br&gt;
-Product Dimensions: 84 1/8"L X 42 1/2"W X 54"H&lt;br&gt;
+Make the room feel complete with ALLIE Bed and its Contemporary character. As a youth bed, it is designed to complement your space. Finished in Rose Gold tones, the Fabric, Acrylic, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 41 3/4"W X 54"H / 84 1/8"L X 42 1/2"W X 54"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
-- Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
-Felt-lined Top Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
-Color: Pearl White&lt;br&gt;
-Weight: 109.62 lbs&lt;/p&gt;</t>
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers with Ball-bearing Metal Side Glides&lt;br&gt;
+Felt-lined Top Drawer&lt;br&gt;
+Optional Convertible Trundle or Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Rose Gold or Pearl White&lt;br&gt;
+Weight: 111 or 109.62 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H145" s="27" t="inlineStr">
@@ -22140,7 +22140,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
@@ -22199,14 +22199,14 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Elevate your space with ARISTON Bed, styled in Contemporary and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Leatherette, Mirror, Solid Wood, Wood Veneer, and Rose Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
-Product Dimensions: 82 1/4"L X 58"W X 54"H&lt;br&gt;
+Product Dimensions: 82 1/4"L X 58"W X 54"H / 82 3/4"L X 59"W X 58"H&lt;br&gt;
 Size: Full&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rose Gold&lt;br&gt;
-Weight: 117.6 lbs&lt;/p&gt;</t>
+Weight: 117.6 or 118.88 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H146" s="34" t="inlineStr">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr">
@@ -22348,15 +22348,15 @@
       <c r="G147" s="34" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ARISTON Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. This youth bed is made to fit naturally into the room. Crafted from Leatherette, Mirror, Solid Wood, Wood Veneer, it is finished in Rose Gold tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 82 3/4"L X 59"W X 58"H&lt;br&gt;
+Elevate your space with ARISTON Bed, styled in Contemporary and designed for everyday comfort. As a youth bed, it is designed to complement your space. With Leatherette, Mirror, Solid Wood, Wood Veneer, and Rose Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 82 1/4"L X 58"W X 54"H / 82 3/4"L X 59"W X 58"H&lt;br&gt;
 Size: Full&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rose Gold&lt;br&gt;
-Weight: 118.88 lbs&lt;/p&gt;</t>
+Weight: 117.6 or 118.88 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H147" s="34" t="inlineStr">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
@@ -22499,14 +22499,14 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ARISTON Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Leatherette, Mirror, Solid Wood, Wood Veneer, it is finished in Rose Gold tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 88 1/4"L X 65"W X 58"H&lt;br&gt;
+Product Dimensions: 88 1/4"L X 65"W X 58"H / 87 3/4"L X 65"W X 58"H&lt;br&gt;
 Size: Queen&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rose Gold&lt;br&gt;
-Weight: 135.34 lbs&lt;/p&gt;</t>
+Weight: 135.34 or 134.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H148" s="54" t="inlineStr">
@@ -22590,7 +22590,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
@@ -22648,15 +22648,15 @@
       <c r="G149" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with ARISTON Bed and its Contemporary character. As a youth bed, it is designed to complement your space. Finished in Rose Gold tones, the Leatherette, Mirror, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 87 3/4"L X 65"W X 58"H&lt;br&gt;
+ARISTON Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from Leatherette, Mirror, Solid Wood, Wood Veneer, it is finished in Rose Gold tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 88 1/4"L X 65"W X 58"H / 87 3/4"L X 65"W X 58"H&lt;br&gt;
 Size: Queen&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rose Gold&lt;br&gt;
-Weight: 134.8 lbs&lt;/p&gt;</t>
+Weight: 135.34 or 134.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H149" s="54" t="inlineStr">
@@ -22740,7 +22740,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
@@ -22799,14 +22799,14 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Elevate your space with ARISTON Bed, styled in Contemporary and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Leatherette, Mirror, Solid Wood, Wood Veneer, and Rose Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
-Product Dimensions: 82 1/4"L X 43"W X 54"H&lt;br&gt;
+Product Dimensions: 82 1/4"L X 43"W X 54"H / 82 3/4"L X 43"W X 58"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rose Gold&lt;br&gt;
-Weight: 99.18 lbs&lt;/p&gt;</t>
+Weight: 99.18 or 107.06 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H150" s="56" t="inlineStr">
@@ -22890,7 +22890,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr">
@@ -22948,15 +22948,15 @@
       <c r="G151" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ARISTON Bed adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Leatherette, Mirror, Solid Wood, Wood Veneer, it is finished in Rose Gold tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 82 3/4"L X 43"W X 58"H&lt;br&gt;
+Elevate your space with ARISTON Bed, styled in Contemporary and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Leatherette, Mirror, Solid Wood, Wood Veneer, and Rose Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 82 1/4"L X 43"W X 54"H / 82 3/4"L X 43"W X 58"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Foundation required Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Top Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rose Gold&lt;br&gt;
-Weight: 107.06 lbs&lt;/p&gt;</t>
+Weight: 99.18 or 107.06 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H151" s="56" t="inlineStr">
@@ -23040,7 +23040,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -23187,7 +23187,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr">
@@ -23334,7 +23334,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr">
@@ -23481,7 +23481,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD154" t="inlineStr">
@@ -23628,7 +23628,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD155" t="inlineStr">
@@ -23773,7 +23773,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD156" t="inlineStr">
@@ -23918,7 +23918,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr">
@@ -24063,7 +24063,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD158" t="inlineStr">
@@ -24123,10 +24123,10 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with CLEMENS Captain Bed and its Transitional character. As a youth bed, it is designed to complement your space. Finished in White tones, the Solid Hardwood, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 43.5"W X 80.5"D X 35.5"H&lt;br&gt;
-Size: Twin Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle w/ 3 Drawer Storage Unit&lt;/p&gt;
-&lt;p&gt;Materials: Solid Hardwood, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 175.26 lbs&lt;/p&gt;</t>
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood or Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: White or Midnight Blue or Dark Walnut&lt;br&gt;
+Weight: 175.26 or 176.13 or 172.87 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H159" s="65" t="inlineStr">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD159" t="inlineStr">
@@ -24268,12 +24268,12 @@
       <c r="G160" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CLEMENS Captain Bed brings a Transitional look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Solid Rubberwood, Engineered Wood construction is complemented by Midnight Blue tones for a polished look.&lt;br&gt;
+Make the room feel complete with CLEMENS Captain Bed and its Transitional character. As a youth bed, it is designed to complement your space. Finished in White tones, the Solid Hardwood, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 43.5"W X 80.5"D X 35.5"H&lt;br&gt;
-Size: Twin Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle w/ 3 Drawer Storage Unit&lt;/p&gt;
-&lt;p&gt;Materials: Solid Rubberwood, Engineered Wood.&lt;br&gt;
-Color: Midnight Blue&lt;br&gt;
-Weight: 176.13 lbs&lt;/p&gt;</t>
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood or Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: White or Midnight Blue or Dark Walnut&lt;br&gt;
+Weight: 175.26 or 176.13 or 172.87 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H160" s="65" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD160" t="inlineStr">
@@ -24419,12 +24419,12 @@
       <c r="G161" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with CLEMENS Captain Bed, styled in Transitional and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Solid Rubberwood, Engineered Wood and Dark Walnut tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with CLEMENS Captain Bed and its Transitional character. As a youth bed, it is designed to complement your space. Finished in White tones, the Solid Hardwood, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 43.5"W X 80.5"D X 35.5"H&lt;br&gt;
-Size: Twin Bonus storage &amp;amp; convenience features (from matching set pieces): Trundle w/ 3 Drawer Storage Unit&lt;/p&gt;
-&lt;p&gt;Materials: Solid Rubberwood, Engineered Wood.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
-Weight: 172.87 lbs&lt;/p&gt;</t>
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Solid Hardwood, Engineered Wood or Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: White or Midnight Blue or Dark Walnut&lt;br&gt;
+Weight: 175.26 or 176.13 or 172.87 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H161" s="65" t="inlineStr">
@@ -24512,7 +24512,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD161" t="inlineStr">
@@ -24657,7 +24657,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD162" t="inlineStr">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD163" t="inlineStr">
@@ -24948,7 +24948,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD164" t="inlineStr">
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD165" t="inlineStr">
@@ -25237,7 +25237,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD166" t="inlineStr">
@@ -25383,7 +25383,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD167" t="inlineStr">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD168" t="inlineStr">
@@ -25590,8 +25590,8 @@
 DUSTRACK Bed adds a Novelty touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from MDF, Particle Board, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 82 1/2"L X 41 1/2"W X 23 1/2"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
-&lt;p&gt;Materials: MDF, Particle Board.&lt;br&gt;
-Color: Blue&lt;br&gt;
+&lt;p&gt;Materials: MDF, Particle Board, Others.&lt;br&gt;
+Color: Blue or Red&lt;br&gt;
 Weight: 94.35 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD169" t="inlineStr">
@@ -25734,11 +25734,11 @@
       <c r="G170" s="34" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with DUSTRACK Bed and its Novelty character. As a youth bed, it is designed to complement your space. Finished in Red tones, the MDF, Particle Board, build balances durability with visual appeal.&lt;br&gt;
+DUSTRACK Bed adds a Novelty touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from MDF, Particle Board, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 82 1/2"L X 41 1/2"W X 23 1/2"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
-&lt;p&gt;Materials: MDF, Particle Board.&lt;br&gt;
-Color: Red&lt;br&gt;
+&lt;p&gt;Materials: MDF, Particle Board, Others.&lt;br&gt;
+Color: Blue or Red&lt;br&gt;
 Weight: 94.35 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25823,7 +25823,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD170" t="inlineStr">
@@ -25966,7 +25966,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD171" t="inlineStr">
@@ -26109,7 +26109,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD172" t="inlineStr">
@@ -26252,7 +26252,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr">
@@ -26538,7 +26538,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr">
@@ -26671,7 +26671,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD176" t="inlineStr">
@@ -26804,7 +26804,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD177" t="inlineStr">
@@ -26947,7 +26947,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD178" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD179" t="inlineStr">
@@ -27231,7 +27231,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD180" t="inlineStr">
@@ -27383,7 +27383,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD181" t="inlineStr">
@@ -27535,7 +27535,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD182" t="inlineStr">
@@ -27680,7 +27680,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD183" t="inlineStr">
@@ -27825,7 +27825,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD184" t="inlineStr">
@@ -27971,7 +27971,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD185" t="inlineStr">
@@ -28117,7 +28117,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD186" t="inlineStr">
@@ -28264,7 +28264,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD188" t="inlineStr">
@@ -28554,7 +28554,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr">
@@ -28701,7 +28701,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD190" t="inlineStr">
@@ -28846,7 +28846,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr">
@@ -28991,7 +28991,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD192" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD193" t="inlineStr">
@@ -29267,7 +29267,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD195" t="inlineStr">
@@ -29543,7 +29543,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD196" t="inlineStr">
@@ -29686,7 +29686,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD197" t="inlineStr">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD198" t="inlineStr">
@@ -29972,7 +29972,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr">
@@ -30120,7 +30120,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr">
@@ -30263,7 +30263,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr">
@@ -30406,7 +30406,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD202" t="inlineStr">
@@ -30549,7 +30549,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD203" t="inlineStr">
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD204" t="inlineStr">
@@ -30839,7 +30839,7 @@
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD205" t="inlineStr">
@@ -30982,7 +30982,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD206" t="inlineStr">
@@ -31125,7 +31125,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr">
@@ -31268,7 +31268,7 @@
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD208" t="inlineStr">
@@ -31411,7 +31411,7 @@
       </c>
       <c r="AC209" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD209" t="inlineStr">
@@ -31554,7 +31554,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
@@ -31687,7 +31687,7 @@
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD211" t="inlineStr">
@@ -31833,7 +31833,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -31979,7 +31979,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD213" t="inlineStr">
@@ -32122,7 +32122,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD214" t="inlineStr">
@@ -32265,7 +32265,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr">
@@ -32410,7 +32410,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
@@ -32555,7 +32555,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr">
@@ -32612,7 +32612,7 @@
 TRACKLITE Car Bed adds a Novelty touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from ABS, Engineered Wood, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 88.5"W X 39"D X 25"H&lt;/p&gt;
 &lt;p&gt;Materials: ABS, Engineered Wood.&lt;br&gt;
-Color: Red&lt;/p&gt;</t>
+Color: Red or White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H218" s="41" t="inlineStr">
@@ -32694,7 +32694,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
@@ -32748,10 +32748,10 @@
       <c r="G219" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with TRACKLITE Car Bed and its Novelty character. As a youth bed, it is designed to complement your space. Finished in White tones, the ABS, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+TRACKLITE Car Bed adds a Novelty touch while keeping the room feeling warm and welcoming. Built as a youth bed, it pairs well with a wide range of interiors. Crafted from ABS, Engineered Wood, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 88.5"W X 39"D X 25"H&lt;/p&gt;
 &lt;p&gt;Materials: ABS, Engineered Wood.&lt;br&gt;
-Color: White&lt;/p&gt;</t>
+Color: Red or White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H219" s="41" t="inlineStr">
@@ -32833,7 +32833,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr">
@@ -32894,8 +32894,8 @@
 TRACKSTER Car Bed brings a Novelty look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Leatherette, ABS, construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 91 3/4"L X 49 1/4"W X 34 1/2"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, ABS.&lt;br&gt;
-Color: Black&lt;br&gt;
+&lt;p&gt;Materials: Leatherette, ABS, Others.&lt;br&gt;
+Color: Black or Blue or Red or White&lt;br&gt;
 Weight: 156.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32980,7 +32980,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">
@@ -33038,11 +33038,11 @@
       <c r="G221" s="43" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with TRACKSTER Car Bed, styled in Novelty and designed for everyday comfort. Built as a youth bed, it pairs well with a wide range of interiors. With Leatherette, ABS, and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+TRACKSTER Car Bed brings a Novelty look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Leatherette, ABS, construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 91 3/4"L X 49 1/4"W X 34 1/2"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, ABS.&lt;br&gt;
-Color: Blue&lt;br&gt;
+&lt;p&gt;Materials: Leatherette, ABS, Others.&lt;br&gt;
+Color: Black or Blue or Red or White&lt;br&gt;
 Weight: 156.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -33127,7 +33127,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD221" t="inlineStr">
@@ -33185,11 +33185,11 @@
       <c r="G222" s="43" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-TRACKSTER Car Bed adds a Novelty touch while keeping the room feeling warm and welcoming. As a youth bed, it is designed to complement your space. Crafted from Leatherette, ABS, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+TRACKSTER Car Bed brings a Novelty look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Leatherette, ABS, construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 91 3/4"L X 49 1/4"W X 34 1/2"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, ABS.&lt;br&gt;
-Color: Red&lt;br&gt;
+&lt;p&gt;Materials: Leatherette, ABS, Others.&lt;br&gt;
+Color: Black or Blue or Red or White&lt;br&gt;
 Weight: 156.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr">
@@ -33332,11 +33332,11 @@
       <c r="G223" s="43" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with TRACKSTER Car Bed and its Novelty character. This youth bed is made to fit naturally into the room. Finished in White tones, the Leatherette, ABS, build balances durability with visual appeal.&lt;br&gt;
+TRACKSTER Car Bed brings a Novelty look to your home with a refined, comfortable feel. This youth bed is made to fit naturally into the room. The Leatherette, ABS, construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 91 3/4"L X 49 1/4"W X 34 1/2"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, ABS.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Leatherette, ABS, Others.&lt;br&gt;
+Color: Black or Blue or Red or White&lt;br&gt;
 Weight: 156.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -33421,7 +33421,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr">
@@ -33565,7 +33565,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr">
@@ -33711,7 +33711,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD225" t="inlineStr">
@@ -33857,7 +33857,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr">
@@ -34000,7 +34000,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr">
@@ -34143,7 +34143,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr">
@@ -34290,7 +34290,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr">
@@ -34437,7 +34437,7 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD230" t="inlineStr">
@@ -34584,7 +34584,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr">
@@ -34727,7 +34727,7 @@
       </c>
       <c r="AC232" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD232" t="inlineStr">
@@ -34786,9 +34786,9 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers&lt;br&gt;
 Felt-lined Top Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Acrylic, Solid Wood.&lt;br&gt;
-Color: Pearl White&lt;br&gt;
-Weight: 160.8 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 160.8 or 161 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H233" s="32" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD233" t="inlineStr">
@@ -34928,14 +34928,14 @@
       <c r="G234" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALLIE Chest brings a Contemporary look to your home with a refined, comfortable feel. This youth chest is made to fit naturally into the room. The Acrylic, Solid Wood, construction is complemented by Rose Gold tones for a polished look.&lt;br&gt;
+Make the room feel complete with ALLIE Chest and its Contemporary character. As a youth chest, it is designed to complement your space. Finished in Pearl White tones, the Acrylic, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 30 1/8"W X 16 1/2"D X 43 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers&lt;br&gt;
-Felt-lined Top Drawer&lt;/p&gt;
-&lt;p&gt;Materials: Acrylic, Solid Wood.&lt;br&gt;
-Color: Rose Gold&lt;br&gt;
-Weight: 161 lbs&lt;/p&gt;</t>
+Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 160.8 or 161 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H234" s="32" t="inlineStr">
@@ -35021,7 +35021,7 @@
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr">
@@ -35164,7 +35164,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr">
@@ -35307,7 +35307,7 @@
       </c>
       <c r="AC236" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD236" t="inlineStr">
@@ -35450,7 +35450,7 @@
       </c>
       <c r="AC237" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD237" t="inlineStr">
@@ -35508,8 +35508,8 @@
 Product Dimensions: 29"W X 17"D X 42"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or White&lt;br&gt;
 Weight: 76 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -35596,7 +35596,7 @@
       </c>
       <c r="AC238" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD238" t="inlineStr">
@@ -35650,12 +35650,12 @@
       <c r="G239" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with CORRY Chest, styled in Transitional and designed for everyday comfort. Built as a youth chest, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+CORRY Chest brings a Transitional look to your home with a refined, comfortable feel. This youth chest is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
 Product Dimensions: 29"W X 17"D X 42"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or White&lt;br&gt;
 Weight: 76 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -35742,7 +35742,7 @@
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD239" t="inlineStr">
@@ -35885,7 +35885,7 @@
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD240" t="inlineStr">
@@ -36028,7 +36028,7 @@
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD241" t="inlineStr">
@@ -36169,7 +36169,7 @@
       </c>
       <c r="AC242" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD242" t="inlineStr">
@@ -36310,7 +36310,7 @@
       </c>
       <c r="AC243" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD243" t="inlineStr">
@@ -36451,7 +36451,7 @@
       </c>
       <c r="AC244" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD244" t="inlineStr">
@@ -36600,7 +36600,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -36743,7 +36743,7 @@
       </c>
       <c r="AC246" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD246" t="inlineStr">
@@ -36887,7 +36887,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr">
@@ -37030,7 +37030,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD248" t="inlineStr">
@@ -37173,7 +37173,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr">
@@ -37327,7 +37327,7 @@
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD250" t="inlineStr">
@@ -37470,7 +37470,7 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr">
@@ -37614,7 +37614,7 @@
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD252" t="inlineStr">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD253" t="inlineStr">
@@ -37815,8 +37815,8 @@
 Product Dimensions: 28"W X 20.5"D X 50"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or Mahogany or White&lt;br&gt;
 Weight: 66 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AC254" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD254" t="inlineStr">
@@ -37957,12 +37957,12 @@
       <c r="G255" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with STAVROS Chest and its Rustic character. As a youth chest, it is designed to complement your space. Finished in Mahogany tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+STAVROS Chest adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a youth chest, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 28"W X 20.5"D X 50"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Mahogany&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or Mahogany or White&lt;br&gt;
 Weight: 66 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -38049,7 +38049,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr">
@@ -38103,12 +38103,12 @@
       <c r="G256" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-STAVROS Chest brings a Rustic look to your home with a refined, comfortable feel. This youth chest is made to fit naturally into the room. The Solid Wood, construction is complemented by White tones for a polished look.&lt;br&gt;
+STAVROS Chest adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a youth chest, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 28"W X 20.5"D X 50"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or Mahogany or White&lt;br&gt;
 Weight: 66 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -38195,7 +38195,7 @@
       </c>
       <c r="AC256" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD256" t="inlineStr">
@@ -38338,7 +38338,7 @@
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD257" t="inlineStr">
@@ -38483,7 +38483,7 @@
       </c>
       <c r="AC258" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD258" t="inlineStr">
@@ -38626,7 +38626,7 @@
       </c>
       <c r="AC259" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD259" t="inlineStr">
@@ -38685,9 +38685,9 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers&lt;br&gt;
 Felt-lined Top Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Acrylic, Solid Wood.&lt;br&gt;
-Color: Pearl White&lt;br&gt;
-Weight: 200.93 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 200.93 or 198 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H260" s="60" t="inlineStr">
@@ -38773,7 +38773,7 @@
       </c>
       <c r="AC260" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD260" t="inlineStr">
@@ -38827,14 +38827,14 @@
       <c r="G261" s="60" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALLIE Dresser adds a Contemporary touch while keeping the room feeling warm and welcoming. As a youth dresser, it is designed to complement your space. Crafted from Acrylic, Solid Wood, it is finished in Rose Gold tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with ALLIE Dresser, styled in Contemporary and designed for everyday comfort. Built as a youth dresser, it pairs well with a wide range of interiors. With Acrylic, Solid Wood, and Pearl White tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 54 1/2"W X 16 1/2"D X 34"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers&lt;br&gt;
-Felt-lined Top Drawer&lt;/p&gt;
-&lt;p&gt;Materials: Acrylic, Solid Wood.&lt;br&gt;
-Color: Rose Gold&lt;br&gt;
-Weight: 198 lbs&lt;/p&gt;</t>
+Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 200.93 or 198 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H261" s="60" t="inlineStr">
@@ -38920,7 +38920,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr">
@@ -39063,7 +39063,7 @@
       </c>
       <c r="AC262" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD262" t="inlineStr">
@@ -39206,7 +39206,7 @@
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD263" t="inlineStr">
@@ -39264,8 +39264,8 @@
 Product Dimensions: 48"W X 17"D X 34"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or White&lt;br&gt;
 Weight: 94.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -39352,7 +39352,7 @@
       </c>
       <c r="AC264" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD264" t="inlineStr">
@@ -39406,12 +39406,12 @@
       <c r="G265" s="60" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with CORRY Dresser and its Transitional character. This youth dresser is made to fit naturally into the room. Finished in White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+CORRY Dresser adds a Transitional touch while keeping the room feeling warm and welcoming. As a youth dresser, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 48"W X 17"D X 34"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or White&lt;br&gt;
 Weight: 94.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -39498,7 +39498,7 @@
       </c>
       <c r="AC265" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD265" t="inlineStr">
@@ -39641,7 +39641,7 @@
       </c>
       <c r="AC266" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD266" t="inlineStr">
@@ -39784,7 +39784,7 @@
       </c>
       <c r="AC267" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD267" t="inlineStr">
@@ -39925,7 +39925,7 @@
       </c>
       <c r="AC268" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD268" t="inlineStr">
@@ -40066,7 +40066,7 @@
       </c>
       <c r="AC269" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD269" t="inlineStr">
@@ -40208,7 +40208,7 @@
       </c>
       <c r="AC270" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD270" t="inlineStr">
@@ -40357,7 +40357,7 @@
       </c>
       <c r="AC271" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD271" t="inlineStr">
@@ -40500,7 +40500,7 @@
       </c>
       <c r="AC272" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD272" t="inlineStr">
@@ -40644,7 +40644,7 @@
       </c>
       <c r="AC273" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD273" t="inlineStr">
@@ -40787,7 +40787,7 @@
       </c>
       <c r="AC274" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD274" t="inlineStr">
@@ -40930,7 +40930,7 @@
       </c>
       <c r="AC275" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD275" t="inlineStr">
@@ -41074,7 +41074,7 @@
       </c>
       <c r="AC276" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD276" t="inlineStr">
@@ -41217,7 +41217,7 @@
       </c>
       <c r="AC277" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD277" t="inlineStr">
@@ -41272,11 +41272,11 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Elevate your space with STAVROS Dresser, styled in Rustic and designed for everyday comfort. Built as a youth dresser, it pairs well with a wide range of interiors. With Solid Wood, and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
-Product Dimensions: 52"W X 21"D X 34"H&lt;/p&gt;
+Product Dimensions: 52"W X 21"D X 34"H / 52"W X 20.5"D X 34"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or Mahogany or White&lt;br&gt;
 Weight: 78 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -41363,7 +41363,7 @@
       </c>
       <c r="AC278" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD278" t="inlineStr">
@@ -41417,12 +41417,12 @@
       <c r="G279" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-STAVROS Dresser adds a Rustic touch while keeping the room feeling warm and welcoming. As a youth dresser, it is designed to complement your space. Crafted from Solid Wood, it is finished in Mahogany tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 52"W X 20.5"D X 34"H&lt;/p&gt;
+Elevate your space with STAVROS Dresser, styled in Rustic and designed for everyday comfort. Built as a youth dresser, it pairs well with a wide range of interiors. With Solid Wood, and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 52"W X 21"D X 34"H / 52"W X 20.5"D X 34"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Mahogany&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or Mahogany or White&lt;br&gt;
 Weight: 78 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -41509,7 +41509,7 @@
       </c>
       <c r="AC279" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD279" t="inlineStr">
@@ -41563,12 +41563,12 @@
       <c r="G280" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with STAVROS Dresser and its Rustic character. This youth dresser is made to fit naturally into the room. Finished in White tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 52"W X 20.5"D X 34"H&lt;/p&gt;
+Elevate your space with STAVROS Dresser, styled in Rustic and designed for everyday comfort. Built as a youth dresser, it pairs well with a wide range of interiors. With Solid Wood, and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 52"W X 21"D X 34"H / 52"W X 20.5"D X 34"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or Mahogany or White&lt;br&gt;
 Weight: 78 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -41655,7 +41655,7 @@
       </c>
       <c r="AC280" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD280" t="inlineStr">
@@ -41798,7 +41798,7 @@
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD281" t="inlineStr">
@@ -41943,7 +41943,7 @@
       </c>
       <c r="AC282" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD282" t="inlineStr">
@@ -42087,7 +42087,7 @@
       </c>
       <c r="AC283" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD283" t="inlineStr">
@@ -42146,9 +42146,9 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers&lt;br&gt;
 Felt-lined Top Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Acrylic, Solid Wood.&lt;br&gt;
-Color: Pearl White&lt;br&gt;
-Weight: 56.42 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 56.42 or 57 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H284" s="51" t="inlineStr">
@@ -42234,7 +42234,7 @@
       </c>
       <c r="AC284" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD284" t="inlineStr">
@@ -42288,14 +42288,14 @@
       <c r="G285" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALLIE Nightstand brings a Contemporary look to your home with a refined, comfortable feel. As a youth night stand, it is designed to complement your space. The Acrylic, Solid Wood, construction is complemented by Rose Gold tones for a polished look.&lt;br&gt;
+Make the room feel complete with ALLIE Nightstand and its Contemporary character. Built as a youth night stand, it pairs well with a wide range of interiors. Finished in Pearl White tones, the Acrylic, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 22 7/8"W X 16 1/2"D X 24"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): English Dovetail Drawers&lt;br&gt;
-Felt-lined Top Drawer&lt;/p&gt;
-&lt;p&gt;Materials: Acrylic, Solid Wood.&lt;br&gt;
-Color: Rose Gold&lt;br&gt;
-Weight: 57 lbs&lt;/p&gt;</t>
+Felt-lined Top Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 56.42 or 57 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H285" s="51" t="inlineStr">
@@ -42381,7 +42381,7 @@
       </c>
       <c r="AC285" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD285" t="inlineStr">
@@ -42524,7 +42524,7 @@
       </c>
       <c r="AC286" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD286" t="inlineStr">
@@ -42668,7 +42668,7 @@
       </c>
       <c r="AC287" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD287" t="inlineStr">
@@ -42811,7 +42811,7 @@
       </c>
       <c r="AC288" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD288" t="inlineStr">
@@ -42869,8 +42869,8 @@
 Product Dimensions: 19"W X 16"D X 21"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or White&lt;br&gt;
 Weight: 28.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -42957,7 +42957,7 @@
       </c>
       <c r="AC289" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD289" t="inlineStr">
@@ -43011,12 +43011,12 @@
       <c r="G290" s="68" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with CORRY Nightstand and its Transitional character. Built as a youth night stand, it pairs well with a wide range of interiors. Finished in White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+CORRY Nightstand adds a Transitional touch while keeping the room feeling warm and welcoming. This youth night stand is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 19"W X 16"D X 21"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or White&lt;br&gt;
 Weight: 28.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -43103,7 +43103,7 @@
       </c>
       <c r="AC290" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD290" t="inlineStr">
@@ -43246,7 +43246,7 @@
       </c>
       <c r="AC291" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD291" t="inlineStr">
@@ -43389,7 +43389,7 @@
       </c>
       <c r="AC292" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD292" t="inlineStr">
@@ -43530,7 +43530,7 @@
       </c>
       <c r="AC293" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD293" t="inlineStr">
@@ -43671,7 +43671,7 @@
       </c>
       <c r="AC294" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD294" t="inlineStr">
@@ -43820,7 +43820,7 @@
       </c>
       <c r="AC295" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD295" t="inlineStr">
@@ -43963,7 +43963,7 @@
       </c>
       <c r="AC296" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD296" t="inlineStr">
@@ -44107,7 +44107,7 @@
       </c>
       <c r="AC297" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD297" t="inlineStr">
@@ -44254,7 +44254,7 @@
       </c>
       <c r="AC298" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD298" t="inlineStr">
@@ -44397,7 +44397,7 @@
       </c>
       <c r="AC299" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD299" t="inlineStr">
@@ -44541,7 +44541,7 @@
       </c>
       <c r="AC300" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD300" t="inlineStr">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="AC301" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD301" t="inlineStr">
@@ -44742,8 +44742,8 @@
 Product Dimensions: 21"W X 15"D X 25"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or Mahogany or White&lt;br&gt;
 Weight: 26 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -44830,7 +44830,7 @@
       </c>
       <c r="AC302" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD302" t="inlineStr">
@@ -44884,12 +44884,12 @@
       <c r="G303" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-STAVROS Nightstand brings a Rustic look to your home with a refined, comfortable feel. As a youth night stand, it is designed to complement your space. The Solid Wood, construction is complemented by Mahogany tones for a polished look.&lt;br&gt;
+Make the room feel complete with STAVROS Nightstand and its Rustic character. Built as a youth night stand, it pairs well with a wide range of interiors. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 21"W X 15"D X 25"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Mahogany&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or Mahogany or White&lt;br&gt;
 Weight: 26 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -44976,7 +44976,7 @@
       </c>
       <c r="AC303" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD303" t="inlineStr">
@@ -45030,12 +45030,12 @@
       <c r="G304" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with STAVROS Nightstand, styled in Rustic and designed for everyday comfort. This youth night stand is made to fit naturally into the room. With Solid Wood, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with STAVROS Nightstand and its Rustic character. Built as a youth night stand, it pairs well with a wide range of interiors. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 21"W X 15"D X 25"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or Mahogany or White&lt;br&gt;
 Weight: 26 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -45122,7 +45122,7 @@
       </c>
       <c r="AC304" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD304" t="inlineStr">
@@ -45265,7 +45265,7 @@
       </c>
       <c r="AC305" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD305" t="inlineStr">
@@ -45410,7 +45410,7 @@
       </c>
       <c r="AC306" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD306" t="inlineStr">
@@ -45553,7 +45553,7 @@
       </c>
       <c r="AC307" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD307" t="inlineStr">
@@ -45696,7 +45696,7 @@
       </c>
       <c r="AC308" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD308" t="inlineStr">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="AC309" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD309" t="inlineStr">
@@ -45982,7 +45982,7 @@
       </c>
       <c r="AC310" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD310" t="inlineStr">
@@ -46040,9 +46040,9 @@
 Product Dimensions: 75 5/8"L X 40 7/8"W X 9 3/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 46.2 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or White&lt;br&gt;
+Weight: 46.2 or 48.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H311" s="65" t="inlineStr">
@@ -46132,7 +46132,7 @@
       </c>
       <c r="AC311" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD311" t="inlineStr">
@@ -46186,13 +46186,13 @@
       <c r="G312" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HOOPLE Trundle brings a Transitional look to your home with a refined, comfortable feel. This youth accessory is made to fit naturally into the room. The Solid Wood, construction is complemented by White tones for a polished look.&lt;br&gt;
+Make the room feel complete with HOOPLE Trundle and its Transitional character. As a youth accessory, it is designed to complement your space. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 75 5/8"L X 40 7/8"W X 9 3/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 48.4 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or White&lt;br&gt;
+Weight: 46.2 or 48.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H312" s="65" t="inlineStr">
@@ -46282,7 +46282,7 @@
       </c>
       <c r="AC312" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD312" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="AC313" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD313" t="inlineStr">
@@ -46480,12 +46480,12 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 OMNUS Trundle brings a Transitional look to your home with a refined, comfortable feel. As a youth accessory, it is designed to complement your space. The Solid Wood, Wood Veneer, construction is complemented by Cherry tones for a polished look.&lt;br&gt;
-Product Dimensions: 74 1/4"L X 40 1/2"W X 10 3/4"H&lt;/p&gt;
+Product Dimensions: 74 1/4"L X 40 1/2"W X 10 3/4"H / 40.5"W X 74"D X 10.5"H / 75"W X 40.5"D X 11"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Cherry&lt;br&gt;
-Weight: 43.65 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others or Solid Wood, Others or Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
+Color: Cherry or Espresso or White&lt;br&gt;
+Weight: 43.65 or 41.8 or 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H314" s="39" t="inlineStr">
@@ -46571,7 +46571,7 @@
       </c>
       <c r="AC314" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD314" t="inlineStr">
@@ -46719,7 +46719,7 @@
       </c>
       <c r="AC315" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD315" t="inlineStr">
@@ -46862,7 +46862,7 @@
       </c>
       <c r="AC316" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD316" t="inlineStr">
@@ -47005,7 +47005,7 @@
       </c>
       <c r="AC317" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD317" t="inlineStr">
@@ -47146,7 +47146,7 @@
       </c>
       <c r="AC318" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD318" t="inlineStr">
@@ -47200,13 +47200,13 @@
       <c r="G319" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with OMNUS Trundle, styled in Transitional and designed for everyday comfort. This youth trundle is made to fit naturally into the room. With Solid Wood, and Espresso tones, it blends structure and softness in one clean profile.&lt;br&gt;
-Product Dimensions: 40.5"W X 74"D X 10.5"H&lt;/p&gt;
+OMNUS Trundle brings a Transitional look to your home with a refined, comfortable feel. As a youth accessory, it is designed to complement your space. The Solid Wood, Wood Veneer, construction is complemented by Cherry tones for a polished look.&lt;br&gt;
+Product Dimensions: 74 1/4"L X 40 1/2"W X 10 3/4"H / 40.5"W X 74"D X 10.5"H / 75"W X 40.5"D X 11"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Converts to Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Espresso&lt;br&gt;
-Weight: 41.8 lbs&lt;/p&gt;</t>
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others or Solid Wood, Others or Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
+Color: Cherry or Espresso or White&lt;br&gt;
+Weight: 43.65 or 41.8 or 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H319" s="39" t="inlineStr">
@@ -47296,7 +47296,7 @@
       </c>
       <c r="AC319" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD319" t="inlineStr">
@@ -47350,13 +47350,13 @@
       <c r="G320" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-OMNUS Trundle adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth trundle, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 75"W X 40.5"D X 11"H&lt;/p&gt;
+OMNUS Trundle brings a Transitional look to your home with a refined, comfortable feel. As a youth accessory, it is designed to complement your space. The Solid Wood, Wood Veneer, construction is complemented by Cherry tones for a polished look.&lt;br&gt;
+Product Dimensions: 74 1/4"L X 40 1/2"W X 10 3/4"H / 40.5"W X 74"D X 10.5"H / 75"W X 40.5"D X 11"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Converts to Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 44 lbs&lt;/p&gt;</t>
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others or Solid Wood, Others or Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
+Color: Cherry or Espresso or White&lt;br&gt;
+Weight: 43.65 or 41.8 or 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H320" s="39" t="inlineStr">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="AC320" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD320" t="inlineStr">
@@ -47500,9 +47500,9 @@
 Product Dimensions: 74 1/4"W X 40 1/2"D X 10 3/4"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
-Weight: 82.67 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or Gray or White&lt;br&gt;
+Weight: 82.67 or 83.75 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H321" s="41" t="inlineStr">
@@ -47592,7 +47592,7 @@
       </c>
       <c r="AC321" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD321" t="inlineStr">
@@ -47646,13 +47646,13 @@
       <c r="G322" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-OMNUS Trundle w/ 2 Dividers brings a Transitional look to your home with a refined, comfortable feel. This youth trundle is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Make the room feel complete with OMNUS Trundle w/ 2 Dividers and its Transitional character. As a youth trundle, it is designed to complement your space. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 74 1/4"W X 40 1/2"D X 10 3/4"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 82.67 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or Gray or White&lt;br&gt;
+Weight: 82.67 or 83.75 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H322" s="41" t="inlineStr">
@@ -47738,7 +47738,7 @@
       </c>
       <c r="AC322" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD322" t="inlineStr">
@@ -47792,13 +47792,13 @@
       <c r="G323" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with OMNUS Trundle w/ 2 Dividers, styled in Transitional and designed for everyday comfort. Built as a youth trundle, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with OMNUS Trundle w/ 2 Dividers and its Transitional character. As a youth trundle, it is designed to complement your space. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 74 1/4"W X 40 1/2"D X 10 3/4"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 83.75 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or Gray or White&lt;br&gt;
+Weight: 82.67 or 83.75 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H323" s="41" t="inlineStr">
@@ -47884,7 +47884,7 @@
       </c>
       <c r="AC323" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD323" t="inlineStr">
@@ -48027,7 +48027,7 @@
       </c>
       <c r="AC324" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD324" t="inlineStr">
@@ -48170,7 +48170,7 @@
       </c>
       <c r="AC325" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD325" t="inlineStr">
@@ -48313,7 +48313,7 @@
       </c>
       <c r="AC326" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD326" t="inlineStr">
@@ -48454,7 +48454,7 @@
       </c>
       <c r="AC327" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD327" t="inlineStr">
@@ -48517,8 +48517,8 @@
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Large Underbed Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or Mahogany&lt;br&gt;
 Weight: 171 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -48603,7 +48603,7 @@
       </c>
       <c r="AC328" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD328" t="inlineStr">
@@ -48661,13 +48661,13 @@
       <c r="G329" s="68" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MARINOS Captain Bed brings a Rustic look to your home with a refined, comfortable feel. Built as a youth day bed, it pairs well with a wide range of interiors. The Solid Wood, construction is complemented by Mahogany tones for a polished look.&lt;br&gt;
+Make the room feel complete with MARINOS Captain Bed and its Rustic character. This youth day bed is made to fit naturally into the room. Finished in Gray tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 78"W X 41"D X 34"H&lt;br&gt;
 Size: Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Large Underbed Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
-Color: Mahogany&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
+Color: Gray or Mahogany&lt;br&gt;
 Weight: 171 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -48752,7 +48752,7 @@
       </c>
       <c r="AC329" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD329" t="inlineStr">
@@ -48810,8 +48810,8 @@
 Product Dimensions: 48"W X 20"D X 32"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Cherry&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Cherry or Dark Walnut or White&lt;br&gt;
 Weight: 88.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -48898,7 +48898,7 @@
       </c>
       <c r="AC330" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD330" t="inlineStr">
@@ -48952,12 +48952,12 @@
       <c r="G331" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with OMNUS Desk and its Transitional character. As a youth desk, it is designed to complement your space. Finished in Dark Walnut tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+OMNUS Desk adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth desk, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Cherry tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 48"W X 20"D X 32"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Cherry or Dark Walnut or White&lt;br&gt;
 Weight: 88.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -49044,7 +49044,7 @@
       </c>
       <c r="AC331" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD331" t="inlineStr">
@@ -49098,12 +49098,12 @@
       <c r="G332" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-OMNUS Desk brings a Transitional look to your home with a refined, comfortable feel. This youth desk is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by White tones for a polished look.&lt;br&gt;
+OMNUS Desk adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a youth desk, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Cherry tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 48"W X 20"D X 32"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Cherry or Dark Walnut or White&lt;br&gt;
 Weight: 88.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -49190,7 +49190,7 @@
       </c>
       <c r="AC332" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD332" t="inlineStr">
@@ -49248,9 +49248,9 @@
 Product Dimensions: 46"W X 12"D X 24"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Cherry&lt;br&gt;
-Weight: 29.76 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Cherry or Dark Walnut or White&lt;br&gt;
+Weight: 29.76 or 27.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H333" s="56" t="inlineStr">
@@ -49336,7 +49336,7 @@
       </c>
       <c r="AC333" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD333" t="inlineStr">
@@ -49390,13 +49390,13 @@
       <c r="G334" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with OMNUS Hutch, styled in Transitional and designed for everyday comfort. As a youth desk, it is designed to complement your space. With Solid Wood, Wood Veneer, and Dark Walnut tones, it blends structure and softness in one clean profile.&lt;br&gt;
+OMNUS Hutch brings a Transitional look to your home with a refined, comfortable feel. Built as a youth desk, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Cherry tones for a polished look.&lt;br&gt;
 Product Dimensions: 46"W X 12"D X 24"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
-Weight: 27.6 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Cherry or Dark Walnut or White&lt;br&gt;
+Weight: 29.76 or 27.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H334" s="56" t="inlineStr">
@@ -49482,7 +49482,7 @@
       </c>
       <c r="AC334" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD334" t="inlineStr">
@@ -49536,13 +49536,13 @@
       <c r="G335" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-OMNUS Hutch adds a Transitional touch while keeping the room feeling warm and welcoming. This youth desk is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+OMNUS Hutch brings a Transitional look to your home with a refined, comfortable feel. Built as a youth desk, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Cherry tones for a polished look.&lt;br&gt;
 Product Dimensions: 46"W X 12"D X 24"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 27.6 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Cherry or Dark Walnut or White&lt;br&gt;
+Weight: 29.76 or 27.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H335" s="56" t="inlineStr">
@@ -49628,7 +49628,7 @@
       </c>
       <c r="AC335" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD335" t="inlineStr">
@@ -49771,7 +49771,7 @@
       </c>
       <c r="AC336" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD336" t="inlineStr">

--- a/FOA Singles/Youth-Single.xlsx
+++ b/FOA Singles/Youth-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/FOA Singles/Youth-Single.xlsx
+++ b/FOA Singles/Youth-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
